--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K245"/>
+  <dimension ref="A1:K261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11308,16 +11308,16 @@
         <v>2025</v>
       </c>
       <c r="D221" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -11700,16 +11700,16 @@
         <v>2025</v>
       </c>
       <c r="D229" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -12513,6 +12513,790 @@
         </is>
       </c>
       <c r="K245" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D246" t="n">
+        <v>44</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>4846</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Rosane Custódio</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D247" t="n">
+        <v>44</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>4623</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D248" t="n">
+        <v>44</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>4590</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D249" t="n">
+        <v>44</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>2679</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D250" t="n">
+        <v>45</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>5248</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D251" t="n">
+        <v>45</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>5230</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D252" t="n">
+        <v>45</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>5226</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D253" t="n">
+        <v>45</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>5213</v>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D254" t="n">
+        <v>45</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>5179</v>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D255" t="n">
+        <v>45</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>5147</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D256" t="n">
+        <v>45</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>5138</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D257" t="n">
+        <v>45</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>5118</v>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D258" t="n">
+        <v>45</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>5112</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D259" t="n">
+        <v>45</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>4992</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D260" t="n">
+        <v>45</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>4973</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Kleberson Matias</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D261" t="n">
+        <v>45</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>5104</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -12529,7 +13313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K727"/>
+  <dimension ref="A1:K775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44725,7 +45509,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -44945,16 +45729,16 @@
         <v>2025</v>
       </c>
       <c r="D659" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G659" t="n">
@@ -44965,7 +45749,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -47150,16 +47934,16 @@
         <v>2025</v>
       </c>
       <c r="D704" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -47170,7 +47954,7 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
@@ -47493,16 +48277,16 @@
         <v>2025</v>
       </c>
       <c r="D711" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G711" t="n">
@@ -47513,7 +48297,7 @@
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
@@ -47567,7 +48351,7 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
@@ -47591,16 +48375,16 @@
         <v>2025</v>
       </c>
       <c r="D713" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G713" t="n">
@@ -47611,7 +48395,7 @@
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
@@ -47640,16 +48424,16 @@
         <v>2025</v>
       </c>
       <c r="D714" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G714" t="n">
@@ -47660,7 +48444,7 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
@@ -47885,16 +48669,16 @@
         <v>2025</v>
       </c>
       <c r="D719" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G719" t="n">
@@ -47905,7 +48689,7 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
@@ -47934,16 +48718,16 @@
         <v>2025</v>
       </c>
       <c r="D720" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G720" t="n">
@@ -47954,7 +48738,7 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
@@ -47983,16 +48767,16 @@
         <v>2025</v>
       </c>
       <c r="D721" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="G721" t="n">
@@ -48003,12 +48787,12 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
@@ -48306,6 +49090,2358 @@
         </is>
       </c>
       <c r="K727" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D728" t="n">
+        <v>44</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G728" t="n">
+        <v>4865</v>
+      </c>
+      <c r="H728" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D729" t="n">
+        <v>44</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G729" t="n">
+        <v>4849</v>
+      </c>
+      <c r="H729" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D730" t="n">
+        <v>44</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G730" t="n">
+        <v>4848</v>
+      </c>
+      <c r="H730" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D731" t="n">
+        <v>44</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G731" t="n">
+        <v>4844</v>
+      </c>
+      <c r="H731" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D732" t="n">
+        <v>45</v>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G732" t="n">
+        <v>4837</v>
+      </c>
+      <c r="H732" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D733" t="n">
+        <v>45</v>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G733" t="n">
+        <v>4836</v>
+      </c>
+      <c r="H733" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D734" t="n">
+        <v>45</v>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G734" t="n">
+        <v>4831</v>
+      </c>
+      <c r="H734" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D735" t="n">
+        <v>45</v>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G735" t="n">
+        <v>4814</v>
+      </c>
+      <c r="H735" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D736" t="n">
+        <v>44</v>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G736" t="n">
+        <v>4792</v>
+      </c>
+      <c r="H736" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D737" t="n">
+        <v>44</v>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G737" t="n">
+        <v>4745</v>
+      </c>
+      <c r="H737" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D738" t="n">
+        <v>45</v>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G738" t="n">
+        <v>4718</v>
+      </c>
+      <c r="H738" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D739" t="n">
+        <v>44</v>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G739" t="n">
+        <v>4679</v>
+      </c>
+      <c r="H739" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D740" t="n">
+        <v>45</v>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G740" t="n">
+        <v>4677</v>
+      </c>
+      <c r="H740" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D741" t="n">
+        <v>44</v>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G741" t="n">
+        <v>4656</v>
+      </c>
+      <c r="H741" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D742" t="n">
+        <v>44</v>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G742" t="n">
+        <v>4636</v>
+      </c>
+      <c r="H742" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D743" t="n">
+        <v>45</v>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G743" t="n">
+        <v>4605</v>
+      </c>
+      <c r="H743" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D744" t="n">
+        <v>45</v>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G744" t="n">
+        <v>4578</v>
+      </c>
+      <c r="H744" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D745" t="n">
+        <v>45</v>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G745" t="n">
+        <v>4527</v>
+      </c>
+      <c r="H745" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D746" t="n">
+        <v>44</v>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G746" t="n">
+        <v>4510</v>
+      </c>
+      <c r="H746" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D747" t="n">
+        <v>44</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G747" t="n">
+        <v>4499</v>
+      </c>
+      <c r="H747" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D748" t="n">
+        <v>45</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G748" t="n">
+        <v>4445</v>
+      </c>
+      <c r="H748" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D749" t="n">
+        <v>45</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G749" t="n">
+        <v>5274</v>
+      </c>
+      <c r="H749" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D750" t="n">
+        <v>45</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G750" t="n">
+        <v>5273</v>
+      </c>
+      <c r="H750" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D751" t="n">
+        <v>45</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G751" t="n">
+        <v>5205</v>
+      </c>
+      <c r="H751" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D752" t="n">
+        <v>45</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G752" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H752" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D753" t="n">
+        <v>45</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G753" t="n">
+        <v>5191</v>
+      </c>
+      <c r="H753" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D754" t="n">
+        <v>45</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G754" t="n">
+        <v>5188</v>
+      </c>
+      <c r="H754" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D755" t="n">
+        <v>45</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G755" t="n">
+        <v>5186</v>
+      </c>
+      <c r="H755" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D756" t="n">
+        <v>45</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G756" t="n">
+        <v>5185</v>
+      </c>
+      <c r="H756" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D757" t="n">
+        <v>45</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G757" t="n">
+        <v>5164</v>
+      </c>
+      <c r="H757" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D758" t="n">
+        <v>45</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G758" t="n">
+        <v>5135</v>
+      </c>
+      <c r="H758" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D759" t="n">
+        <v>45</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G759" t="n">
+        <v>5130</v>
+      </c>
+      <c r="H759" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D760" t="n">
+        <v>45</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G760" t="n">
+        <v>5127</v>
+      </c>
+      <c r="H760" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D761" t="n">
+        <v>45</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G761" t="n">
+        <v>5092</v>
+      </c>
+      <c r="H761" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D762" t="n">
+        <v>45</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G762" t="n">
+        <v>5055</v>
+      </c>
+      <c r="H762" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D763" t="n">
+        <v>45</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G763" t="n">
+        <v>5026</v>
+      </c>
+      <c r="H763" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D764" t="n">
+        <v>45</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G764" t="n">
+        <v>5016</v>
+      </c>
+      <c r="H764" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D765" t="n">
+        <v>45</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G765" t="n">
+        <v>4968</v>
+      </c>
+      <c r="H765" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D766" t="n">
+        <v>45</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G766" t="n">
+        <v>4966</v>
+      </c>
+      <c r="H766" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D767" t="n">
+        <v>45</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G767" t="n">
+        <v>4944</v>
+      </c>
+      <c r="H767" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D768" t="n">
+        <v>45</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G768" t="n">
+        <v>4918</v>
+      </c>
+      <c r="H768" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D769" t="n">
+        <v>45</v>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G769" t="n">
+        <v>4905</v>
+      </c>
+      <c r="H769" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D770" t="n">
+        <v>45</v>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G770" t="n">
+        <v>4896</v>
+      </c>
+      <c r="H770" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D771" t="n">
+        <v>45</v>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G771" t="n">
+        <v>4863</v>
+      </c>
+      <c r="H771" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D772" t="n">
+        <v>45</v>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G772" t="n">
+        <v>4845</v>
+      </c>
+      <c r="H772" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D773" t="n">
+        <v>45</v>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G773" t="n">
+        <v>4736</v>
+      </c>
+      <c r="H773" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D774" t="n">
+        <v>45</v>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G774" t="n">
+        <v>4595</v>
+      </c>
+      <c r="H774" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D775" t="n">
+        <v>45</v>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="G775" t="n">
+        <v>4305</v>
+      </c>
+      <c r="H775" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -12754,7 +12754,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -48400,7 +48400,7 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
@@ -48694,7 +48694,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
@@ -49331,7 +49331,7 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
@@ -49380,7 +49380,7 @@
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
@@ -49429,7 +49429,7 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
@@ -49625,7 +49625,7 @@
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
@@ -49870,7 +49870,7 @@
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
@@ -49968,7 +49968,7 @@
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
@@ -50115,7 +50115,7 @@
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
@@ -50164,7 +50164,7 @@
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -50213,7 +50213,7 @@
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
@@ -50409,7 +50409,7 @@
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
@@ -50458,7 +50458,7 @@
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
@@ -50556,7 +50556,7 @@
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
@@ -50654,7 +50654,7 @@
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
@@ -50703,7 +50703,7 @@
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
@@ -50752,7 +50752,7 @@
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
@@ -50850,7 +50850,7 @@
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
@@ -50997,7 +50997,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
@@ -51095,7 +51095,7 @@
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
@@ -51193,7 +51193,7 @@
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K770" t="inlineStr">
@@ -51242,7 +51242,7 @@
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K771" t="inlineStr">
@@ -51291,7 +51291,7 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K772" t="inlineStr">
@@ -51389,7 +51389,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K261"/>
+  <dimension ref="A1:K270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11308,16 +11308,16 @@
         <v>2025</v>
       </c>
       <c r="D221" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -11700,16 +11700,16 @@
         <v>2025</v>
       </c>
       <c r="D229" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -13170,16 +13170,16 @@
         <v>2025</v>
       </c>
       <c r="D259" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -13268,16 +13268,16 @@
         <v>2025</v>
       </c>
       <c r="D261" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -13297,6 +13297,447 @@
         </is>
       </c>
       <c r="K261" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D262" t="n">
+        <v>46</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>5603</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D263" t="n">
+        <v>46</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>5583</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D264" t="n">
+        <v>46</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>5544</v>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D265" t="n">
+        <v>46</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>5536</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D266" t="n">
+        <v>46</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>5530</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D267" t="n">
+        <v>46</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>5474</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D268" t="n">
+        <v>46</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>5403</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Daniela Klug</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D269" t="n">
+        <v>46</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>5298</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D270" t="n">
+        <v>46</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>5295</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -13313,7 +13754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K775"/>
+  <dimension ref="A1:K813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45729,16 +46170,16 @@
         <v>2025</v>
       </c>
       <c r="D659" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G659" t="n">
@@ -45749,7 +46190,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -47934,16 +48375,16 @@
         <v>2025</v>
       </c>
       <c r="D704" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -47954,7 +48395,7 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
@@ -48277,16 +48718,16 @@
         <v>2025</v>
       </c>
       <c r="D711" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G711" t="n">
@@ -48297,12 +48738,12 @@
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
@@ -48424,16 +48865,16 @@
         <v>2025</v>
       </c>
       <c r="D714" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G714" t="n">
@@ -48444,12 +48885,12 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
@@ -48743,7 +49184,7 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
@@ -49453,16 +49894,16 @@
         <v>2025</v>
       </c>
       <c r="D735" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G735" t="n">
@@ -49473,7 +49914,7 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -49698,16 +50139,16 @@
         <v>2025</v>
       </c>
       <c r="D740" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -49718,12 +50159,12 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
@@ -50237,16 +50678,16 @@
         <v>2025</v>
       </c>
       <c r="D751" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G751" t="n">
@@ -50257,12 +50698,12 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
@@ -50286,16 +50727,16 @@
         <v>2025</v>
       </c>
       <c r="D752" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G752" t="n">
@@ -50306,7 +50747,7 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
@@ -50335,16 +50776,16 @@
         <v>2025</v>
       </c>
       <c r="D753" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G753" t="n">
@@ -50355,12 +50796,12 @@
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
@@ -50482,16 +50923,16 @@
         <v>2025</v>
       </c>
       <c r="D756" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G756" t="n">
@@ -50502,7 +50943,7 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -50776,16 +51217,16 @@
         <v>2025</v>
       </c>
       <c r="D762" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G762" t="n">
@@ -50796,7 +51237,7 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
@@ -50874,16 +51315,16 @@
         <v>2025</v>
       </c>
       <c r="D764" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G764" t="n">
@@ -50894,12 +51335,12 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
@@ -50923,16 +51364,16 @@
         <v>2025</v>
       </c>
       <c r="D765" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G765" t="n">
@@ -50943,7 +51384,7 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -51021,16 +51462,16 @@
         <v>2025</v>
       </c>
       <c r="D767" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G767" t="n">
@@ -51041,12 +51482,12 @@
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
@@ -51315,16 +51756,16 @@
         <v>2025</v>
       </c>
       <c r="D773" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G773" t="n">
@@ -51335,12 +51776,12 @@
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K773" t="inlineStr">
@@ -51438,10 +51879,1872 @@
       </c>
       <c r="J775" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D776" t="n">
+        <v>46</v>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G776" t="n">
+        <v>5672</v>
+      </c>
+      <c r="H776" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D777" t="n">
+        <v>46</v>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G777" t="n">
+        <v>5665</v>
+      </c>
+      <c r="H777" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D778" t="n">
+        <v>46</v>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G778" t="n">
+        <v>5650</v>
+      </c>
+      <c r="H778" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr">
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D779" t="n">
+        <v>46</v>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G779" t="n">
+        <v>5639</v>
+      </c>
+      <c r="H779" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Gabriel Lopez</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D780" t="n">
+        <v>46</v>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G780" t="n">
+        <v>5631</v>
+      </c>
+      <c r="H780" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D781" t="n">
+        <v>46</v>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G781" t="n">
+        <v>5625</v>
+      </c>
+      <c r="H781" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D782" t="n">
+        <v>46</v>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G782" t="n">
+        <v>5611</v>
+      </c>
+      <c r="H782" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D783" t="n">
+        <v>46</v>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G783" t="n">
+        <v>5591</v>
+      </c>
+      <c r="H783" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D784" t="n">
+        <v>46</v>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G784" t="n">
+        <v>5590</v>
+      </c>
+      <c r="H784" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D785" t="n">
+        <v>46</v>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G785" t="n">
+        <v>5587</v>
+      </c>
+      <c r="H785" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D786" t="n">
+        <v>46</v>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G786" t="n">
+        <v>5585</v>
+      </c>
+      <c r="H786" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D787" t="n">
+        <v>46</v>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G787" t="n">
+        <v>5579</v>
+      </c>
+      <c r="H787" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D788" t="n">
+        <v>46</v>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G788" t="n">
+        <v>5576</v>
+      </c>
+      <c r="H788" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D789" t="n">
+        <v>46</v>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G789" t="n">
+        <v>5564</v>
+      </c>
+      <c r="H789" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D790" t="n">
+        <v>46</v>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G790" t="n">
+        <v>5559</v>
+      </c>
+      <c r="H790" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D791" t="n">
+        <v>46</v>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G791" t="n">
+        <v>5547</v>
+      </c>
+      <c r="H791" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D792" t="n">
+        <v>46</v>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G792" t="n">
+        <v>5543</v>
+      </c>
+      <c r="H792" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D793" t="n">
+        <v>46</v>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G793" t="n">
+        <v>5542</v>
+      </c>
+      <c r="H793" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D794" t="n">
+        <v>46</v>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G794" t="n">
+        <v>5540</v>
+      </c>
+      <c r="H794" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D795" t="n">
+        <v>46</v>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G795" t="n">
+        <v>5533</v>
+      </c>
+      <c r="H795" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D796" t="n">
+        <v>46</v>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G796" t="n">
+        <v>5532</v>
+      </c>
+      <c r="H796" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D797" t="n">
+        <v>46</v>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G797" t="n">
+        <v>5515</v>
+      </c>
+      <c r="H797" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D798" t="n">
+        <v>46</v>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G798" t="n">
+        <v>5448</v>
+      </c>
+      <c r="H798" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D799" t="n">
+        <v>46</v>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G799" t="n">
+        <v>5440</v>
+      </c>
+      <c r="H799" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D800" t="n">
+        <v>46</v>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G800" t="n">
+        <v>5435</v>
+      </c>
+      <c r="H800" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D801" t="n">
+        <v>46</v>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G801" t="n">
+        <v>5426</v>
+      </c>
+      <c r="H801" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D802" t="n">
+        <v>46</v>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G802" t="n">
+        <v>5392</v>
+      </c>
+      <c r="H802" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D803" t="n">
+        <v>46</v>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G803" t="n">
+        <v>5387</v>
+      </c>
+      <c r="H803" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D804" t="n">
+        <v>46</v>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G804" t="n">
+        <v>5383</v>
+      </c>
+      <c r="H804" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Gabriel Lopez</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D805" t="n">
+        <v>46</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G805" t="n">
+        <v>5376</v>
+      </c>
+      <c r="H805" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D806" t="n">
+        <v>46</v>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G806" t="n">
+        <v>5364</v>
+      </c>
+      <c r="H806" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D807" t="n">
+        <v>46</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G807" t="n">
+        <v>5361</v>
+      </c>
+      <c r="H807" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Alana Neris</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D808" t="n">
+        <v>46</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G808" t="n">
+        <v>5328</v>
+      </c>
+      <c r="H808" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D809" t="n">
+        <v>46</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G809" t="n">
+        <v>5304</v>
+      </c>
+      <c r="H809" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D810" t="n">
+        <v>46</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G810" t="n">
+        <v>5287</v>
+      </c>
+      <c r="H810" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D811" t="n">
+        <v>46</v>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G811" t="n">
+        <v>5259</v>
+      </c>
+      <c r="H811" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D812" t="n">
+        <v>46</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G812" t="n">
+        <v>5172</v>
+      </c>
+      <c r="H812" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D813" t="n">
+        <v>46</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>21/11/2025</t>
+        </is>
+      </c>
+      <c r="G813" t="n">
+        <v>5157</v>
+      </c>
+      <c r="H813" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -48074,7 +48074,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -48760,7 +48760,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -48809,7 +48809,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -49544,7 +49544,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C728" t="n">
@@ -49564,10 +49564,10 @@
         </is>
       </c>
       <c r="G728" t="n">
-        <v>4865</v>
+        <v>4792</v>
       </c>
       <c r="H728" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I728" t="inlineStr">
         <is>
@@ -49593,34 +49593,34 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C729" t="n">
         <v>2025</v>
       </c>
       <c r="D729" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G729" t="n">
-        <v>4849</v>
+        <v>4677</v>
       </c>
       <c r="H729" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
@@ -49642,7 +49642,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -49662,10 +49662,10 @@
         </is>
       </c>
       <c r="G730" t="n">
-        <v>4848</v>
+        <v>4679</v>
       </c>
       <c r="H730" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I730" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -49740,7 +49740,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -49789,7 +49789,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -49838,7 +49838,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -49887,7 +49887,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -49936,34 +49936,34 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C736" t="n">
         <v>2025</v>
       </c>
       <c r="D736" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>4792</v>
+        <v>4718</v>
       </c>
       <c r="H736" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -49985,34 +49985,34 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C737" t="n">
         <v>2025</v>
       </c>
       <c r="D737" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>4745</v>
+        <v>4605</v>
       </c>
       <c r="H737" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
@@ -50034,34 +50034,34 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C738" t="n">
         <v>2025</v>
       </c>
       <c r="D738" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>4718</v>
+        <v>4656</v>
       </c>
       <c r="H738" s="2" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
@@ -50083,34 +50083,34 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C739" t="n">
         <v>2025</v>
       </c>
       <c r="D739" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G739" t="n">
-        <v>4679</v>
+        <v>4445</v>
       </c>
       <c r="H739" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
@@ -50132,34 +50132,34 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C740" t="n">
         <v>2025</v>
       </c>
       <c r="D740" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>4677</v>
+        <v>4865</v>
       </c>
       <c r="H740" s="2" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
@@ -50181,7 +50181,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -50201,7 +50201,7 @@
         </is>
       </c>
       <c r="G741" t="n">
-        <v>4656</v>
+        <v>4849</v>
       </c>
       <c r="H741" s="2" t="n">
         <v>45962</v>
@@ -50250,10 +50250,10 @@
         </is>
       </c>
       <c r="G742" t="n">
-        <v>4636</v>
+        <v>4848</v>
       </c>
       <c r="H742" s="2" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I742" t="inlineStr">
         <is>
@@ -50279,34 +50279,34 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C743" t="n">
         <v>2025</v>
       </c>
       <c r="D743" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="G743" t="n">
-        <v>4605</v>
+        <v>4745</v>
       </c>
       <c r="H743" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
@@ -50328,34 +50328,34 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C744" t="n">
         <v>2025</v>
       </c>
       <c r="D744" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="G744" t="n">
-        <v>4578</v>
+        <v>4636</v>
       </c>
       <c r="H744" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
@@ -50377,7 +50377,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -50397,7 +50397,7 @@
         </is>
       </c>
       <c r="G745" t="n">
-        <v>4527</v>
+        <v>4578</v>
       </c>
       <c r="H745" s="2" t="n">
         <v>45931</v>
@@ -50524,7 +50524,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -50544,7 +50544,7 @@
         </is>
       </c>
       <c r="G748" t="n">
-        <v>4445</v>
+        <v>4527</v>
       </c>
       <c r="H748" s="2" t="n">
         <v>45931</v>
@@ -50573,39 +50573,39 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C749" t="n">
         <v>2025</v>
       </c>
       <c r="D749" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G749" t="n">
-        <v>5274</v>
+        <v>5200</v>
       </c>
       <c r="H749" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -50622,34 +50622,34 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C750" t="n">
         <v>2025</v>
       </c>
       <c r="D750" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G750" t="n">
-        <v>5273</v>
+        <v>5191</v>
       </c>
       <c r="H750" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
@@ -50671,34 +50671,34 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C751" t="n">
         <v>2025</v>
       </c>
       <c r="D751" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G751" t="n">
-        <v>5205</v>
+        <v>5186</v>
       </c>
       <c r="H751" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
@@ -50720,39 +50720,39 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C752" t="n">
         <v>2025</v>
       </c>
       <c r="D752" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G752" t="n">
-        <v>5200</v>
+        <v>5135</v>
       </c>
       <c r="H752" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
@@ -50769,34 +50769,34 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C753" t="n">
         <v>2025</v>
       </c>
       <c r="D753" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G753" t="n">
-        <v>5191</v>
+        <v>5130</v>
       </c>
       <c r="H753" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -50818,7 +50818,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -50838,7 +50838,7 @@
         </is>
       </c>
       <c r="G754" t="n">
-        <v>5188</v>
+        <v>5127</v>
       </c>
       <c r="H754" s="2" t="n">
         <v>45962</v>
@@ -50867,7 +50867,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -50887,7 +50887,7 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>5186</v>
+        <v>5092</v>
       </c>
       <c r="H755" s="2" t="n">
         <v>45962</v>
@@ -50916,7 +50916,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -50936,7 +50936,7 @@
         </is>
       </c>
       <c r="G756" t="n">
-        <v>5185</v>
+        <v>5055</v>
       </c>
       <c r="H756" s="2" t="n">
         <v>45962</v>
@@ -50965,34 +50965,34 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C757" t="n">
         <v>2025</v>
       </c>
       <c r="D757" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G757" t="n">
-        <v>5164</v>
+        <v>5016</v>
       </c>
       <c r="H757" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
@@ -51014,39 +51014,39 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C758" t="n">
         <v>2025</v>
       </c>
       <c r="D758" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G758" t="n">
-        <v>5135</v>
+        <v>4968</v>
       </c>
       <c r="H758" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
@@ -51063,7 +51063,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -51083,7 +51083,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>5130</v>
+        <v>4966</v>
       </c>
       <c r="H759" s="2" t="n">
         <v>45962</v>
@@ -51112,34 +51112,34 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C760" t="n">
         <v>2025</v>
       </c>
       <c r="D760" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>5127</v>
+        <v>4944</v>
       </c>
       <c r="H760" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
@@ -51161,7 +51161,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -51181,7 +51181,7 @@
         </is>
       </c>
       <c r="G761" t="n">
-        <v>5092</v>
+        <v>4905</v>
       </c>
       <c r="H761" s="2" t="n">
         <v>45962</v>
@@ -51210,39 +51210,39 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C762" t="n">
         <v>2025</v>
       </c>
       <c r="D762" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G762" t="n">
-        <v>5055</v>
+        <v>4896</v>
       </c>
       <c r="H762" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
@@ -51259,7 +51259,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -51279,7 +51279,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>5026</v>
+        <v>4863</v>
       </c>
       <c r="H763" s="2" t="n">
         <v>45962</v>
@@ -51308,7 +51308,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -51328,7 +51328,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>5016</v>
+        <v>4736</v>
       </c>
       <c r="H764" s="2" t="n">
         <v>45962</v>
@@ -51357,39 +51357,39 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C765" t="n">
         <v>2025</v>
       </c>
       <c r="D765" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G765" t="n">
-        <v>4968</v>
+        <v>5274</v>
       </c>
       <c r="H765" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
@@ -51406,7 +51406,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -51426,7 +51426,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>4966</v>
+        <v>4918</v>
       </c>
       <c r="H766" s="2" t="n">
         <v>45962</v>
@@ -51455,34 +51455,34 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C767" t="n">
         <v>2025</v>
       </c>
       <c r="D767" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G767" t="n">
-        <v>4944</v>
+        <v>4845</v>
       </c>
       <c r="H767" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
@@ -51504,7 +51504,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="G768" t="n">
-        <v>4918</v>
+        <v>5164</v>
       </c>
       <c r="H768" s="2" t="n">
         <v>45962</v>
@@ -51553,7 +51553,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -51573,7 +51573,7 @@
         </is>
       </c>
       <c r="G769" t="n">
-        <v>4905</v>
+        <v>5273</v>
       </c>
       <c r="H769" s="2" t="n">
         <v>45962</v>
@@ -51602,7 +51602,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -51622,7 +51622,7 @@
         </is>
       </c>
       <c r="G770" t="n">
-        <v>4896</v>
+        <v>5188</v>
       </c>
       <c r="H770" s="2" t="n">
         <v>45962</v>
@@ -51651,7 +51651,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -51671,7 +51671,7 @@
         </is>
       </c>
       <c r="G771" t="n">
-        <v>4863</v>
+        <v>5026</v>
       </c>
       <c r="H771" s="2" t="n">
         <v>45962</v>
@@ -51700,7 +51700,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -51720,10 +51720,10 @@
         </is>
       </c>
       <c r="G772" t="n">
-        <v>4845</v>
+        <v>4595</v>
       </c>
       <c r="H772" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I772" t="inlineStr">
         <is>
@@ -51749,34 +51749,34 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C773" t="n">
         <v>2025</v>
       </c>
       <c r="D773" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="G773" t="n">
-        <v>4736</v>
+        <v>4305</v>
       </c>
       <c r="H773" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
@@ -51798,39 +51798,39 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C774" t="n">
         <v>2025</v>
       </c>
       <c r="D774" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G774" t="n">
-        <v>4595</v>
+        <v>5185</v>
       </c>
       <c r="H774" s="2" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -51847,34 +51847,34 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C775" t="n">
         <v>2025</v>
       </c>
       <c r="D775" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="G775" t="n">
-        <v>4305</v>
+        <v>5205</v>
       </c>
       <c r="H775" s="2" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -51945,7 +51945,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -51965,7 +51965,7 @@
         </is>
       </c>
       <c r="G777" t="n">
-        <v>5665</v>
+        <v>5625</v>
       </c>
       <c r="H777" s="2" t="n">
         <v>45962</v>
@@ -51994,7 +51994,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -52014,7 +52014,7 @@
         </is>
       </c>
       <c r="G778" t="n">
-        <v>5650</v>
+        <v>5611</v>
       </c>
       <c r="H778" s="2" t="n">
         <v>45962</v>
@@ -52026,7 +52026,7 @@
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
@@ -52043,7 +52043,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -52063,7 +52063,7 @@
         </is>
       </c>
       <c r="G779" t="n">
-        <v>5639</v>
+        <v>5587</v>
       </c>
       <c r="H779" s="2" t="n">
         <v>45962</v>
@@ -52092,7 +52092,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Gabriel Lopez</t>
+          <t>Alana Neris</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -52112,7 +52112,7 @@
         </is>
       </c>
       <c r="G780" t="n">
-        <v>5631</v>
+        <v>5426</v>
       </c>
       <c r="H780" s="2" t="n">
         <v>45962</v>
@@ -52161,7 +52161,7 @@
         </is>
       </c>
       <c r="G781" t="n">
-        <v>5625</v>
+        <v>5361</v>
       </c>
       <c r="H781" s="2" t="n">
         <v>45962</v>
@@ -52210,7 +52210,7 @@
         </is>
       </c>
       <c r="G782" t="n">
-        <v>5611</v>
+        <v>5328</v>
       </c>
       <c r="H782" s="2" t="n">
         <v>45962</v>
@@ -52239,7 +52239,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -52259,7 +52259,7 @@
         </is>
       </c>
       <c r="G783" t="n">
-        <v>5591</v>
+        <v>5392</v>
       </c>
       <c r="H783" s="2" t="n">
         <v>45962</v>
@@ -52271,7 +52271,7 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -52288,7 +52288,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Emerson Pellis</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -52308,7 +52308,7 @@
         </is>
       </c>
       <c r="G784" t="n">
-        <v>5590</v>
+        <v>5387</v>
       </c>
       <c r="H784" s="2" t="n">
         <v>45962</v>
@@ -52337,7 +52337,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -52357,7 +52357,7 @@
         </is>
       </c>
       <c r="G785" t="n">
-        <v>5587</v>
+        <v>5591</v>
       </c>
       <c r="H785" s="2" t="n">
         <v>45962</v>
@@ -52369,7 +52369,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
@@ -52386,7 +52386,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -52435,7 +52435,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -52455,7 +52455,7 @@
         </is>
       </c>
       <c r="G787" t="n">
-        <v>5579</v>
+        <v>5542</v>
       </c>
       <c r="H787" s="2" t="n">
         <v>45962</v>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="G788" t="n">
-        <v>5576</v>
+        <v>5540</v>
       </c>
       <c r="H788" s="2" t="n">
         <v>45962</v>
@@ -52533,7 +52533,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -52553,7 +52553,7 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>5564</v>
+        <v>5532</v>
       </c>
       <c r="H789" s="2" t="n">
         <v>45962</v>
@@ -52582,7 +52582,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -52602,7 +52602,7 @@
         </is>
       </c>
       <c r="G790" t="n">
-        <v>5559</v>
+        <v>5440</v>
       </c>
       <c r="H790" s="2" t="n">
         <v>45962</v>
@@ -52631,7 +52631,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -52651,7 +52651,7 @@
         </is>
       </c>
       <c r="G791" t="n">
-        <v>5547</v>
+        <v>5435</v>
       </c>
       <c r="H791" s="2" t="n">
         <v>45962</v>
@@ -52663,7 +52663,7 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
@@ -52680,7 +52680,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -52700,7 +52700,7 @@
         </is>
       </c>
       <c r="G792" t="n">
-        <v>5543</v>
+        <v>5172</v>
       </c>
       <c r="H792" s="2" t="n">
         <v>45962</v>
@@ -52712,7 +52712,7 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K792" t="inlineStr">
@@ -52729,7 +52729,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Erick da Silva</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -52749,7 +52749,7 @@
         </is>
       </c>
       <c r="G793" t="n">
-        <v>5542</v>
+        <v>5157</v>
       </c>
       <c r="H793" s="2" t="n">
         <v>45962</v>
@@ -52778,7 +52778,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -52798,7 +52798,7 @@
         </is>
       </c>
       <c r="G794" t="n">
-        <v>5540</v>
+        <v>5533</v>
       </c>
       <c r="H794" s="2" t="n">
         <v>45962</v>
@@ -52847,7 +52847,7 @@
         </is>
       </c>
       <c r="G795" t="n">
-        <v>5533</v>
+        <v>5383</v>
       </c>
       <c r="H795" s="2" t="n">
         <v>45962</v>
@@ -52876,7 +52876,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -52896,7 +52896,7 @@
         </is>
       </c>
       <c r="G796" t="n">
-        <v>5532</v>
+        <v>5364</v>
       </c>
       <c r="H796" s="2" t="n">
         <v>45962</v>
@@ -52925,7 +52925,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -52945,7 +52945,7 @@
         </is>
       </c>
       <c r="G797" t="n">
-        <v>5515</v>
+        <v>5287</v>
       </c>
       <c r="H797" s="2" t="n">
         <v>45962</v>
@@ -52974,7 +52974,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Gabriel Lopez</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -52994,7 +52994,7 @@
         </is>
       </c>
       <c r="G798" t="n">
-        <v>5448</v>
+        <v>5631</v>
       </c>
       <c r="H798" s="2" t="n">
         <v>45962</v>
@@ -53006,7 +53006,7 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
@@ -53023,7 +53023,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Gabriel Lopez</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -53043,7 +53043,7 @@
         </is>
       </c>
       <c r="G799" t="n">
-        <v>5440</v>
+        <v>5376</v>
       </c>
       <c r="H799" s="2" t="n">
         <v>45962</v>
@@ -53055,7 +53055,7 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K799" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -53092,7 +53092,7 @@
         </is>
       </c>
       <c r="G800" t="n">
-        <v>5435</v>
+        <v>5650</v>
       </c>
       <c r="H800" s="2" t="n">
         <v>45962</v>
@@ -53104,7 +53104,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -53141,7 +53141,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>5426</v>
+        <v>5515</v>
       </c>
       <c r="H801" s="2" t="n">
         <v>45962</v>
@@ -53170,7 +53170,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -53190,7 +53190,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>5392</v>
+        <v>5665</v>
       </c>
       <c r="H802" s="2" t="n">
         <v>45962</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -53239,7 +53239,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>5387</v>
+        <v>5579</v>
       </c>
       <c r="H803" s="2" t="n">
         <v>45962</v>
@@ -53251,7 +53251,7 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K803" t="inlineStr">
@@ -53268,7 +53268,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -53288,7 +53288,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>5383</v>
+        <v>5564</v>
       </c>
       <c r="H804" s="2" t="n">
         <v>45962</v>
@@ -53317,7 +53317,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Gabriel Lopez</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -53337,7 +53337,7 @@
         </is>
       </c>
       <c r="G805" t="n">
-        <v>5376</v>
+        <v>5547</v>
       </c>
       <c r="H805" s="2" t="n">
         <v>45962</v>
@@ -53349,7 +53349,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K805" t="inlineStr">
@@ -53366,7 +53366,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -53386,7 +53386,7 @@
         </is>
       </c>
       <c r="G806" t="n">
-        <v>5364</v>
+        <v>5543</v>
       </c>
       <c r="H806" s="2" t="n">
         <v>45962</v>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
@@ -53415,7 +53415,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -53435,7 +53435,7 @@
         </is>
       </c>
       <c r="G807" t="n">
-        <v>5361</v>
+        <v>5448</v>
       </c>
       <c r="H807" s="2" t="n">
         <v>45962</v>
@@ -53447,7 +53447,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K807" t="inlineStr">
@@ -53464,7 +53464,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Alana Neris</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -53484,7 +53484,7 @@
         </is>
       </c>
       <c r="G808" t="n">
-        <v>5328</v>
+        <v>5259</v>
       </c>
       <c r="H808" s="2" t="n">
         <v>45962</v>
@@ -53496,7 +53496,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K808" t="inlineStr">
@@ -53562,7 +53562,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -53582,7 +53582,7 @@
         </is>
       </c>
       <c r="G810" t="n">
-        <v>5287</v>
+        <v>5639</v>
       </c>
       <c r="H810" s="2" t="n">
         <v>45962</v>
@@ -53611,7 +53611,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -53631,7 +53631,7 @@
         </is>
       </c>
       <c r="G811" t="n">
-        <v>5259</v>
+        <v>5590</v>
       </c>
       <c r="H811" s="2" t="n">
         <v>45962</v>
@@ -53660,7 +53660,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -53680,7 +53680,7 @@
         </is>
       </c>
       <c r="G812" t="n">
-        <v>5172</v>
+        <v>5576</v>
       </c>
       <c r="H812" s="2" t="n">
         <v>45962</v>
@@ -53709,7 +53709,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -53729,7 +53729,7 @@
         </is>
       </c>
       <c r="G813" t="n">
-        <v>5157</v>
+        <v>5559</v>
       </c>
       <c r="H813" s="2" t="n">
         <v>45962</v>
@@ -53741,7 +53741,7 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K270"/>
+  <dimension ref="A1:K272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11700,16 +11700,16 @@
         <v>2025</v>
       </c>
       <c r="D229" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13170,16 +13170,16 @@
         <v>2025</v>
       </c>
       <c r="D259" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -13268,16 +13268,16 @@
         <v>2025</v>
       </c>
       <c r="D261" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -13317,16 +13317,16 @@
         <v>2025</v>
       </c>
       <c r="D262" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -13738,6 +13738,104 @@
         </is>
       </c>
       <c r="K270" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Ivonei Feiler</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D271" t="n">
+        <v>47</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>6061</v>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D272" t="n">
+        <v>47</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>4285</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -13754,7 +13852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K813"/>
+  <dimension ref="A1:K858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46170,16 +46268,16 @@
         <v>2025</v>
       </c>
       <c r="D659" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G659" t="n">
@@ -46190,7 +46288,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -48375,16 +48473,16 @@
         <v>2025</v>
       </c>
       <c r="D704" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -48395,7 +48493,7 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
@@ -49887,23 +49985,23 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Erick da Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C735" t="n">
         <v>2025</v>
       </c>
       <c r="D735" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G735" t="n">
@@ -49914,7 +50012,7 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -50573,23 +50671,23 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Erick da Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C749" t="n">
         <v>2025</v>
       </c>
       <c r="D749" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G749" t="n">
@@ -50600,7 +50698,7 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
@@ -50916,23 +51014,23 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Erick da Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C756" t="n">
         <v>2025</v>
       </c>
       <c r="D756" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G756" t="n">
@@ -50943,7 +51041,7 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -51014,23 +51112,23 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Erick da Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C758" t="n">
         <v>2025</v>
       </c>
       <c r="D758" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G758" t="n">
@@ -51041,7 +51139,7 @@
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
@@ -51805,16 +51903,16 @@
         <v>2025</v>
       </c>
       <c r="D774" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G774" t="n">
@@ -51825,7 +51923,7 @@
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -52295,16 +52393,16 @@
         <v>2025</v>
       </c>
       <c r="D784" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G784" t="n">
@@ -52315,7 +52413,7 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -52337,23 +52435,23 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Erick da Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C785" t="n">
         <v>2025</v>
       </c>
       <c r="D785" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G785" t="n">
@@ -52364,7 +52462,7 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
@@ -52614,7 +52712,7 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
@@ -53079,16 +53177,16 @@
         <v>2025</v>
       </c>
       <c r="D800" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -53099,7 +53197,7 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
@@ -53324,16 +53422,16 @@
         <v>2025</v>
       </c>
       <c r="D805" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G805" t="n">
@@ -53344,7 +53442,7 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
@@ -53373,16 +53471,16 @@
         <v>2025</v>
       </c>
       <c r="D806" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G806" t="n">
@@ -53393,7 +53491,7 @@
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
@@ -53422,16 +53520,16 @@
         <v>2025</v>
       </c>
       <c r="D807" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G807" t="n">
@@ -53442,7 +53540,7 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
@@ -53471,16 +53569,16 @@
         <v>2025</v>
       </c>
       <c r="D808" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G808" t="n">
@@ -53491,7 +53589,7 @@
       </c>
       <c r="I808" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J808" t="inlineStr">
@@ -53520,16 +53618,16 @@
         <v>2025</v>
       </c>
       <c r="D809" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G809" t="n">
@@ -53540,7 +53638,7 @@
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
@@ -53618,16 +53716,16 @@
         <v>2025</v>
       </c>
       <c r="D811" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G811" t="n">
@@ -53638,7 +53736,7 @@
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J811" t="inlineStr">
@@ -53716,16 +53814,16 @@
         <v>2025</v>
       </c>
       <c r="D813" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="G813" t="n">
@@ -53736,7 +53834,7 @@
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J813" t="inlineStr">
@@ -53745,6 +53843,2211 @@
         </is>
       </c>
       <c r="K813" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D814" t="n">
+        <v>47</v>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G814" t="n">
+        <v>4975</v>
+      </c>
+      <c r="H814" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D815" t="n">
+        <v>47</v>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G815" t="n">
+        <v>5862</v>
+      </c>
+      <c r="H815" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D816" t="n">
+        <v>47</v>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G816" t="n">
+        <v>5911</v>
+      </c>
+      <c r="H816" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D817" t="n">
+        <v>47</v>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G817" t="n">
+        <v>5920</v>
+      </c>
+      <c r="H817" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D818" t="n">
+        <v>47</v>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G818" t="n">
+        <v>5996</v>
+      </c>
+      <c r="H818" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D819" t="n">
+        <v>47</v>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G819" t="n">
+        <v>6030</v>
+      </c>
+      <c r="H819" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D820" t="n">
+        <v>47</v>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G820" t="n">
+        <v>6047</v>
+      </c>
+      <c r="H820" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D821" t="n">
+        <v>47</v>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G821" t="n">
+        <v>6097</v>
+      </c>
+      <c r="H821" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D822" t="n">
+        <v>47</v>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G822" t="n">
+        <v>6115</v>
+      </c>
+      <c r="H822" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D823" t="n">
+        <v>47</v>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G823" t="n">
+        <v>6171</v>
+      </c>
+      <c r="H823" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D824" t="n">
+        <v>47</v>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G824" t="n">
+        <v>5581</v>
+      </c>
+      <c r="H824" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D825" t="n">
+        <v>47</v>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G825" t="n">
+        <v>6016</v>
+      </c>
+      <c r="H825" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D826" t="n">
+        <v>47</v>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G826" t="n">
+        <v>6083</v>
+      </c>
+      <c r="H826" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D827" t="n">
+        <v>47</v>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G827" t="n">
+        <v>6084</v>
+      </c>
+      <c r="H827" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D828" t="n">
+        <v>47</v>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G828" t="n">
+        <v>6090</v>
+      </c>
+      <c r="H828" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D829" t="n">
+        <v>47</v>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G829" t="n">
+        <v>6091</v>
+      </c>
+      <c r="H829" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D830" t="n">
+        <v>47</v>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G830" t="n">
+        <v>6094</v>
+      </c>
+      <c r="H830" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D831" t="n">
+        <v>47</v>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G831" t="n">
+        <v>6098</v>
+      </c>
+      <c r="H831" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D832" t="n">
+        <v>47</v>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G832" t="n">
+        <v>6099</v>
+      </c>
+      <c r="H832" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D833" t="n">
+        <v>47</v>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G833" t="n">
+        <v>6104</v>
+      </c>
+      <c r="H833" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D834" t="n">
+        <v>47</v>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G834" t="n">
+        <v>6105</v>
+      </c>
+      <c r="H834" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D835" t="n">
+        <v>47</v>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G835" t="n">
+        <v>6106</v>
+      </c>
+      <c r="H835" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D836" t="n">
+        <v>47</v>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G836" t="n">
+        <v>6107</v>
+      </c>
+      <c r="H836" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D837" t="n">
+        <v>47</v>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G837" t="n">
+        <v>6113</v>
+      </c>
+      <c r="H837" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D838" t="n">
+        <v>47</v>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G838" t="n">
+        <v>6116</v>
+      </c>
+      <c r="H838" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D839" t="n">
+        <v>47</v>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G839" t="n">
+        <v>6118</v>
+      </c>
+      <c r="H839" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D840" t="n">
+        <v>47</v>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>6120</v>
+      </c>
+      <c r="H840" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D841" t="n">
+        <v>47</v>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G841" t="n">
+        <v>6122</v>
+      </c>
+      <c r="H841" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D842" t="n">
+        <v>47</v>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G842" t="n">
+        <v>6135</v>
+      </c>
+      <c r="H842" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D843" t="n">
+        <v>47</v>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G843" t="n">
+        <v>6142</v>
+      </c>
+      <c r="H843" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D844" t="n">
+        <v>47</v>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G844" t="n">
+        <v>6215</v>
+      </c>
+      <c r="H844" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D845" t="n">
+        <v>47</v>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G845" t="n">
+        <v>5713</v>
+      </c>
+      <c r="H845" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D846" t="n">
+        <v>47</v>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G846" t="n">
+        <v>6056</v>
+      </c>
+      <c r="H846" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D847" t="n">
+        <v>47</v>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G847" t="n">
+        <v>6062</v>
+      </c>
+      <c r="H847" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D848" t="n">
+        <v>47</v>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G848" t="n">
+        <v>5715</v>
+      </c>
+      <c r="H848" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D849" t="n">
+        <v>47</v>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G849" t="n">
+        <v>5823</v>
+      </c>
+      <c r="H849" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D850" t="n">
+        <v>47</v>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G850" t="n">
+        <v>5916</v>
+      </c>
+      <c r="H850" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D851" t="n">
+        <v>47</v>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G851" t="n">
+        <v>6015</v>
+      </c>
+      <c r="H851" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D852" t="n">
+        <v>47</v>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G852" t="n">
+        <v>6050</v>
+      </c>
+      <c r="H852" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D853" t="n">
+        <v>47</v>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G853" t="n">
+        <v>6073</v>
+      </c>
+      <c r="H853" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D854" t="n">
+        <v>47</v>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G854" t="n">
+        <v>6080</v>
+      </c>
+      <c r="H854" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D855" t="n">
+        <v>47</v>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G855" t="n">
+        <v>5683</v>
+      </c>
+      <c r="H855" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D856" t="n">
+        <v>47</v>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G856" t="n">
+        <v>6010</v>
+      </c>
+      <c r="H856" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D857" t="n">
+        <v>47</v>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G857" t="n">
+        <v>5863</v>
+      </c>
+      <c r="H857" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Patrick Doyle</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D858" t="n">
+        <v>47</v>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="G858" t="n">
+        <v>5841</v>
+      </c>
+      <c r="H858" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K272"/>
+  <dimension ref="A1:K275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -13268,16 +13268,16 @@
         <v>2025</v>
       </c>
       <c r="D261" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -13758,16 +13758,16 @@
         <v>2025</v>
       </c>
       <c r="D271" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -13832,10 +13832,157 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D273" t="n">
+        <v>48</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>6403</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D274" t="n">
+        <v>48</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>6554</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D275" t="n">
+        <v>48</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>6670</v>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -13852,7 +13999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K858"/>
+  <dimension ref="A1:K885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46293,7 +46440,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
@@ -48498,7 +48645,7 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
@@ -50017,7 +50164,7 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
@@ -50678,16 +50825,16 @@
         <v>2025</v>
       </c>
       <c r="D749" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G749" t="n">
@@ -50698,7 +50845,7 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
@@ -51021,16 +51168,16 @@
         <v>2025</v>
       </c>
       <c r="D756" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G756" t="n">
@@ -51041,7 +51188,7 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -51144,7 +51291,7 @@
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
@@ -51903,16 +52050,16 @@
         <v>2025</v>
       </c>
       <c r="D774" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G774" t="n">
@@ -51923,7 +52070,7 @@
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -52393,16 +52540,16 @@
         <v>2025</v>
       </c>
       <c r="D784" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G784" t="n">
@@ -52413,7 +52560,7 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -52467,7 +52614,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
@@ -53177,16 +53324,16 @@
         <v>2025</v>
       </c>
       <c r="D800" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -53197,7 +53344,7 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
@@ -53447,7 +53594,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K805" t="inlineStr">
@@ -53471,16 +53618,16 @@
         <v>2025</v>
       </c>
       <c r="D806" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G806" t="n">
@@ -53491,7 +53638,7 @@
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
@@ -53520,16 +53667,16 @@
         <v>2025</v>
       </c>
       <c r="D807" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G807" t="n">
@@ -53540,7 +53687,7 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
@@ -53569,16 +53716,16 @@
         <v>2025</v>
       </c>
       <c r="D808" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G808" t="n">
@@ -53589,7 +53736,7 @@
       </c>
       <c r="I808" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J808" t="inlineStr">
@@ -53618,16 +53765,16 @@
         <v>2025</v>
       </c>
       <c r="D809" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G809" t="n">
@@ -53638,7 +53785,7 @@
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
@@ -53716,16 +53863,16 @@
         <v>2025</v>
       </c>
       <c r="D811" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G811" t="n">
@@ -53736,7 +53883,7 @@
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J811" t="inlineStr">
@@ -53814,16 +53961,16 @@
         <v>2025</v>
       </c>
       <c r="D813" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G813" t="n">
@@ -53834,7 +53981,7 @@
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J813" t="inlineStr">
@@ -53888,7 +54035,7 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K814" t="inlineStr">
@@ -53937,7 +54084,7 @@
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K815" t="inlineStr">
@@ -53986,7 +54133,7 @@
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K816" t="inlineStr">
@@ -54035,7 +54182,7 @@
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K817" t="inlineStr">
@@ -54059,16 +54206,16 @@
         <v>2025</v>
       </c>
       <c r="D818" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G818" t="n">
@@ -54079,7 +54226,7 @@
       </c>
       <c r="I818" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J818" t="inlineStr">
@@ -54133,7 +54280,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K819" t="inlineStr">
@@ -54182,7 +54329,7 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K820" t="inlineStr">
@@ -54206,16 +54353,16 @@
         <v>2025</v>
       </c>
       <c r="D821" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G821" t="n">
@@ -54226,7 +54373,7 @@
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
@@ -54280,7 +54427,7 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K822" t="inlineStr">
@@ -54329,7 +54476,7 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K823" t="inlineStr">
@@ -54353,16 +54500,16 @@
         <v>2025</v>
       </c>
       <c r="D824" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G824" t="n">
@@ -54373,7 +54520,7 @@
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
@@ -54402,16 +54549,16 @@
         <v>2025</v>
       </c>
       <c r="D825" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G825" t="n">
@@ -54422,7 +54569,7 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
@@ -54476,7 +54623,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K826" t="inlineStr">
@@ -54525,7 +54672,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K827" t="inlineStr">
@@ -54574,7 +54721,7 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K828" t="inlineStr">
@@ -54623,7 +54770,7 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K829" t="inlineStr">
@@ -54672,7 +54819,7 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K830" t="inlineStr">
@@ -54721,7 +54868,7 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K831" t="inlineStr">
@@ -54770,7 +54917,7 @@
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K832" t="inlineStr">
@@ -54819,7 +54966,7 @@
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K833" t="inlineStr">
@@ -54868,7 +55015,7 @@
       </c>
       <c r="J834" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K834" t="inlineStr">
@@ -54917,7 +55064,7 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K835" t="inlineStr">
@@ -54966,7 +55113,7 @@
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K836" t="inlineStr">
@@ -55015,7 +55162,7 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K837" t="inlineStr">
@@ -55064,7 +55211,7 @@
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K838" t="inlineStr">
@@ -55113,7 +55260,7 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K839" t="inlineStr">
@@ -55162,7 +55309,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K840" t="inlineStr">
@@ -55211,7 +55358,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K841" t="inlineStr">
@@ -55260,7 +55407,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K842" t="inlineStr">
@@ -55309,7 +55456,7 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K843" t="inlineStr">
@@ -55358,7 +55505,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K844" t="inlineStr">
@@ -55407,7 +55554,7 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K845" t="inlineStr">
@@ -55456,7 +55603,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K846" t="inlineStr">
@@ -55505,7 +55652,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K847" t="inlineStr">
@@ -55554,7 +55701,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K848" t="inlineStr">
@@ -55603,7 +55750,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K849" t="inlineStr">
@@ -55652,7 +55799,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K850" t="inlineStr">
@@ -55676,16 +55823,16 @@
         <v>2025</v>
       </c>
       <c r="D851" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G851" t="n">
@@ -55696,7 +55843,7 @@
       </c>
       <c r="I851" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J851" t="inlineStr">
@@ -55750,7 +55897,7 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K852" t="inlineStr">
@@ -55799,7 +55946,7 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K853" t="inlineStr">
@@ -55848,7 +55995,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K854" t="inlineStr">
@@ -55897,7 +56044,7 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K855" t="inlineStr">
@@ -55946,7 +56093,7 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K856" t="inlineStr">
@@ -55970,16 +56117,16 @@
         <v>2025</v>
       </c>
       <c r="D857" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G857" t="n">
@@ -55990,7 +56137,7 @@
       </c>
       <c r="I857" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="J857" t="inlineStr">
@@ -56044,10 +56191,1333 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D859" t="n">
+        <v>48</v>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G859" t="n">
+        <v>5876</v>
+      </c>
+      <c r="H859" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr">
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D860" t="n">
+        <v>48</v>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G860" t="n">
+        <v>6165</v>
+      </c>
+      <c r="H860" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D861" t="n">
+        <v>48</v>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G861" t="n">
+        <v>6183</v>
+      </c>
+      <c r="H861" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D862" t="n">
+        <v>48</v>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G862" t="n">
+        <v>6250</v>
+      </c>
+      <c r="H862" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D863" t="n">
+        <v>48</v>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G863" t="n">
+        <v>6260</v>
+      </c>
+      <c r="H863" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D864" t="n">
+        <v>48</v>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G864" t="n">
+        <v>6267</v>
+      </c>
+      <c r="H864" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D865" t="n">
+        <v>48</v>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G865" t="n">
+        <v>6281</v>
+      </c>
+      <c r="H865" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D866" t="n">
+        <v>48</v>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G866" t="n">
+        <v>6291</v>
+      </c>
+      <c r="H866" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D867" t="n">
+        <v>48</v>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G867" t="n">
+        <v>6364</v>
+      </c>
+      <c r="H867" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D868" t="n">
+        <v>48</v>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G868" t="n">
+        <v>6365</v>
+      </c>
+      <c r="H868" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D869" t="n">
+        <v>48</v>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G869" t="n">
+        <v>6367</v>
+      </c>
+      <c r="H869" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D870" t="n">
+        <v>48</v>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G870" t="n">
+        <v>6379</v>
+      </c>
+      <c r="H870" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D871" t="n">
+        <v>48</v>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G871" t="n">
+        <v>6382</v>
+      </c>
+      <c r="H871" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D872" t="n">
+        <v>48</v>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G872" t="n">
+        <v>6443</v>
+      </c>
+      <c r="H872" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D873" t="n">
+        <v>48</v>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G873" t="n">
+        <v>6456</v>
+      </c>
+      <c r="H873" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D874" t="n">
+        <v>48</v>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G874" t="n">
+        <v>6464</v>
+      </c>
+      <c r="H874" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D875" t="n">
+        <v>48</v>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G875" t="n">
+        <v>6468</v>
+      </c>
+      <c r="H875" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D876" t="n">
+        <v>48</v>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G876" t="n">
+        <v>6473</v>
+      </c>
+      <c r="H876" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D877" t="n">
+        <v>48</v>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G877" t="n">
+        <v>6515</v>
+      </c>
+      <c r="H877" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D878" t="n">
+        <v>48</v>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G878" t="n">
+        <v>6517</v>
+      </c>
+      <c r="H878" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D879" t="n">
+        <v>48</v>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G879" t="n">
+        <v>6525</v>
+      </c>
+      <c r="H879" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D880" t="n">
+        <v>48</v>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G880" t="n">
+        <v>6529</v>
+      </c>
+      <c r="H880" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D881" t="n">
+        <v>48</v>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G881" t="n">
+        <v>6537</v>
+      </c>
+      <c r="H881" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D882" t="n">
+        <v>48</v>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G882" t="n">
+        <v>6544</v>
+      </c>
+      <c r="H882" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D883" t="n">
+        <v>48</v>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G883" t="n">
+        <v>6560</v>
+      </c>
+      <c r="H883" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D884" t="n">
+        <v>48</v>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G884" t="n">
+        <v>6564</v>
+      </c>
+      <c r="H884" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D885" t="n">
+        <v>48</v>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="G885" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H885" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -13881,7 +13881,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -53643,7 +53643,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
@@ -53790,7 +53790,7 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K809" t="inlineStr">
@@ -53888,7 +53888,7 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K811" t="inlineStr">
@@ -53986,7 +53986,7 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
@@ -54231,7 +54231,7 @@
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K818" t="inlineStr">
@@ -54378,7 +54378,7 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K821" t="inlineStr">
@@ -56142,7 +56142,7 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K857" t="inlineStr">
@@ -56208,7 +56208,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Maria de Oliveira</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -56228,7 +56228,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>5876</v>
+        <v>6364</v>
       </c>
       <c r="H859" s="2" t="n">
         <v>45962</v>
@@ -56257,7 +56257,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>6165</v>
+        <v>6365</v>
       </c>
       <c r="H860" s="2" t="n">
         <v>45962</v>
@@ -56306,7 +56306,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Maria de Oliveira</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -56326,7 +56326,7 @@
         </is>
       </c>
       <c r="G861" t="n">
-        <v>6183</v>
+        <v>6379</v>
       </c>
       <c r="H861" s="2" t="n">
         <v>45962</v>
@@ -56338,7 +56338,7 @@
       </c>
       <c r="J861" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K861" t="inlineStr">
@@ -56355,7 +56355,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -56375,7 +56375,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>6250</v>
+        <v>6473</v>
       </c>
       <c r="H862" s="2" t="n">
         <v>45962</v>
@@ -56387,7 +56387,7 @@
       </c>
       <c r="J862" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K862" t="inlineStr">
@@ -56404,7 +56404,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -56424,10 +56424,10 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>6260</v>
+        <v>6544</v>
       </c>
       <c r="H863" s="2" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I863" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -56473,10 +56473,10 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>6267</v>
+        <v>6564</v>
       </c>
       <c r="H864" s="2" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I864" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
       </c>
       <c r="J864" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K864" t="inlineStr">
@@ -56502,7 +56502,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria de Oliveira</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -56522,7 +56522,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>6281</v>
+        <v>6267</v>
       </c>
       <c r="H865" s="2" t="n">
         <v>45962</v>
@@ -56534,7 +56534,7 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K865" t="inlineStr">
@@ -56551,7 +56551,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria de Oliveira</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -56562,7 +56562,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>20/09/1917</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
@@ -56571,7 +56571,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>6291</v>
+        <v>6367</v>
       </c>
       <c r="H866" s="2" t="n">
         <v>45962</v>
@@ -56600,7 +56600,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Maria de Oliveira</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -56620,7 +56620,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>6364</v>
+        <v>6443</v>
       </c>
       <c r="H867" s="2" t="n">
         <v>45962</v>
@@ -56649,7 +56649,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -56669,7 +56669,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>6365</v>
+        <v>6281</v>
       </c>
       <c r="H868" s="2" t="n">
         <v>45962</v>
@@ -56698,7 +56698,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -56718,7 +56718,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>6367</v>
+        <v>6291</v>
       </c>
       <c r="H869" s="2" t="n">
         <v>45962</v>
@@ -56730,7 +56730,7 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K869" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -56767,7 +56767,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>6379</v>
+        <v>6382</v>
       </c>
       <c r="H870" s="2" t="n">
         <v>45962</v>
@@ -56779,7 +56779,7 @@
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K870" t="inlineStr">
@@ -56816,7 +56816,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>6382</v>
+        <v>6468</v>
       </c>
       <c r="H871" s="2" t="n">
         <v>45962</v>
@@ -56828,7 +56828,7 @@
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K871" t="inlineStr">
@@ -56845,7 +56845,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -56865,7 +56865,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>6443</v>
+        <v>6537</v>
       </c>
       <c r="H872" s="2" t="n">
         <v>45962</v>
@@ -56877,7 +56877,7 @@
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K872" t="inlineStr">
@@ -56894,7 +56894,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -56914,10 +56914,10 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>6456</v>
+        <v>6560</v>
       </c>
       <c r="H873" s="2" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I873" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K873" t="inlineStr">
@@ -56943,7 +56943,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -56963,10 +56963,10 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>6464</v>
+        <v>6525</v>
       </c>
       <c r="H874" s="2" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I874" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K874" t="inlineStr">
@@ -56992,7 +56992,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -57012,10 +57012,10 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>6468</v>
+        <v>6529</v>
       </c>
       <c r="H875" s="2" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I875" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K875" t="inlineStr">
@@ -57041,7 +57041,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -57061,7 +57061,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>6473</v>
+        <v>6260</v>
       </c>
       <c r="H876" s="2" t="n">
         <v>45962</v>
@@ -57073,7 +57073,7 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K876" t="inlineStr">
@@ -57110,10 +57110,10 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>6515</v>
+        <v>6456</v>
       </c>
       <c r="H877" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I877" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K877" t="inlineStr">
@@ -57139,7 +57139,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -57159,7 +57159,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>6517</v>
+        <v>6515</v>
       </c>
       <c r="H878" s="2" t="n">
         <v>45992</v>
@@ -57188,7 +57188,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -57208,10 +57208,10 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>6525</v>
+        <v>6165</v>
       </c>
       <c r="H879" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I879" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K879" t="inlineStr">
@@ -57237,7 +57237,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -57257,7 +57257,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>6529</v>
+        <v>6517</v>
       </c>
       <c r="H880" s="2" t="n">
         <v>45992</v>
@@ -57269,7 +57269,7 @@
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K880" t="inlineStr">
@@ -57286,7 +57286,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria de Oliveira</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -57306,7 +57306,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>6537</v>
+        <v>5876</v>
       </c>
       <c r="H881" s="2" t="n">
         <v>45962</v>
@@ -57335,7 +57335,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Maria de Oliveira</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -57355,10 +57355,10 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>6544</v>
+        <v>6183</v>
       </c>
       <c r="H882" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I882" t="inlineStr">
         <is>
@@ -57384,7 +57384,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria de Oliveira</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -57404,7 +57404,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>6560</v>
+        <v>6600</v>
       </c>
       <c r="H883" s="2" t="n">
         <v>45992</v>
@@ -57433,7 +57433,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -57453,10 +57453,10 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>6564</v>
+        <v>6250</v>
       </c>
       <c r="H884" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I884" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
       </c>
       <c r="J884" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K884" t="inlineStr">
@@ -57482,7 +57482,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Maria de Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -57502,10 +57502,10 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>6600</v>
+        <v>6464</v>
       </c>
       <c r="H885" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I885" t="inlineStr">
         <is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K275"/>
+  <dimension ref="A1:K280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -13758,16 +13758,16 @@
         <v>2025</v>
       </c>
       <c r="D271" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -13905,27 +13905,27 @@
         <v>2025</v>
       </c>
       <c r="D274" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G274" t="n">
         <v>6554</v>
       </c>
       <c r="H274" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -13947,23 +13947,23 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Mara Moraes</t>
         </is>
       </c>
       <c r="C275" t="n">
         <v>2025</v>
       </c>
       <c r="D275" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -13983,6 +13983,251 @@
         </is>
       </c>
       <c r="K275" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D276" t="n">
+        <v>49</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>6589</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D277" t="n">
+        <v>49</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>6740</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D278" t="n">
+        <v>49</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>6832</v>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Luana Giese</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D279" t="n">
+        <v>49</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>6890</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D280" t="n">
+        <v>49</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>6913</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -13999,7 +14244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K885"/>
+  <dimension ref="A1:K895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50850,7 +51095,7 @@
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -51193,7 +51438,7 @@
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
@@ -52075,7 +52320,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -52565,7 +52810,7 @@
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -53324,16 +53569,16 @@
         <v>2025</v>
       </c>
       <c r="D800" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -53344,7 +53589,7 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
@@ -53667,16 +53912,16 @@
         <v>2025</v>
       </c>
       <c r="D807" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G807" t="n">
@@ -53687,7 +53932,7 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
@@ -53741,7 +53986,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K808" t="inlineStr">
@@ -54500,16 +54745,16 @@
         <v>2025</v>
       </c>
       <c r="D824" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G824" t="n">
@@ -54520,7 +54765,7 @@
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
@@ -54549,16 +54794,16 @@
         <v>2025</v>
       </c>
       <c r="D825" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G825" t="n">
@@ -54569,7 +54814,7 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
@@ -55823,16 +56068,16 @@
         <v>2025</v>
       </c>
       <c r="D851" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G851" t="n">
@@ -55843,7 +56088,7 @@
       </c>
       <c r="I851" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J851" t="inlineStr">
@@ -56240,7 +56485,7 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K859" t="inlineStr">
@@ -56289,7 +56534,7 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K860" t="inlineStr">
@@ -56436,7 +56681,7 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K863" t="inlineStr">
@@ -56551,23 +56796,23 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Maria de Oliveira</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C866" t="n">
         <v>2025</v>
       </c>
       <c r="D866" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>20/09/1917</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G866" t="n">
@@ -56578,7 +56823,7 @@
       </c>
       <c r="I866" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J866" t="inlineStr">
@@ -56632,7 +56877,7 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K867" t="inlineStr">
@@ -56656,16 +56901,16 @@
         <v>2025</v>
       </c>
       <c r="D868" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G868" t="n">
@@ -56676,7 +56921,7 @@
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J868" t="inlineStr">
@@ -57146,16 +57391,16 @@
         <v>2025</v>
       </c>
       <c r="D878" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G878" t="n">
@@ -57166,7 +57411,7 @@
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
@@ -57318,7 +57563,7 @@
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K881" t="inlineStr">
@@ -57367,7 +57612,7 @@
       </c>
       <c r="J882" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K882" t="inlineStr">
@@ -57384,23 +57629,23 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Maria de Oliveira</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C883" t="n">
         <v>2025</v>
       </c>
       <c r="D883" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G883" t="n">
@@ -57411,7 +57656,7 @@
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="J883" t="inlineStr">
@@ -57514,10 +57759,500 @@
       </c>
       <c r="J885" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D886" t="n">
+        <v>49</v>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G886" t="n">
+        <v>5828</v>
+      </c>
+      <c r="H886" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr">
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D887" t="n">
+        <v>49</v>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G887" t="n">
+        <v>6726</v>
+      </c>
+      <c r="H887" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D888" t="n">
+        <v>49</v>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G888" t="n">
+        <v>6728</v>
+      </c>
+      <c r="H888" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D889" t="n">
+        <v>49</v>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G889" t="n">
+        <v>6897</v>
+      </c>
+      <c r="H889" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D890" t="n">
+        <v>49</v>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G890" t="n">
+        <v>6923</v>
+      </c>
+      <c r="H890" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D891" t="n">
+        <v>49</v>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G891" t="n">
+        <v>6932</v>
+      </c>
+      <c r="H891" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D892" t="n">
+        <v>49</v>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G892" t="n">
+        <v>6933</v>
+      </c>
+      <c r="H892" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D893" t="n">
+        <v>49</v>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G893" t="n">
+        <v>6961</v>
+      </c>
+      <c r="H893" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D894" t="n">
+        <v>49</v>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G894" t="n">
+        <v>6994</v>
+      </c>
+      <c r="H894" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D895" t="n">
+        <v>49</v>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="G895" t="n">
+        <v>7122</v>
+      </c>
+      <c r="H895" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K280"/>
+  <dimension ref="A1:K282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -13905,16 +13905,16 @@
         <v>2025</v>
       </c>
       <c r="D274" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -14224,10 +14224,108 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Daniela Klug</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D281" t="n">
+        <v>50</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>7209</v>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D282" t="n">
+        <v>50</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>7380</v>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -14244,7 +14342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K895"/>
+  <dimension ref="A1:K915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53594,7 +53692,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
@@ -53937,7 +54035,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K807" t="inlineStr">
@@ -54770,7 +54868,7 @@
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K824" t="inlineStr">
@@ -54819,7 +54917,7 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K825" t="inlineStr">
@@ -56093,7 +56191,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K851" t="inlineStr">
@@ -56828,7 +56926,7 @@
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K866" t="inlineStr">
@@ -56901,16 +56999,16 @@
         <v>2025</v>
       </c>
       <c r="D868" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="G868" t="n">
@@ -56921,7 +57019,7 @@
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="J868" t="inlineStr">
@@ -57416,7 +57514,7 @@
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K878" t="inlineStr">
@@ -57636,16 +57734,16 @@
         <v>2025</v>
       </c>
       <c r="D883" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="G883" t="n">
@@ -57656,7 +57754,7 @@
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="J883" t="inlineStr">
@@ -57776,7 +57874,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Kaua Barros</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -57796,10 +57894,10 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>5828</v>
+        <v>6923</v>
       </c>
       <c r="H886" s="2" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I886" t="inlineStr">
         <is>
@@ -57808,7 +57906,7 @@
       </c>
       <c r="J886" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K886" t="inlineStr">
@@ -57825,7 +57923,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -57845,7 +57943,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>6726</v>
+        <v>6961</v>
       </c>
       <c r="H887" s="2" t="n">
         <v>45992</v>
@@ -57857,7 +57955,7 @@
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K887" t="inlineStr">
@@ -57874,7 +57972,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -57894,7 +57992,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>6728</v>
+        <v>6726</v>
       </c>
       <c r="H888" s="2" t="n">
         <v>45992</v>
@@ -57906,7 +58004,7 @@
       </c>
       <c r="J888" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K888" t="inlineStr">
@@ -57923,7 +58021,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -57943,7 +58041,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>6897</v>
+        <v>7122</v>
       </c>
       <c r="H889" s="2" t="n">
         <v>45992</v>
@@ -57955,7 +58053,7 @@
       </c>
       <c r="J889" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K889" t="inlineStr">
@@ -57972,7 +58070,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Kaua Barros</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -57992,10 +58090,10 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>6923</v>
+        <v>5828</v>
       </c>
       <c r="H890" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I890" t="inlineStr">
         <is>
@@ -58004,7 +58102,7 @@
       </c>
       <c r="J890" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K890" t="inlineStr">
@@ -58021,7 +58119,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Kaua Barros</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -58041,7 +58139,7 @@
         </is>
       </c>
       <c r="G891" t="n">
-        <v>6932</v>
+        <v>6994</v>
       </c>
       <c r="H891" s="2" t="n">
         <v>45992</v>
@@ -58053,7 +58151,7 @@
       </c>
       <c r="J891" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K891" t="inlineStr">
@@ -58090,7 +58188,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>6933</v>
+        <v>6897</v>
       </c>
       <c r="H892" s="2" t="n">
         <v>45992</v>
@@ -58102,7 +58200,7 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K892" t="inlineStr">
@@ -58119,7 +58217,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -58139,7 +58237,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>6961</v>
+        <v>6932</v>
       </c>
       <c r="H893" s="2" t="n">
         <v>45992</v>
@@ -58151,7 +58249,7 @@
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K893" t="inlineStr">
@@ -58168,7 +58266,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Kaua Barros</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -58188,7 +58286,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>6994</v>
+        <v>6933</v>
       </c>
       <c r="H894" s="2" t="n">
         <v>45992</v>
@@ -58200,7 +58298,7 @@
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K894" t="inlineStr">
@@ -58217,7 +58315,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -58237,7 +58335,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>7122</v>
+        <v>6728</v>
       </c>
       <c r="H895" s="2" t="n">
         <v>45992</v>
@@ -58249,10 +58347,990 @@
       </c>
       <c r="J895" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D896" t="n">
+        <v>50</v>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G896" t="n">
+        <v>6992</v>
+      </c>
+      <c r="H896" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K895" t="inlineStr">
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D897" t="n">
+        <v>50</v>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G897" t="n">
+        <v>7117</v>
+      </c>
+      <c r="H897" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D898" t="n">
+        <v>50</v>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G898" t="n">
+        <v>7123</v>
+      </c>
+      <c r="H898" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D899" t="n">
+        <v>50</v>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G899" t="n">
+        <v>7135</v>
+      </c>
+      <c r="H899" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D900" t="n">
+        <v>50</v>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G900" t="n">
+        <v>7165</v>
+      </c>
+      <c r="H900" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D901" t="n">
+        <v>50</v>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G901" t="n">
+        <v>7175</v>
+      </c>
+      <c r="H901" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D902" t="n">
+        <v>50</v>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G902" t="n">
+        <v>7202</v>
+      </c>
+      <c r="H902" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D903" t="n">
+        <v>50</v>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G903" t="n">
+        <v>7213</v>
+      </c>
+      <c r="H903" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D904" t="n">
+        <v>50</v>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G904" t="n">
+        <v>7227</v>
+      </c>
+      <c r="H904" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D905" t="n">
+        <v>50</v>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G905" t="n">
+        <v>7228</v>
+      </c>
+      <c r="H905" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D906" t="n">
+        <v>50</v>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G906" t="n">
+        <v>7258</v>
+      </c>
+      <c r="H906" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D907" t="n">
+        <v>50</v>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G907" t="n">
+        <v>7269</v>
+      </c>
+      <c r="H907" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D908" t="n">
+        <v>50</v>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G908" t="n">
+        <v>7323</v>
+      </c>
+      <c r="H908" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D909" t="n">
+        <v>50</v>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G909" t="n">
+        <v>7330</v>
+      </c>
+      <c r="H909" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D910" t="n">
+        <v>50</v>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G910" t="n">
+        <v>7335</v>
+      </c>
+      <c r="H910" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D911" t="n">
+        <v>50</v>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G911" t="n">
+        <v>7348</v>
+      </c>
+      <c r="H911" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D912" t="n">
+        <v>50</v>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G912" t="n">
+        <v>7389</v>
+      </c>
+      <c r="H912" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D913" t="n">
+        <v>50</v>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G913" t="n">
+        <v>7400</v>
+      </c>
+      <c r="H913" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D914" t="n">
+        <v>50</v>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G914" t="n">
+        <v>7401</v>
+      </c>
+      <c r="H914" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Patrick Doyle</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D915" t="n">
+        <v>50</v>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G915" t="n">
+        <v>7403</v>
+      </c>
+      <c r="H915" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luan Pierry</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,7 +993,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7905</v>
+        <v>7937</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>45992</v>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7937</v>
+        <v>7953</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>45992</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7953</v>
+        <v>7969</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7969</v>
+        <v>7975</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7975</v>
+        <v>7976</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>45992</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7976</v>
+        <v>7980</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>45992</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7980</v>
+        <v>7983</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>45992</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7983</v>
+        <v>8007</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>45992</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Emerson Simette</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8007</v>
+        <v>8113</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Maria Eduarda</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8113</v>
+        <v>8195</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>46023</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8195</v>
+        <v>8206</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>46023</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>8206</v>
+        <v>8241</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>46023</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>8241</v>
+        <v>8273</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>46023</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>8273</v>
+        <v>8275</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>46023</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>8275</v>
+        <v>8282</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>46023</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8282</v>
+        <v>8305</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>46023</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8305</v>
+        <v>8306</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>46023</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8306</v>
+        <v>8317</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>46023</v>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8317</v>
+        <v>8318</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>46023</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>8318</v>
+        <v>8320</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>46023</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Maria Eduarda</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8320</v>
+        <v>8337</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>46023</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>8337</v>
+        <v>8340</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>46023</v>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8340</v>
+        <v>8346</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>46023</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8346</v>
+        <v>8356</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>46023</v>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8356</v>
+        <v>8362</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>46023</v>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8362</v>
+        <v>8367</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>46023</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8367</v>
+        <v>8373</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>46023</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8373</v>
+        <v>8376</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>46023</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8376</v>
+        <v>8387</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>46023</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>8387</v>
+        <v>8398</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>46023</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8398</v>
+        <v>8428</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>46023</v>
@@ -2610,59 +2610,10 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
-        <is>
-          <t>Emerson Simette</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ITI</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Alana Oliveira</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>12/01/2026</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>16/01/2026</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>8428</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12/01/2026</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,8 +517,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>7779</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7779</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>45992</v>
@@ -566,8 +568,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>7841</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7841</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>45992</v>
@@ -615,8 +619,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>7854</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7854</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
         <v>45992</v>
@@ -628,7 +634,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -664,8 +670,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>8213</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8213</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
         <v>46023</v>
@@ -713,8 +721,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>8228</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8228</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
         <v>46023</v>
@@ -762,8 +772,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>8261</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8261</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>46023</v>
@@ -799,27 +811,29 @@
         <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>8262</v>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8262</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -848,27 +862,29 @@
         <v>2026</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>8288</v>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8288</t>
+        </is>
       </c>
       <c r="H9" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -877,6 +893,57 @@
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8731</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -893,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,8 +1047,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>7895</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>45992</v>
@@ -1029,8 +1098,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>7898</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7898</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>45992</v>
@@ -1078,8 +1149,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>7901</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
         <v>45992</v>
@@ -1127,8 +1200,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>7937</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
         <v>45992</v>
@@ -1157,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1176,8 +1251,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>7953</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7937</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
         <v>45992</v>
@@ -1206,7 +1283,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1225,11 +1302,13 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>7969</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7953</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1238,7 +1317,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1255,7 +1334,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1274,11 +1353,13 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>7975</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7969</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1287,7 +1368,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1323,8 +1404,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>7976</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7975</t>
+        </is>
       </c>
       <c r="H9" s="2" t="n">
         <v>45992</v>
@@ -1336,7 +1419,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1372,8 +1455,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>7980</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
         <v>45992</v>
@@ -1385,7 +1470,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1402,7 +1487,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1421,8 +1506,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>7983</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7980</t>
+        </is>
       </c>
       <c r="H11" s="2" t="n">
         <v>45992</v>
@@ -1434,7 +1521,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1451,7 +1538,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1470,8 +1557,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>8007</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
       </c>
       <c r="H12" s="2" t="n">
         <v>45992</v>
@@ -1500,7 +1589,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1519,11 +1608,13 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>8113</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1532,7 +1623,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1549,7 +1640,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Emerson Simette</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1568,8 +1659,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>8195</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8113</t>
+        </is>
       </c>
       <c r="H14" s="2" t="n">
         <v>46023</v>
@@ -1581,7 +1674,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1598,7 +1691,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Maria Eduarda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1617,8 +1710,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>8206</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8195</t>
+        </is>
       </c>
       <c r="H15" s="2" t="n">
         <v>46023</v>
@@ -1647,7 +1742,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1666,8 +1761,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>8241</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
       </c>
       <c r="H16" s="2" t="n">
         <v>46023</v>
@@ -1696,7 +1793,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1715,8 +1812,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>8273</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8241</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>46023</v>
@@ -1745,7 +1844,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1764,8 +1863,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>8275</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8273</t>
+        </is>
       </c>
       <c r="H18" s="2" t="n">
         <v>46023</v>
@@ -1777,7 +1878,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1813,8 +1914,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>8282</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8275</t>
+        </is>
       </c>
       <c r="H19" s="2" t="n">
         <v>46023</v>
@@ -1826,7 +1929,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1843,39 +1946,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2026</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>8305</v>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8282</t>
+        </is>
       </c>
       <c r="H20" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1911,8 +2016,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>8306</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
       </c>
       <c r="H21" s="2" t="n">
         <v>46023</v>
@@ -1960,8 +2067,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>8317</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
       </c>
       <c r="H22" s="2" t="n">
         <v>46023</v>
@@ -2009,8 +2118,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>8318</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8317</t>
+        </is>
       </c>
       <c r="H23" s="2" t="n">
         <v>46023</v>
@@ -2058,8 +2169,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>8320</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8318</t>
+        </is>
       </c>
       <c r="H24" s="2" t="n">
         <v>46023</v>
@@ -2088,7 +2201,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2107,8 +2220,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>8337</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
       </c>
       <c r="H25" s="2" t="n">
         <v>46023</v>
@@ -2120,7 +2235,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2137,39 +2252,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2026</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>8340</v>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>8337</t>
+        </is>
       </c>
       <c r="H26" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2186,7 +2303,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2205,8 +2322,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>8346</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>8340</t>
+        </is>
       </c>
       <c r="H27" s="2" t="n">
         <v>46023</v>
@@ -2235,7 +2354,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2254,8 +2373,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>8356</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>8346</t>
+        </is>
       </c>
       <c r="H28" s="2" t="n">
         <v>46023</v>
@@ -2267,7 +2388,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2284,7 +2405,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2303,8 +2424,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>8362</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>8356</t>
+        </is>
       </c>
       <c r="H29" s="2" t="n">
         <v>46023</v>
@@ -2352,8 +2475,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>8367</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>8362</t>
+        </is>
       </c>
       <c r="H30" s="2" t="n">
         <v>46023</v>
@@ -2382,7 +2507,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2401,8 +2526,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>8373</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
       </c>
       <c r="H31" s="2" t="n">
         <v>46023</v>
@@ -2450,8 +2577,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>8376</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>8373</t>
+        </is>
       </c>
       <c r="H32" s="2" t="n">
         <v>46023</v>
@@ -2480,7 +2609,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2499,8 +2628,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>8387</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>8376</t>
+        </is>
       </c>
       <c r="H33" s="2" t="n">
         <v>46023</v>
@@ -2529,7 +2660,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2548,8 +2679,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>8398</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>8387</t>
+        </is>
       </c>
       <c r="H34" s="2" t="n">
         <v>46023</v>
@@ -2561,7 +2694,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2597,8 +2730,10 @@
           <t>16/01/2026</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>8428</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8398</t>
+        </is>
       </c>
       <c r="H35" s="2" t="n">
         <v>46023</v>
@@ -2614,6 +2749,618 @@
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8428</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>8541</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8555</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8571</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>8647</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8699</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8715</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8723</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8757</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>8860</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SPN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ITI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITI" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,7 +838,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -940,10 +940,571 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8179</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8983</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>9137</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Luan Pierry</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>9140</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>9258</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9313</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Denis Silva</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>9315</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>9341</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>9345</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>9363</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -960,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1980,7 +2541,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2286,7 +2847,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2820,16 +3381,16 @@
         <v>2026</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2842,7 +3403,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2898,7 +3459,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2949,7 +3510,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3000,7 +3561,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3024,16 +3585,16 @@
         <v>2026</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3046,7 +3607,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3102,7 +3663,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3153,7 +3714,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3204,7 +3765,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3255,7 +3816,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3306,7 +3867,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3357,10 +3918,1030 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>8455</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8852</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8861</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>8902</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>8997</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Maria Eduarda</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>9079</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>9136</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>9191</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>9260</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>9273</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>9382</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>9411</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luan Pierry</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Luan Pierry</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Denis Silva</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Denis Silva</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Luan Pierry</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Luan Pierry</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4007,11 +4007,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4058,11 +4058,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4109,11 +4109,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Maria Eduarda</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4670,11 +4670,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4721,11 +4721,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Maria Eduarda</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1066,16 +1066,16 @@
         <v>2026</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1168,16 +1168,16 @@
         <v>2026</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1372,16 +1372,16 @@
         <v>2026</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1467,23 +1467,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luan Pierry</t>
+          <t>Luan Nicocelli</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2026</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1505,6 +1505,312 @@
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>9444</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>9457</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>9804</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Isabela Borchardt</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>9935</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -1521,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3942,16 +4248,16 @@
         <v>2026</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3964,7 +4270,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4020,7 +4326,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4095,16 +4401,16 @@
         <v>2026</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4117,7 +4423,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4173,7 +4479,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4326,7 +4632,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4581,7 +4887,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4632,7 +4938,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4942,6 +5248,618 @@
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>9392</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>9634</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>9683</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>9771</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>9790</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>9819</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>9878</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>9914</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luan Nicocelli</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Isabela Borchardt</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1678,21 +1678,21 @@
         <v>2026</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1773,44 +1773,707 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Isabela Borchardt</t>
+          <t>Luan Nicocelli</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2026</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>10075</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>10170</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>10378</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>10181</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>10613</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>10694</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10909</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>10924</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -1827,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4248,16 +4911,16 @@
         <v>2026</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4270,7 +4933,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4299,16 +4962,16 @@
         <v>2026</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4317,16 +4980,16 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4428,7 +5091,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5261,7 +5924,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5282,7 +5945,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
@@ -5295,7 +5958,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5333,11 +5996,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5346,7 +6009,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5363,7 +6026,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5384,7 +6047,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -5397,7 +6060,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5448,7 +6111,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5499,7 +6162,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5550,7 +6213,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5567,7 +6230,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -5588,7 +6251,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
@@ -5601,7 +6264,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5639,11 +6302,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5652,7 +6315,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5669,7 +6332,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5690,7 +6353,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
@@ -5703,7 +6366,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5720,7 +6383,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -5741,11 +6404,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5754,7 +6417,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5805,7 +6468,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5822,7 +6485,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -5843,23 +6506,2471 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>10016</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>10164</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>10233</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>10254</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>10363</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>10200</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D87" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D89" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>9868</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>9874</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>9978</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>10132</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D94" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>10436</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>10479</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>10315</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>10435</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D98" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>10483</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D99" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>10542</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>10432</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D101" t="n">
+        <v>6</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D102" t="n">
+        <v>6</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>10470</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>10509</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D104" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>10605</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D105" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>10664</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>10696</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D107" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>10732</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D108" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>10733</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D109" t="n">
+        <v>6</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10759</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D110" t="n">
+        <v>6</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>10766</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D111" t="n">
+        <v>6</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>10782</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D112" t="n">
+        <v>6</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>10797</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D113" t="n">
+        <v>6</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>10798</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>10806</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D115" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>10833</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D116" t="n">
+        <v>6</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>10835</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D117" t="n">
+        <v>6</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>10871</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D118" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>10877</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D119" t="n">
+        <v>6</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>10881</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D120" t="n">
+        <v>6</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>10883</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D121" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>10888</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D122" t="n">
+        <v>6</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D123" t="n">
+        <v>6</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>10908</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D124" t="n">
+        <v>6</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>10931</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>10980</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D126" t="n">
+        <v>6</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>10986</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D127" t="n">
+        <v>6</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>11014</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Mara Neves</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Mara Neves</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kaua Barros</t>
+          <t>Emerson Simette</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>sostenes silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Kaua Barros</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>sostenes silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="H122" s="2" t="n">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="H123" s="2" t="n">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="H124" s="2" t="n">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="H125" s="2" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>sostenes silva</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="H126" s="2" t="n">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>sostenes silva</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2341,16 +2341,16 @@
         <v>2026</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2392,16 +2392,16 @@
         <v>2026</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2474,6 +2474,261 @@
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10758</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>11185</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>11259</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>11308</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -2490,7 +2745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,7 +5193,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4962,16 +5217,16 @@
         <v>2026</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4984,7 +5239,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5261,23 +5516,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5290,12 +5545,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6186,16 +6441,16 @@
         <v>2026</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6208,12 +6463,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6543,16 +6798,16 @@
         <v>2026</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6565,7 +6820,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6594,16 +6849,16 @@
         <v>2026</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6616,7 +6871,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6696,16 +6951,16 @@
         <v>2026</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6718,12 +6973,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6876,7 +7131,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6978,7 +7233,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7002,16 +7257,16 @@
         <v>2026</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7024,7 +7279,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7155,16 +7410,16 @@
         <v>2026</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7177,7 +7432,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7488,7 +7743,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7563,16 +7818,16 @@
         <v>2026</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7585,7 +7840,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -7641,7 +7896,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7665,16 +7920,16 @@
         <v>2026</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7687,7 +7942,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7716,16 +7971,16 @@
         <v>2026</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7738,7 +7993,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7818,16 +8073,16 @@
         <v>2026</v>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7840,7 +8095,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -8022,16 +8277,16 @@
         <v>2026</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8044,7 +8299,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -8151,7 +8406,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -8253,7 +8508,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8304,7 +8559,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8355,7 +8610,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8610,7 +8865,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8685,16 +8940,16 @@
         <v>2026</v>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8707,7 +8962,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8971,6 +9226,516 @@
         </is>
       </c>
       <c r="K127" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D128" t="n">
+        <v>7</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>11252</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D129" t="n">
+        <v>7</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>10870</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D131" t="n">
+        <v>7</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>10955</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D132" t="n">
+        <v>7</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>11268</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D133" t="n">
+        <v>7</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>11286</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D134" t="n">
+        <v>7</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>11287</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D135" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D136" t="n">
+        <v>7</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>11310</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D137" t="n">
+        <v>7</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>11338</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2538,28 +2538,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Luan Nicocelli</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2026</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Luan Nicocelli</t>
+          <t>Mara Neves</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -2725,10 +2725,367 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>11548</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>11711</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>11785</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Clanderson Oliveira</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>11644</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>11511</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>11489</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rosane Custodio</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>10889</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -2745,7 +3102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5244,7 +5601,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5550,7 +5907,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6468,7 +6825,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6825,7 +7182,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6876,7 +7233,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6978,7 +7335,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7284,7 +7641,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7437,7 +7794,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7845,7 +8202,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7947,7 +8304,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7998,7 +8355,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8100,7 +8457,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8304,7 +8661,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -8967,7 +9324,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -9273,7 +9630,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9324,7 +9681,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -9375,7 +9732,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9426,7 +9783,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9477,7 +9834,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9501,16 +9858,16 @@
         <v>2026</v>
       </c>
       <c r="D133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9523,7 +9880,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -9579,7 +9936,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9630,7 +9987,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9681,7 +10038,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9705,16 +10062,16 @@
         <v>2026</v>
       </c>
       <c r="D137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9727,7 +10084,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9736,6 +10093,1230 @@
         </is>
       </c>
       <c r="K137" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D138" t="n">
+        <v>8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>11810</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D139" t="n">
+        <v>8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D140" t="n">
+        <v>8</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>11479</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D141" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>11620</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D142" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>11621</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D143" t="n">
+        <v>8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>11704</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D144" t="n">
+        <v>8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>11705</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D145" t="n">
+        <v>8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>11714</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D146" t="n">
+        <v>8</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>11722</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>11792</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>11814</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D149" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>11884</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D150" t="n">
+        <v>8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D151" t="n">
+        <v>8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>11696</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D152" t="n">
+        <v>8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>11562</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D153" t="n">
+        <v>8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>11871</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D154" t="n">
+        <v>8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>11586</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D155" t="n">
+        <v>8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>11873</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D156" t="n">
+        <v>8</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>11964</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D157" t="n">
+        <v>8</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>11585</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D158" t="n">
+        <v>8</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>11770</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D159" t="n">
+        <v>8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D160" t="n">
+        <v>8</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>11786</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D161" t="n">
+        <v>8</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>11943</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2749,16 +2749,16 @@
         <v>2026</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2800,16 +2800,16 @@
         <v>2026</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,16 +2851,16 @@
         <v>2026</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2902,16 +2902,16 @@
         <v>2026</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>2026</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3073,19 +3073,274 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>11955</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Clanderson Oliveira</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D54" t="n">
+        <v>9</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>12115</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D56" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>12154</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>12257</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -3102,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5880,16 +6135,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5902,12 +6157,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7155,16 +7410,16 @@
         <v>2026</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7177,12 +7432,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9885,7 +10140,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -10089,7 +10344,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -10140,7 +10395,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -10191,7 +10446,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -10215,16 +10470,16 @@
         <v>2026</v>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10237,7 +10492,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -10293,7 +10548,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -10344,7 +10599,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10395,7 +10650,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10446,7 +10701,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10497,7 +10752,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10548,7 +10803,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10599,7 +10854,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10650,7 +10905,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10701,7 +10956,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10752,7 +11007,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10803,7 +11058,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10854,7 +11109,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10905,7 +11160,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10929,16 +11184,16 @@
         <v>2026</v>
       </c>
       <c r="D154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10951,7 +11206,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -11007,7 +11262,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -11058,7 +11313,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -11109,7 +11364,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -11160,7 +11415,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -11211,7 +11466,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11262,7 +11517,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11313,10 +11568,979 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D162" t="n">
+        <v>9</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>11970</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D163" t="n">
+        <v>9</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D164" t="n">
+        <v>9</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>12209</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D165" t="n">
+        <v>9</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>12219</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D166" t="n">
+        <v>9</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>12244</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D167" t="n">
+        <v>9</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>12249</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D168" t="n">
+        <v>9</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>12275</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D169" t="n">
+        <v>9</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>12309</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D170" t="n">
+        <v>9</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>12314</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D171" t="n">
+        <v>9</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>12315</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D172" t="n">
+        <v>9</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>12320</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D173" t="n">
+        <v>9</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>12333</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D174" t="n">
+        <v>9</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>12338</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D175" t="n">
+        <v>9</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>12339</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D176" t="n">
+        <v>9</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>12349</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D177" t="n">
+        <v>9</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>12351</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D178" t="n">
+        <v>9</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>12354</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D179" t="n">
+        <v>9</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>12374</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D180" t="n">
+        <v>9</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>12482</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -2827,7 +2827,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11202,7 +11202,7 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -11657,11 +11657,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11759,11 +11759,11 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="H167" s="2" t="n">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="H169" s="2" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="H176" s="2" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="H177" s="2" t="n">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="H178" s="2" t="n">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="H179" s="2" t="n">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3337,10 +3337,1744 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>12460</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>12467</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>12468</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D61" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>12530</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D62" t="n">
+        <v>11</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>12713</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>12760</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>12808</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>12809</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>12636</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>12658</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>12665</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>12691</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>12693</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>12798</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D72" t="n">
+        <v>11</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>12638</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>12814</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D74" t="n">
+        <v>11</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>12179</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>12252</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D77" t="n">
+        <v>11</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>12596</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D78" t="n">
+        <v>11</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>12832</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D79" t="n">
+        <v>11</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>12921</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D80" t="n">
+        <v>11</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>12932</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D81" t="n">
+        <v>11</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D82" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>13034</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D83" t="n">
+        <v>11</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>13118</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D84" t="n">
+        <v>11</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>13166</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D85" t="n">
+        <v>11</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>13038</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D86" t="n">
+        <v>11</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Denis Silva</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D87" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>12479</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D88" t="n">
+        <v>11</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>12922</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D89" t="n">
+        <v>11</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>13124</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D90" t="n">
+        <v>11</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>11713</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D91" t="n">
+        <v>11</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>13177</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -3357,7 +5091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6135,16 +7869,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6153,11 +7887,11 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7410,16 +9144,16 @@
         <v>2026</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7432,7 +9166,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11184,16 +12918,16 @@
         <v>2026</v>
       </c>
       <c r="D154" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11202,11 +12936,11 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -11847,16 +13581,16 @@
         <v>2026</v>
       </c>
       <c r="D167" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -11869,7 +13603,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11898,16 +13632,16 @@
         <v>2026</v>
       </c>
       <c r="D168" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11920,12 +13654,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11949,16 +13683,16 @@
         <v>2026</v>
       </c>
       <c r="D169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11971,12 +13705,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -12541,6 +14275,1791 @@
         </is>
       </c>
       <c r="K180" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D181" t="n">
+        <v>10</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D182" t="n">
+        <v>10</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>12596</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D183" t="n">
+        <v>10</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>12628</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D184" t="n">
+        <v>10</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>12652</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D185" t="n">
+        <v>10</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>12869</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D186" t="n">
+        <v>11</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>12727</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D187" t="n">
+        <v>10</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>12774</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D188" t="n">
+        <v>10</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>12776</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D189" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>12779</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D190" t="n">
+        <v>10</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>12780</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D191" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>12781</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>12783</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D193" t="n">
+        <v>10</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>12735</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>12817</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D195" t="n">
+        <v>11</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>12365</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D196" t="n">
+        <v>10</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D197" t="n">
+        <v>10</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>12828</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D198" t="n">
+        <v>10</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>12934</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D199" t="n">
+        <v>11</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>12860</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D200" t="n">
+        <v>11</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>13183</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D201" t="n">
+        <v>11</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>13252</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D202" t="n">
+        <v>11</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>13200</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D203" t="n">
+        <v>11</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>13231</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D204" t="n">
+        <v>11</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>13017</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D205" t="n">
+        <v>11</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>13136</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D206" t="n">
+        <v>11</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>13222</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D207" t="n">
+        <v>11</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>13226</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D208" t="n">
+        <v>11</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>13283</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D209" t="n">
+        <v>11</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D210" t="n">
+        <v>11</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>13258</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D211" t="n">
+        <v>11</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>13071</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D212" t="n">
+        <v>11</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>13147</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D213" t="n">
+        <v>11</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>13232</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D214" t="n">
+        <v>11</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>13165</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D215" t="n">
+        <v>11</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>13195</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4177,16 +4177,16 @@
         <v>2026</v>
       </c>
       <c r="D74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4330,16 +4330,16 @@
         <v>2026</v>
       </c>
       <c r="D77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4381,16 +4381,16 @@
         <v>2026</v>
       </c>
       <c r="D78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4534,16 +4534,16 @@
         <v>2026</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4585,16 +4585,16 @@
         <v>2026</v>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4636,16 +4636,16 @@
         <v>2026</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>2026</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4738,16 +4738,16 @@
         <v>2026</v>
       </c>
       <c r="D85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4993,16 +4993,16 @@
         <v>2026</v>
       </c>
       <c r="D90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5071,10 +5071,622 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D92" t="n">
+        <v>12</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>13410</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D93" t="n">
+        <v>12</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>13673</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D94" t="n">
+        <v>12</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>13383</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D95" t="n">
+        <v>12</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>13326</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D96" t="n">
+        <v>12</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>13329</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D97" t="n">
+        <v>12</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>13348</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D98" t="n">
+        <v>12</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>13457</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>13702</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D100" t="n">
+        <v>12</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>13738</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mara neves</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D101" t="n">
+        <v>12</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>13451</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D102" t="n">
+        <v>12</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>13721</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D103" t="n">
+        <v>12</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>13771</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -5091,7 +5703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K215"/>
+  <dimension ref="A1:K227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7869,16 +8481,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7891,7 +8503,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9171,7 +9783,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -12945,7 +13557,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -13608,7 +14220,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -14577,7 +15189,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -15036,7 +15648,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -15240,7 +15852,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -15291,7 +15903,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -15342,7 +15954,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -15366,16 +15978,16 @@
         <v>2026</v>
       </c>
       <c r="D202" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15388,7 +16000,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -15444,7 +16056,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -15468,16 +16080,16 @@
         <v>2026</v>
       </c>
       <c r="D204" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15490,7 +16102,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -15546,7 +16158,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -15597,7 +16209,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -15648,7 +16260,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -15699,7 +16311,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -15750,7 +16362,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -15801,7 +16413,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -15852,7 +16464,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -15876,16 +16488,16 @@
         <v>2026</v>
       </c>
       <c r="D212" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15898,7 +16510,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -15954,7 +16566,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -16005,7 +16617,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -16056,10 +16668,622 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D216" t="n">
+        <v>12</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>12612</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D217" t="n">
+        <v>12</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>13294</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>José Hugo Almeida</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D218" t="n">
+        <v>12</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>13386</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>emerson pellis</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D219" t="n">
+        <v>12</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>13435</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>emerson pellis</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D220" t="n">
+        <v>12</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>13446</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D221" t="n">
+        <v>12</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>13480</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>sostenes silva</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D222" t="n">
+        <v>12</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>13489</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D223" t="n">
+        <v>12</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>13705</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D224" t="n">
+        <v>12</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>13763</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D225" t="n">
+        <v>12</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D226" t="n">
+        <v>12</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>13808</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D227" t="n">
+        <v>12</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>13834</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4177,16 +4177,16 @@
         <v>2026</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5197,16 +5197,16 @@
         <v>2026</v>
       </c>
       <c r="D94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5248,16 +5248,16 @@
         <v>2026</v>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5350,16 +5350,16 @@
         <v>2026</v>
       </c>
       <c r="D97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5547,23 +5547,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mara neves</t>
+          <t>Mara Neves</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>2026</v>
       </c>
       <c r="D101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5683,10 +5683,163 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D104" t="n">
+        <v>13</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>13891</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Denis da Silva</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D105" t="n">
+        <v>13</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>14120</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D106" t="n">
+        <v>13</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>14131</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -5703,7 +5856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K227"/>
+  <dimension ref="A1:K244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8481,16 +8634,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8499,11 +8652,11 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46023</v>
+        <v>46045.66640046296</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -16005,7 +16158,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -16107,7 +16260,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -16515,7 +16668,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -16719,7 +16872,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -16770,7 +16923,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -16794,16 +16947,16 @@
         <v>2026</v>
       </c>
       <c r="D218" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16812,11 +16965,11 @@
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46082</v>
+        <v>46105.60100694445</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -16838,23 +16991,23 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>emerson pellis</t>
+          <t>Emerson Pellis</t>
         </is>
       </c>
       <c r="C219" t="n">
         <v>2026</v>
       </c>
       <c r="D219" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16863,11 +17016,11 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46082</v>
+        <v>46105.60737268518</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -16889,23 +17042,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>emerson pellis</t>
+          <t>Emerson Pellis</t>
         </is>
       </c>
       <c r="C220" t="n">
         <v>2026</v>
       </c>
       <c r="D220" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16914,11 +17067,11 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46082</v>
+        <v>46105.68079861111</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -16974,7 +17127,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -17025,7 +17178,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -17076,7 +17229,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -17127,7 +17280,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -17151,16 +17304,16 @@
         <v>2026</v>
       </c>
       <c r="D225" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -17169,11 +17322,11 @@
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>46082</v>
+        <v>46108.70833333334</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -17229,7 +17382,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -17280,10 +17433,877 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D228" t="n">
+        <v>13</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>13764</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>46112.41462962963</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D229" t="n">
+        <v>13</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>13829</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>46113.44739583333</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D230" t="n">
+        <v>13</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>13876</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>46112.69475694445</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D231" t="n">
+        <v>13</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>14007</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>46114.42952546296</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D232" t="n">
+        <v>13</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>14016</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>46114.35668981481</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D233" t="n">
+        <v>13</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>14030</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>46113.56847222222</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D234" t="n">
+        <v>13</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>14068</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>46115.56099537037</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D235" t="n">
+        <v>13</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>14091</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>46115.6622337963</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D236" t="n">
+        <v>13</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>14098</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>46115.43804398148</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D237" t="n">
+        <v>13</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>14130</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>46115.64065972222</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D238" t="n">
+        <v>13</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>14136</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>46118.56533564815</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D239" t="n">
+        <v>13</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>14145</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>46115.58333333334</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D240" t="n">
+        <v>13</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>46118.49258101852</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D241" t="n">
+        <v>13</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>46118.70175925926</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D242" t="n">
+        <v>13</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>46119.41722222222</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D243" t="n">
+        <v>13</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>14297</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>46118.33337962963</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D244" t="n">
+        <v>13</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>46119.41666666666</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -5581,7 +5581,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Luan Nicocelli</t>
+          <t>Denis da Silva</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Denis da Silva</t>
+          <t>Luan Nicocelli</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46045.66640046296</v>
+        <v>46105.60100694445</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46105.60100694445</v>
+        <v>46115.64065972222</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46105.60737268518</v>
+        <v>46105.68079861111</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46105.68079861111</v>
+        <v>46112.41462962963</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>46108.70833333334</v>
+        <v>46118.70175925926</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -17471,11 +17471,11 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>46112.41462962963</v>
+        <v>46045.66640046296</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -17522,11 +17522,11 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>46113.44739583333</v>
+        <v>46105.60737268518</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -17573,11 +17573,11 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>46112.69475694445</v>
+        <v>46108.70833333334</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -17624,11 +17624,11 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>46114.42952546296</v>
+        <v>46113.44739583333</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         </is>
       </c>
       <c r="H232" s="2" t="n">
-        <v>46114.35668981481</v>
+        <v>46112.69475694445</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -17726,11 +17726,11 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="H233" s="2" t="n">
-        <v>46113.56847222222</v>
+        <v>46114.42952546296</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -17777,11 +17777,11 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="H234" s="2" t="n">
-        <v>46115.56099537037</v>
+        <v>46114.35668981481</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -17828,11 +17828,11 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="H235" s="2" t="n">
-        <v>46115.6622337963</v>
+        <v>46113.56847222222</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -17879,11 +17879,11 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="H236" s="2" t="n">
-        <v>46115.43804398148</v>
+        <v>46115.56099537037</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -17930,11 +17930,11 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="H237" s="2" t="n">
-        <v>46115.64065972222</v>
+        <v>46115.6622337963</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -17981,11 +17981,11 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46118.56533564815</v>
+        <v>46115.43804398148</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -18032,11 +18032,11 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="H239" s="2" t="n">
-        <v>46115.58333333334</v>
+        <v>46118.56533564815</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -18083,11 +18083,11 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>46118.49258101852</v>
+        <v>46115.58333333334</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -18134,11 +18134,11 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="H241" s="2" t="n">
-        <v>46118.70175925926</v>
+        <v>46118.49258101852</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="H242" s="2" t="n">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>14030</t>
         </is>
       </c>
       <c r="H243" s="2" t="n">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="H244" s="2" t="n">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -4204,7 +4204,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5197,16 +5197,16 @@
         <v>2026</v>
       </c>
       <c r="D94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5215,11 +5215,11 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46082</v>
+        <v>46105.59543981482</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5248,16 +5248,16 @@
         <v>2026</v>
       </c>
       <c r="D95" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5266,11 +5266,11 @@
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46082</v>
+        <v>46104.70833333334</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5350,16 +5350,16 @@
         <v>2026</v>
       </c>
       <c r="D97" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5368,11 +5368,11 @@
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46082</v>
+        <v>46105.40059027778</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5809,16 +5809,16 @@
         <v>2026</v>
       </c>
       <c r="D106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5827,11 +5827,11 @@
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46113</v>
+        <v>46122.64236111111</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K244"/>
+  <dimension ref="A1:K260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8634,16 +8634,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8652,11 +8652,11 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46105.60100694445</v>
+        <v>46045.66640046296</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -16998,16 +16998,16 @@
         <v>2026</v>
       </c>
       <c r="D219" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -17016,11 +17016,11 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46105.68079861111</v>
+        <v>46105.60737268518</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -17049,16 +17049,16 @@
         <v>2026</v>
       </c>
       <c r="D220" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -17067,11 +17067,11 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46112.41462962963</v>
+        <v>46105.68079861111</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -17508,16 +17508,16 @@
         <v>2026</v>
       </c>
       <c r="D229" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17526,11 +17526,11 @@
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>46105.60737268518</v>
+        <v>46115.6622337963</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -17603,23 +17603,23 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>2026</v>
       </c>
       <c r="D231" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17628,11 +17628,11 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>46113.44739583333</v>
+        <v>46112.69475694445</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -17712,16 +17712,16 @@
         <v>2026</v>
       </c>
       <c r="D233" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17730,11 +17730,11 @@
         </is>
       </c>
       <c r="H233" s="2" t="n">
-        <v>46114.42952546296</v>
+        <v>46115.43804398148</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -17756,23 +17756,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C234" t="n">
         <v>2026</v>
       </c>
       <c r="D234" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17781,11 +17781,11 @@
         </is>
       </c>
       <c r="H234" s="2" t="n">
-        <v>46114.35668981481</v>
+        <v>46115.64065972222</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -17814,16 +17814,16 @@
         <v>2026</v>
       </c>
       <c r="D235" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17832,11 +17832,11 @@
         </is>
       </c>
       <c r="H235" s="2" t="n">
-        <v>46113.56847222222</v>
+        <v>46115.58333333334</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -17967,16 +17967,16 @@
         <v>2026</v>
       </c>
       <c r="D238" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46115.43804398148</v>
+        <v>46118.49258101852</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -18011,23 +18011,23 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C239" t="n">
         <v>2026</v>
       </c>
       <c r="D239" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -18222,16 +18222,16 @@
         <v>2026</v>
       </c>
       <c r="D243" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18240,11 +18240,11 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>46118.33337962963</v>
+        <v>46113.56847222222</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -18304,6 +18304,822 @@
         </is>
       </c>
       <c r="K244" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D245" t="n">
+        <v>14</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>14250</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>46119.45128472222</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D246" t="n">
+        <v>14</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>14372</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>46121.45960648148</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D247" t="n">
+        <v>14</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>46121.57119212963</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D248" t="n">
+        <v>14</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>14406</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>46121.52210648148</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D249" t="n">
+        <v>14</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>14409</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>46121.53282407407</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D250" t="n">
+        <v>14</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>14431</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>46121.58333333334</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D251" t="n">
+        <v>14</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>14441</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>46122.38736111111</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D252" t="n">
+        <v>14</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>46122.40847222223</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D253" t="n">
+        <v>14</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>14467</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>46122.40086805556</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D254" t="n">
+        <v>14</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>14468</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>46122.52670138889</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D255" t="n">
+        <v>14</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>14494</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>46122.68505787037</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D256" t="n">
+        <v>14</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>14497</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>46122.69494212963</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D257" t="n">
+        <v>14</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>14518</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>46125.34267361111</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D258" t="n">
+        <v>14</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>14525</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>46122.65364583334</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D259" t="n">
+        <v>14</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>14535</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>46125.45486111111</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D260" t="n">
+        <v>14</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>14570</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>46122.61519675926</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -5224,7 +5224,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46045.66640046296</v>
+        <v>46115.6622337963</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46105.60737268518</v>
+        <v>46118.56533564815</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46105.68079861111</v>
+        <v>46115.58333333334</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>46115.6622337963</v>
+        <v>46115.43804398148</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>46112.69475694445</v>
+        <v>46122.40086805556</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="H233" s="2" t="n">
-        <v>46115.43804398148</v>
+        <v>46121.45960648148</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         </is>
       </c>
       <c r="H234" s="2" t="n">
-        <v>46115.64065972222</v>
+        <v>46122.52670138889</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="H235" s="2" t="n">
-        <v>46115.58333333334</v>
+        <v>46121.57119212963</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46118.49258101852</v>
+        <v>46121.53282407407</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="H239" s="2" t="n">
-        <v>46118.56533564815</v>
+        <v>46115.64065972222</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -18240,7 +18240,7 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>46113.56847222222</v>
+        <v>46122.69494212963</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -18338,11 +18338,11 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="H245" s="2" t="n">
-        <v>46119.45128472222</v>
+        <v>46045.66640046296</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -18389,11 +18389,11 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>46121.45960648148</v>
+        <v>46105.60737268518</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -18440,11 +18440,11 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="H247" s="2" t="n">
-        <v>46121.57119212963</v>
+        <v>46105.68079861111</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -18491,11 +18491,11 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="H248" s="2" t="n">
-        <v>46121.52210648148</v>
+        <v>46112.69475694445</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -18542,11 +18542,11 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="H249" s="2" t="n">
-        <v>46121.53282407407</v>
+        <v>46113.56847222222</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -18593,11 +18593,11 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>46121.58333333334</v>
+        <v>46118.49258101852</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Emerson Pellis</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -18644,11 +18644,11 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>46122.38736111111</v>
+        <v>46119.45128472222</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -18695,11 +18695,11 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>46122.40847222223</v>
+        <v>46121.52210648148</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -18746,11 +18746,11 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="H253" s="2" t="n">
-        <v>46122.40086805556</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -18776,7 +18776,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -18797,11 +18797,11 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>46122.52670138889</v>
+        <v>46122.38736111111</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -18848,11 +18848,11 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>46122.68505787037</v>
+        <v>46122.40847222223</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -18899,11 +18899,11 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="H256" s="2" t="n">
-        <v>46122.69494212963</v>
+        <v>46122.68505787037</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="H257" s="2" t="n">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="H258" s="2" t="n">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="H259" s="2" t="n">
@@ -19116,7 +19116,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5248,16 +5248,16 @@
         <v>2026</v>
       </c>
       <c r="D95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5809,16 +5809,16 @@
         <v>2026</v>
       </c>
       <c r="D106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5840,6 +5840,465 @@
         </is>
       </c>
       <c r="K106" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D107" t="n">
+        <v>15</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>14640</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>46126.62421296296</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D108" t="n">
+        <v>15</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>14845</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>46128.65608796296</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D109" t="n">
+        <v>15</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>14854</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>46128.675</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D110" t="n">
+        <v>15</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>14905</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>46129.47980324074</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D111" t="n">
+        <v>15</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>46132.42730324074</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D112" t="n">
+        <v>15</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>14991</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>46129.47251157407</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D113" t="n">
+        <v>15</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>15009</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>46132.60649305556</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D114" t="n">
+        <v>15</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>15018</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46132.63126157408</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D115" t="n">
+        <v>15</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>15062</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>46133.40931712963</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -5856,7 +6315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K260"/>
+  <dimension ref="A1:K285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8661,7 +9120,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -17025,7 +17484,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -17076,7 +17535,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -17637,7 +18096,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -17739,7 +18198,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -17790,7 +18249,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -17841,7 +18300,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -17967,16 +18426,16 @@
         <v>2026</v>
       </c>
       <c r="D238" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17985,11 +18444,11 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46121.53282407407</v>
+        <v>46118.49258101852</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -18351,7 +18810,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -18453,7 +18912,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -18579,16 +19038,16 @@
         <v>2026</v>
       </c>
       <c r="D250" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18597,11 +19056,11 @@
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>46118.49258101852</v>
+        <v>46121.53282407407</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -18630,16 +19089,16 @@
         <v>2026</v>
       </c>
       <c r="D251" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18648,11 +19107,11 @@
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>46119.45128472222</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -18681,16 +19140,16 @@
         <v>2026</v>
       </c>
       <c r="D252" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18703,7 +19162,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -18783,16 +19242,16 @@
         <v>2026</v>
       </c>
       <c r="D254" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -18801,11 +19260,11 @@
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>46122.38736111111</v>
+        <v>46122.40847222223</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -18834,16 +19293,16 @@
         <v>2026</v>
       </c>
       <c r="D255" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -18852,11 +19311,11 @@
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>46122.40847222223</v>
+        <v>46121.45960648148</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -18987,16 +19446,16 @@
         <v>2026</v>
       </c>
       <c r="D258" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19005,11 +19464,11 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>46122.65364583334</v>
+        <v>46122.69494212963</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -19065,7 +19524,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -19120,6 +19579,1281 @@
         </is>
       </c>
       <c r="K260" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D261" t="n">
+        <v>15</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>14583</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>46128.375625</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D262" t="n">
+        <v>15</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>46127.35106481481</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D263" t="n">
+        <v>15</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>14790</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>46127.62325231481</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D264" t="n">
+        <v>15</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>14792</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>46127.63143518518</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D265" t="n">
+        <v>15</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>14799</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>46128.67709490741</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D266" t="n">
+        <v>15</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>14857</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>46128.69707175926</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D267" t="n">
+        <v>15</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>14858</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>46127.70364583333</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D268" t="n">
+        <v>15</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>14891</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>46128.62407407408</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D269" t="n">
+        <v>15</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>14898</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>46133.34523148148</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D270" t="n">
+        <v>15</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>14900</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>46129.43733796296</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D271" t="n">
+        <v>15</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>14925</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>46129.63375</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D272" t="n">
+        <v>15</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>14940</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>46129.33358796296</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D273" t="n">
+        <v>15</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>46127.66684027778</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D274" t="n">
+        <v>15</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>14972</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>46132.37733796296</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D275" t="n">
+        <v>15</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>14973</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>46132.38037037037</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D276" t="n">
+        <v>15</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>46133.40105324074</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D277" t="n">
+        <v>15</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>15019</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>46132.64863425926</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D278" t="n">
+        <v>15</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>15050</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>46133.36008101852</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D279" t="n">
+        <v>15</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>15055</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>46133.38364583333</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D280" t="n">
+        <v>15</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>15060</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>46133.40050925926</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D281" t="n">
+        <v>15</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>15084</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>46132.54476851852</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D282" t="n">
+        <v>15</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>15103</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>46132.64361111111</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D283" t="n">
+        <v>15</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>15138</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>46133.36665509259</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D284" t="n">
+        <v>15</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>15152</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>46133.44292824074</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D285" t="n">
+        <v>15</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>15240</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>46133.41666666666</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Elisandra Chaves</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46126.62421296296</v>
+        <v>46129.47251157407</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5911,29 +5911,29 @@
         <v>2026</v>
       </c>
       <c r="D108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46128.65608796296</v>
+        <v>46126.62421296296</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5962,29 +5962,29 @@
         <v>2026</v>
       </c>
       <c r="D109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>14854</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46128.675</v>
+        <v>46128.65608796296</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46129.47980324074</v>
+        <v>46128.675</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6078,11 +6078,11 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46132.42730324074</v>
+        <v>46129.47980324074</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Elisandra Chaves</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46129.47251157407</v>
+        <v>46132.42730324074</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6295,10 +6295,163 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D116" t="n">
+        <v>16</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>15129</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>46133.70833333334</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D117" t="n">
+        <v>16</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>15180</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>46134.64966435185</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Marcos Silva</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D118" t="n">
+        <v>16</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>15219</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>46134.58334490741</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -6315,7 +6468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K285"/>
+  <dimension ref="A1:K297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9093,16 +9246,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -9111,16 +9264,16 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46115.6622337963</v>
+        <v>46121.45960648148</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -17457,16 +17610,16 @@
         <v>2026</v>
       </c>
       <c r="D219" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -17475,16 +17628,16 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46118.56533564815</v>
+        <v>46121.52210648148</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -17508,16 +17661,16 @@
         <v>2026</v>
       </c>
       <c r="D220" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -17526,16 +17679,16 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46115.58333333334</v>
+        <v>46121.53282407407</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -18444,7 +18597,7 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46118.49258101852</v>
+        <v>46129.33358796296</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18453,7 +18606,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -19038,16 +19191,16 @@
         <v>2026</v>
       </c>
       <c r="D250" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -19056,11 +19209,11 @@
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>46121.53282407407</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -19089,16 +19242,16 @@
         <v>2026</v>
       </c>
       <c r="D251" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -19107,11 +19260,11 @@
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>46121.58333333334</v>
+        <v>46122.69494212963</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -19140,16 +19293,16 @@
         <v>2026</v>
       </c>
       <c r="D252" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -19158,11 +19311,11 @@
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>46121.52210648148</v>
+        <v>46128.67709490741</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -19260,7 +19413,7 @@
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>46122.40847222223</v>
+        <v>46132.38037037037</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -19269,7 +19422,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -19293,16 +19446,16 @@
         <v>2026</v>
       </c>
       <c r="D255" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19311,11 +19464,11 @@
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>46121.45960648148</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -19446,16 +19599,16 @@
         <v>2026</v>
       </c>
       <c r="D258" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19464,11 +19617,11 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>46122.69494212963</v>
+        <v>46139.33881944444</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -19592,7 +19745,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -19613,11 +19766,11 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="H261" s="2" t="n">
-        <v>46128.375625</v>
+        <v>46118.49258101852</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -19626,7 +19779,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -19643,28 +19796,28 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Emerson Pellis</t>
         </is>
       </c>
       <c r="C262" t="n">
         <v>2026</v>
       </c>
       <c r="D262" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="H262" s="2" t="n">
@@ -19672,7 +19825,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -19694,36 +19847,36 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C263" t="n">
         <v>2026</v>
       </c>
       <c r="D263" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="H263" s="2" t="n">
-        <v>46127.62325231481</v>
+        <v>46128.69707175926</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -19745,36 +19898,36 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C264" t="n">
         <v>2026</v>
       </c>
       <c r="D264" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="H264" s="2" t="n">
-        <v>46127.63143518518</v>
+        <v>46128.62407407408</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -19796,7 +19949,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -19817,11 +19970,11 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="H265" s="2" t="n">
-        <v>46128.67709490741</v>
+        <v>46128.375625</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -19830,7 +19983,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -19868,11 +20021,11 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="H266" s="2" t="n">
-        <v>46128.69707175926</v>
+        <v>46127.35106481481</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -19881,7 +20034,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -19898,7 +20051,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Kaua Barros</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -19919,11 +20072,11 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>46127.70364583333</v>
+        <v>46127.62325231481</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -19932,7 +20085,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -19949,7 +20102,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -19970,11 +20123,11 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>46128.62407407408</v>
+        <v>46127.63143518518</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -19983,7 +20136,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -20000,7 +20153,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -20021,11 +20174,11 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>46133.34523148148</v>
+        <v>46128.67709490741</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -20034,7 +20187,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -20058,29 +20211,29 @@
         <v>2026</v>
       </c>
       <c r="D270" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>46129.43733796296</v>
+        <v>46135.47771990741</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -20102,7 +20255,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -20123,11 +20276,11 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>46129.63375</v>
+        <v>46127.70364583333</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -20136,7 +20289,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -20153,7 +20306,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Kaua Barros</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -20174,11 +20327,11 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="H272" s="2" t="n">
-        <v>46129.33358796296</v>
+        <v>46128.62407407408</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -20187,7 +20340,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -20204,7 +20357,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -20225,11 +20378,11 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="H273" s="2" t="n">
-        <v>46127.66684027778</v>
+        <v>46133.34523148148</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -20238,7 +20391,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -20276,11 +20429,11 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="H274" s="2" t="n">
-        <v>46132.37733796296</v>
+        <v>46129.43733796296</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -20289,7 +20442,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -20306,7 +20459,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -20327,11 +20480,11 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="H275" s="2" t="n">
-        <v>46132.38037037037</v>
+        <v>46129.63375</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -20340,7 +20493,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -20357,7 +20510,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Kaua Barros</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -20378,11 +20531,11 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="H276" s="2" t="n">
-        <v>46133.40105324074</v>
+        <v>46127.66684027778</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -20391,7 +20544,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -20408,7 +20561,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Kaua Barros</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -20429,11 +20582,11 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="H277" s="2" t="n">
-        <v>46132.64863425926</v>
+        <v>46132.37733796296</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -20442,7 +20595,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -20459,36 +20612,36 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C278" t="n">
         <v>2026</v>
       </c>
       <c r="D278" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>46133.36008101852</v>
+        <v>46135.53177083333</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -20510,7 +20663,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -20531,11 +20684,11 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="H279" s="2" t="n">
-        <v>46133.38364583333</v>
+        <v>46132.64863425926</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -20544,7 +20697,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -20561,7 +20714,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -20582,11 +20735,11 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="H280" s="2" t="n">
-        <v>46133.40050925926</v>
+        <v>46133.36008101852</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -20595,7 +20748,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -20612,7 +20765,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -20633,11 +20786,11 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="H281" s="2" t="n">
-        <v>46132.54476851852</v>
+        <v>46133.38364583333</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -20646,7 +20799,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -20663,7 +20816,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -20684,11 +20837,11 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="H282" s="2" t="n">
-        <v>46132.64361111111</v>
+        <v>46133.40050925926</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -20697,7 +20850,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -20714,7 +20867,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -20735,11 +20888,11 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="H283" s="2" t="n">
-        <v>46133.36665509259</v>
+        <v>46132.54476851852</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -20748,7 +20901,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -20765,7 +20918,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -20786,11 +20939,11 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="H284" s="2" t="n">
-        <v>46133.44292824074</v>
+        <v>46133.36665509259</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -20799,7 +20952,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -20816,7 +20969,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -20837,7 +20990,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="H285" s="2" t="n">
@@ -20850,10 +21003,622 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D286" t="n">
+        <v>16</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>15279</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>46045.66640046296</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D287" t="n">
+        <v>16</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>15353</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>46105.60737268518</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D288" t="n">
+        <v>16</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>15394</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>46105.68079861111</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D289" t="n">
+        <v>16</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>15299</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>46127.63143518518</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D290" t="n">
+        <v>16</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>15228</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>46136.33554398148</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D291" t="n">
+        <v>16</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>15321</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>46133.61673611111</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D292" t="n">
+        <v>16</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>15306</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>46135.41539351852</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D293" t="n">
+        <v>16</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>15346</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>46136.48953703704</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D294" t="n">
+        <v>16</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>15298</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>46136.36600694444</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D295" t="n">
+        <v>16</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>15146</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="n">
+        <v>46136.61752314815</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D296" t="n">
+        <v>16</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>15360</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="n">
+        <v>46136.58333333334</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D297" t="n">
+        <v>16</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>46136.70833333334</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -6448,10 +6448,571 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D119" t="n">
+        <v>17</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>15398</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>46140.56631944444</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>15506</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>46140.70833333334</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Marcos Silva</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D121" t="n">
+        <v>17</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>15634</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>46141.58336805556</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D122" t="n">
+        <v>17</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>15776</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>46143.41532407407</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D123" t="n">
+        <v>17</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>15792</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>46143.46954861111</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D124" t="n">
+        <v>17</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>15795</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>46143.47502314814</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>15816</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>46143.56460648148</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>15837</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>46143.63870370371</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D127" t="n">
+        <v>17</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>15843</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>46143.65645833333</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D128" t="n">
+        <v>17</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>15852</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>46143.67925925926</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D129" t="n">
+        <v>17</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>15875</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>46146.34138888889</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -6468,7 +7029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K297"/>
+  <dimension ref="A1:K345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9246,16 +9807,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -9264,11 +9825,11 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46121.45960648148</v>
+        <v>46045.66640046296</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -17637,7 +18198,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -17688,7 +18249,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -19218,7 +19779,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -19269,7 +19830,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -19320,7 +19881,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -19473,7 +20034,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -19599,16 +20160,16 @@
         <v>2026</v>
       </c>
       <c r="D258" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19617,11 +20178,11 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>46139.33881944444</v>
+        <v>46122.69494212963</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -19803,16 +20364,16 @@
         <v>2026</v>
       </c>
       <c r="D262" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19821,11 +20382,11 @@
         </is>
       </c>
       <c r="H262" s="2" t="n">
-        <v>46127.35106481481</v>
+        <v>46128.62407407408</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -19854,16 +20415,16 @@
         <v>2026</v>
       </c>
       <c r="D263" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19872,11 +20433,11 @@
         </is>
       </c>
       <c r="H263" s="2" t="n">
-        <v>46128.69707175926</v>
+        <v>46127.35106481481</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -19932,7 +20493,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -20238,7 +20799,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -20612,23 +21173,23 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C278" t="n">
         <v>2026</v>
       </c>
       <c r="D278" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20637,11 +21198,11 @@
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>46135.53177083333</v>
+        <v>46128.67709490741</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -21054,7 +21615,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -21105,7 +21666,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -21156,7 +21717,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -21180,16 +21741,16 @@
         <v>2026</v>
       </c>
       <c r="D289" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21198,11 +21759,11 @@
         </is>
       </c>
       <c r="H289" s="2" t="n">
-        <v>46127.63143518518</v>
+        <v>46136.36600694444</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -21258,7 +21819,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -21309,7 +21870,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -21333,16 +21894,16 @@
         <v>2026</v>
       </c>
       <c r="D292" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21351,11 +21912,11 @@
         </is>
       </c>
       <c r="H292" s="2" t="n">
-        <v>46135.41539351852</v>
+        <v>46135.53177083333</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -21384,16 +21945,16 @@
         <v>2026</v>
       </c>
       <c r="D293" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21402,11 +21963,11 @@
         </is>
       </c>
       <c r="H293" s="2" t="n">
-        <v>46136.48953703704</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -21462,7 +22023,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -21479,23 +22040,23 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C295" t="n">
         <v>2026</v>
       </c>
       <c r="D295" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -21504,11 +22065,11 @@
         </is>
       </c>
       <c r="H295" s="2" t="n">
-        <v>46136.61752314815</v>
+        <v>46136.33554398148</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -21564,7 +22125,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -21615,10 +22176,2458 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D298" t="n">
+        <v>17</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>46140.62729166666</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D299" t="n">
+        <v>17</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>15393</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="n">
+        <v>46141.61875</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D300" t="n">
+        <v>17</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>15431</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D301" t="n">
+        <v>17</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>15451</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>46139.65947916666</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D302" t="n">
+        <v>17</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>15467</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>46140.54799768519</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D303" t="n">
+        <v>17</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>15485</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>46140.67614583333</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D304" t="n">
+        <v>17</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>15505</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>46140.70833333334</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D305" t="n">
+        <v>17</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>15561</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>46141.65</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D306" t="n">
+        <v>17</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>15620</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="n">
+        <v>46142.58518518518</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D307" t="n">
+        <v>17</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>15621</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>46142.37891203703</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D308" t="n">
+        <v>17</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>46141.70833333334</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D309" t="n">
+        <v>17</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>15629</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="n">
+        <v>46142.33395833334</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D310" t="n">
+        <v>17</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>15658</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="n">
+        <v>46142.4056712963</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D311" t="n">
+        <v>17</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>15666</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>46142.45151620371</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D312" t="n">
+        <v>17</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>15675</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>46143.59346064815</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D313" t="n">
+        <v>17</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>15689</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>46143.49875</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D314" t="n">
+        <v>17</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>15701</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>46142.5589699074</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D315" t="n">
+        <v>17</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>15709</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>46142.58479166667</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D316" t="n">
+        <v>17</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>15720</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>46142.70833333334</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D317" t="n">
+        <v>17</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>15733</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="n">
+        <v>46142.55833333333</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D318" t="n">
+        <v>17</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>15734</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>46142.6835300926</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D319" t="n">
+        <v>17</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>15736</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>46142.70052083334</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D320" t="n">
+        <v>17</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>15749</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>46142.70833333334</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D321" t="n">
+        <v>17</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>15758</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>46143.70833333334</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D322" t="n">
+        <v>17</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>15761</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>46146.33358796296</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D323" t="n">
+        <v>17</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>15793</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="n">
+        <v>46143.47351851852</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D324" t="n">
+        <v>17</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>15799</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>46143.48122685185</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D325" t="n">
+        <v>17</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>15804</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>46143.53856481481</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D326" t="n">
+        <v>17</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>15805</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>46143.54399305556</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D327" t="n">
+        <v>17</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>15811</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="n">
+        <v>46143.57472222222</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D328" t="n">
+        <v>17</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>15824</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>46143.59677083333</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D329" t="n">
+        <v>17</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>15828</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>46146.33333333334</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D330" t="n">
+        <v>17</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>15834</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>46142.6321875</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D331" t="n">
+        <v>17</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>15836</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>46143.6365625</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D332" t="n">
+        <v>17</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>15838</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>46143.6802662037</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D333" t="n">
+        <v>17</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>15841</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>46143.64694444444</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D334" t="n">
+        <v>17</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>15842</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>46141.35642361111</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D335" t="n">
+        <v>17</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>15844</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>46143.66479166667</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D336" t="n">
+        <v>17</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>15845</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>46143.54165509259</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D337" t="n">
+        <v>17</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>15889</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="n">
+        <v>46146.39172453704</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D338" t="n">
+        <v>17</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>15891</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>46146.39480324074</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Emerson Pellis</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D339" t="n">
+        <v>17</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>15901</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>46143.70009259259</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D340" t="n">
+        <v>17</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>15913</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>46143.48795138889</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D341" t="n">
+        <v>17</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>15916</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>46143.5303587963</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D342" t="n">
+        <v>17</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>15964</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>46143.70453703704</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D343" t="n">
+        <v>17</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>15994</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>46146.34652777778</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D344" t="n">
+        <v>17</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>16002</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>46146.37653935186</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D345" t="n">
+        <v>17</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>16055</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>46146.3334375</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -6523,16 +6523,16 @@
         <v>2026</v>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Elisandra Chaves</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6945,11 +6945,11 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>46143.67925925926</v>
+        <v>46146.34138888889</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6975,44 +6975,503 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elisandra Chaves</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>2026</v>
       </c>
       <c r="D129" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="H129" s="2" t="n">
-        <v>46146.34138888889</v>
+        <v>46150.35175925926</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D130" t="n">
+        <v>18</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>16267</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>46150.49650462963</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D131" t="n">
+        <v>18</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>16324</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>46150.70833333334</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D132" t="n">
+        <v>18</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>16334</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>46153.35800925926</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D133" t="n">
+        <v>18</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>16354</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>46153.44553240741</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D134" t="n">
+        <v>18</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>16010</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>46147.40179398148</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D135" t="n">
+        <v>18</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>16184</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>46149.65032407407</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D136" t="n">
+        <v>18</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>16277</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>46150.57346064815</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D137" t="n">
+        <v>18</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>16365</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>46153.53527777778</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D138" t="n">
+        <v>18</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>16133</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>46151.99998842592</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -7029,7 +7488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K345"/>
+  <dimension ref="A1:K361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9807,16 +10266,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -9829,7 +10288,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -20160,16 +20619,16 @@
         <v>2026</v>
       </c>
       <c r="D258" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -20178,11 +20637,11 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>46122.69494212963</v>
+        <v>46149.5</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -20382,7 +20841,7 @@
         </is>
       </c>
       <c r="H262" s="2" t="n">
-        <v>46128.62407407408</v>
+        <v>46142.37891203703</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -20391,7 +20850,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -20433,7 +20892,7 @@
         </is>
       </c>
       <c r="H263" s="2" t="n">
-        <v>46127.35106481481</v>
+        <v>46142.4056712963</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -20442,7 +20901,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21198,7 +21657,7 @@
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>46128.67709490741</v>
+        <v>46045.66640046296</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21207,7 +21666,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -21759,7 +22218,7 @@
         </is>
       </c>
       <c r="H289" s="2" t="n">
-        <v>46136.36600694444</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -21768,7 +22227,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -21912,7 +22371,7 @@
         </is>
       </c>
       <c r="H292" s="2" t="n">
-        <v>46135.53177083333</v>
+        <v>46143.54399305556</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -21921,7 +22380,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -21963,7 +22422,7 @@
         </is>
       </c>
       <c r="H293" s="2" t="n">
-        <v>46136.70833333334</v>
+        <v>46143.59677083333</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -21972,7 +22431,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -22065,7 +22524,7 @@
         </is>
       </c>
       <c r="H295" s="2" t="n">
-        <v>46136.33554398148</v>
+        <v>46122.69494212963</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -22074,7 +22533,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -22218,7 +22677,7 @@
         </is>
       </c>
       <c r="H298" s="2" t="n">
-        <v>46140.62729166666</v>
+        <v>46127.35106481481</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -22227,7 +22686,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -22244,7 +22703,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -22265,11 +22724,11 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="H299" s="2" t="n">
-        <v>46141.61875</v>
+        <v>46128.67709490741</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -22278,7 +22737,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -22295,7 +22754,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -22316,11 +22775,11 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="H300" s="2" t="n">
-        <v>46139.58333333334</v>
+        <v>46128.62407407408</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -22329,7 +22788,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -22367,11 +22826,11 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="H301" s="2" t="n">
-        <v>46139.65947916666</v>
+        <v>46136.33554398148</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -22380,7 +22839,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -22397,7 +22856,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -22418,11 +22877,11 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="H302" s="2" t="n">
-        <v>46140.54799768519</v>
+        <v>46140.62729166666</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -22431,7 +22890,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -22469,11 +22928,11 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="H303" s="2" t="n">
-        <v>46140.67614583333</v>
+        <v>46136.36600694444</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -22482,7 +22941,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -22499,7 +22958,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -22520,11 +22979,11 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="H304" s="2" t="n">
-        <v>46140.70833333334</v>
+        <v>46135.53177083333</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -22533,7 +22992,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -22550,7 +23009,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -22571,11 +23030,11 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="H305" s="2" t="n">
-        <v>46141.65</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -22584,7 +23043,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -22601,7 +23060,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -22622,11 +23081,11 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="H306" s="2" t="n">
-        <v>46142.58518518518</v>
+        <v>46141.61875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -22635,7 +23094,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -22652,7 +23111,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -22673,11 +23132,11 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="H307" s="2" t="n">
-        <v>46142.37891203703</v>
+        <v>46139.58333333334</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -22686,7 +23145,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -22703,7 +23162,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -22724,11 +23183,11 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="H308" s="2" t="n">
-        <v>46141.70833333334</v>
+        <v>46139.65947916666</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -22737,7 +23196,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -22754,7 +23213,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -22775,11 +23234,11 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="H309" s="2" t="n">
-        <v>46142.33395833334</v>
+        <v>46140.54799768519</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -22788,7 +23247,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -22805,7 +23264,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -22826,11 +23285,11 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="H310" s="2" t="n">
-        <v>46142.4056712963</v>
+        <v>46140.67614583333</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -22839,7 +23298,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -22877,11 +23336,11 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="H311" s="2" t="n">
-        <v>46142.45151620371</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -22890,7 +23349,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -22907,36 +23366,36 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C312" t="n">
         <v>2026</v>
       </c>
       <c r="D312" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="H312" s="2" t="n">
-        <v>46143.59346064815</v>
+        <v>46122.69494212963</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -22958,7 +23417,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Emerson Pellis</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -22979,11 +23438,11 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="H313" s="2" t="n">
-        <v>46143.49875</v>
+        <v>46142.33395833334</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -22992,7 +23451,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -23009,41 +23468,41 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C314" t="n">
         <v>2026</v>
       </c>
       <c r="D314" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="H314" s="2" t="n">
-        <v>46142.5589699074</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -23081,11 +23540,11 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="H315" s="2" t="n">
-        <v>46142.58479166667</v>
+        <v>46142.45151620371</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -23094,7 +23553,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -23111,7 +23570,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -23132,11 +23591,11 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="H316" s="2" t="n">
-        <v>46142.70833333334</v>
+        <v>46143.59346064815</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -23145,7 +23604,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -23162,7 +23621,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -23183,11 +23642,11 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="H317" s="2" t="n">
-        <v>46142.55833333333</v>
+        <v>46143.49875</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -23196,7 +23655,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -23213,7 +23672,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -23234,11 +23693,11 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="H318" s="2" t="n">
-        <v>46142.6835300926</v>
+        <v>46142.5589699074</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -23247,7 +23706,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -23264,7 +23723,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -23285,11 +23744,11 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="H319" s="2" t="n">
-        <v>46142.70052083334</v>
+        <v>46142.58479166667</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -23298,7 +23757,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -23315,7 +23774,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -23336,7 +23795,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="H320" s="2" t="n">
@@ -23349,7 +23808,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -23387,11 +23846,11 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="H321" s="2" t="n">
-        <v>46143.70833333334</v>
+        <v>46142.55833333333</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -23400,7 +23859,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -23438,11 +23897,11 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="H322" s="2" t="n">
-        <v>46146.33358796296</v>
+        <v>46142.6835300926</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -23451,7 +23910,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -23468,7 +23927,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -23489,11 +23948,11 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="H323" s="2" t="n">
-        <v>46143.47351851852</v>
+        <v>46142.70052083334</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -23502,7 +23961,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -23519,7 +23978,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -23540,11 +23999,11 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="H324" s="2" t="n">
-        <v>46143.48122685185</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -23553,7 +24012,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -23570,7 +24029,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -23591,11 +24050,11 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="H325" s="2" t="n">
-        <v>46143.53856481481</v>
+        <v>46143.70833333334</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -23604,7 +24063,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -23621,7 +24080,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -23642,11 +24101,11 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="H326" s="2" t="n">
-        <v>46143.54399305556</v>
+        <v>46146.33358796296</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -23655,7 +24114,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -23672,7 +24131,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -23693,11 +24152,11 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="H327" s="2" t="n">
-        <v>46143.57472222222</v>
+        <v>46143.47351851852</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -23706,7 +24165,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -23723,7 +24182,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -23744,11 +24203,11 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>15824</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="H328" s="2" t="n">
-        <v>46143.59677083333</v>
+        <v>46143.48122685185</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -23757,7 +24216,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -23774,7 +24233,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -23795,11 +24254,11 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="H329" s="2" t="n">
-        <v>46146.33333333334</v>
+        <v>46143.53856481481</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -23808,7 +24267,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -23825,41 +24284,41 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C330" t="n">
         <v>2026</v>
       </c>
       <c r="D330" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="H330" s="2" t="n">
-        <v>46142.6321875</v>
+        <v>46149.68517361111</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -23876,7 +24335,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -23897,11 +24356,11 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="H331" s="2" t="n">
-        <v>46143.6365625</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -23910,7 +24369,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -23927,7 +24386,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -23948,11 +24407,11 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="H332" s="2" t="n">
-        <v>46143.6802662037</v>
+        <v>46142.6321875</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -23961,7 +24420,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -23978,7 +24437,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -23999,11 +24458,11 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="H333" s="2" t="n">
-        <v>46143.64694444444</v>
+        <v>46143.6365625</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -24012,7 +24471,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -24029,7 +24488,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -24050,11 +24509,11 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="H334" s="2" t="n">
-        <v>46141.35642361111</v>
+        <v>46143.6802662037</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -24063,7 +24522,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -24080,7 +24539,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -24101,11 +24560,11 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="H335" s="2" t="n">
-        <v>46143.66479166667</v>
+        <v>46143.64694444444</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -24114,7 +24573,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -24131,7 +24590,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -24152,11 +24611,11 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="H336" s="2" t="n">
-        <v>46143.54165509259</v>
+        <v>46141.35642361111</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -24165,7 +24624,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -24182,7 +24641,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -24203,11 +24662,11 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="H337" s="2" t="n">
-        <v>46146.39172453704</v>
+        <v>46143.66479166667</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -24216,7 +24675,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -24233,7 +24692,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -24254,11 +24713,11 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="H338" s="2" t="n">
-        <v>46146.39480324074</v>
+        <v>46143.54165509259</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -24267,7 +24726,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -24284,7 +24743,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Emerson Pellis</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -24305,11 +24764,11 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="H339" s="2" t="n">
-        <v>46143.70009259259</v>
+        <v>46146.39172453704</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -24318,7 +24777,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -24335,7 +24794,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -24356,11 +24815,11 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="H340" s="2" t="n">
-        <v>46143.48795138889</v>
+        <v>46146.39480324074</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -24369,7 +24828,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -24386,7 +24845,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -24407,11 +24866,11 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="H341" s="2" t="n">
-        <v>46143.5303587963</v>
+        <v>46143.48795138889</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -24420,7 +24879,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -24437,7 +24896,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -24458,11 +24917,11 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="H342" s="2" t="n">
-        <v>46143.70453703704</v>
+        <v>46143.5303587963</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -24471,7 +24930,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -24509,11 +24968,11 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="H343" s="2" t="n">
-        <v>46146.34652777778</v>
+        <v>46143.70453703704</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -24522,7 +24981,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -24539,7 +24998,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -24560,11 +25019,11 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="H344" s="2" t="n">
-        <v>46146.37653935186</v>
+        <v>46146.34652777778</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -24573,7 +25032,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -24611,23 +25070,839 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
+          <t>15994</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>46146.37653935186</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D346" t="n">
+        <v>17</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
           <t>16055</t>
         </is>
       </c>
-      <c r="H345" s="2" t="n">
+      <c r="H346" s="2" t="n">
         <v>46146.3334375</v>
       </c>
-      <c r="I345" t="inlineStr">
+      <c r="I346" t="inlineStr">
         <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="J345" t="inlineStr">
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D347" t="n">
+        <v>18</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>16366</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D348" t="n">
+        <v>18</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>15914</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="n">
+        <v>46143.67925925926</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D349" t="n">
+        <v>18</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>16051</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>46153.51006944444</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D350" t="n">
+        <v>18</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>46151.99998842592</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D351" t="n">
+        <v>18</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>16158</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="n">
+        <v>46147.58333333334</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D352" t="n">
+        <v>18</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>16183</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="n">
+        <v>46151.99998842592</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D353" t="n">
+        <v>18</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>46149.3475462963</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D354" t="n">
+        <v>18</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>16270</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>46151.99998842592</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D355" t="n">
+        <v>18</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>16329</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="n">
+        <v>46150.99998842592</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D356" t="n">
+        <v>18</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>16048</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>46149.52372685185</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D357" t="n">
+        <v>18</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>16351</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>46150.37532407408</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D358" t="n">
+        <v>18</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>16246</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>46150.5165162037</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D359" t="n">
+        <v>18</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>16046</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>46153.33694444445</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D360" t="n">
+        <v>18</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>15911</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>46150.6764699074</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D361" t="n">
+        <v>18</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>16421</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>46153.53671296296</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6523,16 +6523,16 @@
         <v>2026</v>
       </c>
       <c r="D120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7084,16 +7084,16 @@
         <v>2026</v>
       </c>
       <c r="D131" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7468,10 +7468,1030 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D139" t="n">
+        <v>19</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>16480</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>46150.45435185185</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D140" t="n">
+        <v>19</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>16631</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>46156.36233796296</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D141" t="n">
+        <v>19</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>16636</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>46158.99998842592</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D142" t="n">
+        <v>19</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>16643</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>46158.99998842592</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D143" t="n">
+        <v>19</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>16671</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>46158.99998842592</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D144" t="n">
+        <v>19</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>16755</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>46157.33951388889</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D145" t="n">
+        <v>19</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>16758</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>46157.35835648148</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D146" t="n">
+        <v>19</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>16762</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>46157.36909722222</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D147" t="n">
+        <v>19</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>16793</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>46157.488125</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D148" t="n">
+        <v>19</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>16814</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>46157.63480324074</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D149" t="n">
+        <v>19</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>16821</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>46157.64824074074</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D150" t="n">
+        <v>19</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>16824</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>46157.66125</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D151" t="n">
+        <v>19</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>16832</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>46156.69478009259</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D152" t="n">
+        <v>19</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>16835</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>46157.70833333334</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D153" t="n">
+        <v>19</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>16853</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>46160.37273148148</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D154" t="n">
+        <v>19</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>16706</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>46156.64516203704</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D155" t="n">
+        <v>19</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>16506</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>46155.33430555555</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D156" t="n">
+        <v>19</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>16660</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>46156.48416666667</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D157" t="n">
+        <v>19</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>16699</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>46156.62493055555</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D158" t="n">
+        <v>19</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>16722</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>46156.69226851852</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -7488,7 +8508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K361"/>
+  <dimension ref="A1:K378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10266,16 +11286,16 @@
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -10288,7 +11308,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -20646,7 +21666,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -23400,7 +24420,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25770,16 +26790,16 @@
         <v>2026</v>
       </c>
       <c r="D359" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -25788,11 +26808,11 @@
         </is>
       </c>
       <c r="H359" s="2" t="n">
-        <v>46153.33694444445</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -25903,6 +26923,873 @@
         </is>
       </c>
       <c r="K361" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D362" t="n">
+        <v>19</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>16398</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="n">
+        <v>46151.99998842592</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D363" t="n">
+        <v>19</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>16525</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>46153.5590162037</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D364" t="n">
+        <v>19</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>16684</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>46155.42356481482</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D365" t="n">
+        <v>19</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>16704</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>46157.66753472222</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D366" t="n">
+        <v>19</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>16852</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="n">
+        <v>46156.63346064815</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D367" t="n">
+        <v>19</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>16856</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>46156.6994212963</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D368" t="n">
+        <v>19</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>16872</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="n">
+        <v>46156.57993055556</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D369" t="n">
+        <v>19</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>16884</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="n">
+        <v>46157.35186342592</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D370" t="n">
+        <v>19</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>16789</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="n">
+        <v>46157.5919212963</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D371" t="n">
+        <v>19</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>16988</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>46156.56027777777</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D372" t="n">
+        <v>19</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>16823</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>46157.53070601852</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D373" t="n">
+        <v>19</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>16836</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>46160.3703125</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D374" t="n">
+        <v>19</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>16791</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>46160.37774305556</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D375" t="n">
+        <v>19</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>16728</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>46160.42920138889</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D376" t="n">
+        <v>19</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>16800</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="n">
+        <v>46160.48353009259</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D377" t="n">
+        <v>19</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>16726</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>46160.52505787037</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D378" t="n">
+        <v>19</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>17050</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>46160.33336805556</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -7111,7 +7111,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -26817,7 +26817,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -27072,7 +27072,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
@@ -27327,7 +27327,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -27582,7 +27582,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7434,23 +7434,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Luan Nicocelli</t>
+          <t>Gabriel Coelho</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>2026</v>
       </c>
       <c r="D138" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -7459,16 +7459,16 @@
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>46151.99998842592</v>
+        <v>46163.99930555555</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8308,16 +8308,16 @@
         <v>2026</v>
       </c>
       <c r="D155" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -8492,6 +8492,1740 @@
         </is>
       </c>
       <c r="K158" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D159" t="n">
+        <v>20</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>17101</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>46162.65229166667</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D160" t="n">
+        <v>20</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>16956</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>46161.37039351852</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D161" t="n">
+        <v>20</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>17053</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>46162.38668981481</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D162" t="n">
+        <v>22</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>17252</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>46163.70833333334</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D163" t="n">
+        <v>20</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>17293</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>46164.46084490741</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D164" t="n">
+        <v>20</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>17298</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>46164.35240740741</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D165" t="n">
+        <v>21</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>17178</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>46163.38953703704</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D166" t="n">
+        <v>21</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>17457</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>46168.35542824074</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D167" t="n">
+        <v>22</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>17608</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>46169.55157407407</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D168" t="n">
+        <v>21</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>17615</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>46168.59733796296</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D169" t="n">
+        <v>22</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>17749</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>46171.70833333334</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D170" t="n">
+        <v>21</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>17785</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>46174.34743055556</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D171" t="n">
+        <v>21</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>17808</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>46174.44751157407</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D172" t="n">
+        <v>22</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>18116</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>46176.62567129629</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D173" t="n">
+        <v>22</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>18205</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>46177.4203125</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D174" t="n">
+        <v>22</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>18212</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>46177.44097222222</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Clanderson Oliveira</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D175" t="n">
+        <v>22</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>17840</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>46174.65693287037</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D176" t="n">
+        <v>22</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>18346</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>46178.53854166667</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D177" t="n">
+        <v>22</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>18276</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>46177.70833333334</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D178" t="n">
+        <v>22</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>18451</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>46181.44583333333</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D179" t="n">
+        <v>22</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>17076</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>46174.69118055556</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D180" t="n">
+        <v>22</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>46175.34121527777</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D181" t="n">
+        <v>22</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>17997</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D182" t="n">
+        <v>22</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>18006</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D183" t="n">
+        <v>22</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>18176</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>46177.33506944445</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D184" t="n">
+        <v>22</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>46177.70833333334</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D185" t="n">
+        <v>22</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>18333</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>46178.44940972222</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D186" t="n">
+        <v>22</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>18339</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>46178.45815972222</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D187" t="n">
+        <v>22</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>18385</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>46177.66613425926</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D188" t="n">
+        <v>22</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>18403</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>46178.70833333334</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D189" t="n">
+        <v>22</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>18434</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>46181.36931712963</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D190" t="n">
+        <v>22</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>18450</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>46181.44561342592</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D191" t="n">
+        <v>22</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>18460</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>46181.50734953704</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Luan Nicocelli</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D192" t="n">
+        <v>22</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>18407</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>46178.49583333333</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -8508,7 +10242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K378"/>
+  <dimension ref="A1:K441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11313,7 +13047,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -24393,16 +26127,16 @@
         <v>2026</v>
       </c>
       <c r="D312" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -24411,11 +26145,11 @@
         </is>
       </c>
       <c r="H312" s="2" t="n">
-        <v>46122.69494212963</v>
+        <v>46139.58333333334</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -26943,16 +28677,16 @@
         <v>2026</v>
       </c>
       <c r="D362" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -26961,16 +28695,16 @@
         </is>
       </c>
       <c r="H362" s="2" t="n">
-        <v>46151.99998842592</v>
+        <v>46153.5590162037</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -27123,7 +28857,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -27198,16 +28932,16 @@
         <v>2026</v>
       </c>
       <c r="D367" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -27216,16 +28950,16 @@
         </is>
       </c>
       <c r="H367" s="2" t="n">
-        <v>46156.6994212963</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -27480,7 +29214,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -27504,16 +29238,16 @@
         <v>2026</v>
       </c>
       <c r="D373" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -27522,16 +29256,16 @@
         </is>
       </c>
       <c r="H373" s="2" t="n">
-        <v>46160.3703125</v>
+        <v>46164.63939814815</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -27684,7 +29418,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -27790,6 +29524,3219 @@
         </is>
       </c>
       <c r="K378" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D379" t="n">
+        <v>22</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>17306</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="n">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D380" t="n">
+        <v>21</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>46163.45768518518</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D381" t="n">
+        <v>20</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>17287</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>46160.70833333334</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D382" t="n">
+        <v>20</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>17426</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>46165.99998842592</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D383" t="n">
+        <v>20</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>17672</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>46162.69203703704</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D384" t="n">
+        <v>22</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>17195</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>46181.42672453704</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D385" t="n">
+        <v>20</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>17352</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>46161.66633101852</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D386" t="n">
+        <v>20</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>17371</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>46161.70833333334</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D387" t="n">
+        <v>20</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>16931</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="n">
+        <v>46163.40166666666</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D388" t="n">
+        <v>20</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>17178</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>46163.3453125</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D389" t="n">
+        <v>20</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>17308</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>46162.62407407408</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D390" t="n">
+        <v>20</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>17363</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>46163.38953703704</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D391" t="n">
+        <v>20</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>17127</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>46165.99998842592</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D392" t="n">
+        <v>20</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>17423</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>46163.45768518518</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D393" t="n">
+        <v>20</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>16746</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>46162.64236111111</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D394" t="n">
+        <v>20</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>16933</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>46164.44891203703</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D395" t="n">
+        <v>20</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>17046</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>46164.42878472222</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D396" t="n">
+        <v>20</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>17060</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>46164.56079861111</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D397" t="n">
+        <v>20</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>17175</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>46164.58333333334</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D398" t="n">
+        <v>20</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>17190</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>46164.70833333334</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D399" t="n">
+        <v>20</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>17234</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="n">
+        <v>46164.58333333334</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D400" t="n">
+        <v>22</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>17160</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>46178.66927083334</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D401" t="n">
+        <v>22</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>16947</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>46181.41347222222</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D402" t="n">
+        <v>21</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>17153</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>46163.40166666666</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D403" t="n">
+        <v>22</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>46177.33384259259</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D404" t="n">
+        <v>22</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>17382</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>46179.99998842592</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D405" t="n">
+        <v>21</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>17590</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>46169.42894675926</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D406" t="n">
+        <v>21</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>17622</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>46169.6337037037</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D407" t="n">
+        <v>21</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>17677</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="n">
+        <v>46171.3628125</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D408" t="n">
+        <v>21</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>17708</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="n">
+        <v>46174.37847222222</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D409" t="n">
+        <v>22</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>17794</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>46177.37328703704</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D410" t="n">
+        <v>21</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>18068</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="n">
+        <v>46174.35002314814</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D411" t="n">
+        <v>22</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>18299</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>46167.70700231481</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D412" t="n">
+        <v>22</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>18302</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>46162.69203703704</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D413" t="n">
+        <v>22</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>18345</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>46163.3453125</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D414" t="n">
+        <v>22</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>46165.99998842592</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D415" t="n">
+        <v>22</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>18382</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>46164.42878472222</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D416" t="n">
+        <v>22</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>18348</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>46175.54391203704</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D417" t="n">
+        <v>22</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>17481</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>46179.99998842592</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D418" t="n">
+        <v>22</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>17927</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="n">
+        <v>46171.3843287037</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D419" t="n">
+        <v>22</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>18186</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>46175.50818287037</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D420" t="n">
+        <v>22</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>18326</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="n">
+        <v>46177.47008101852</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D421" t="n">
+        <v>22</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>18367</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>46174.68819444445</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D422" t="n">
+        <v>22</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>18430</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="n">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D423" t="n">
+        <v>22</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>18184</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>46174.41666666666</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D424" t="n">
+        <v>22</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>18482</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>46176.61097222222</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D425" t="n">
+        <v>22</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>18443</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>46178.365625</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D426" t="n">
+        <v>22</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>18217</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>46176.45597222223</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D427" t="n">
+        <v>22</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>18281</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>46178.65739583333</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D428" t="n">
+        <v>22</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>17926</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>46177.58333333334</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D429" t="n">
+        <v>22</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>17950</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>46177.58333333334</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D430" t="n">
+        <v>22</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>18089</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>46177.58939814815</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D431" t="n">
+        <v>22</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>18140</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>46178.44984953704</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D432" t="n">
+        <v>22</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>18167</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>46178.49792824074</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D433" t="n">
+        <v>22</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>18257</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="n">
+        <v>46181.55126157407</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D434" t="n">
+        <v>22</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>18292</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>46178.49097222222</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D435" t="n">
+        <v>22</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>18472</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>46178.66917824074</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D436" t="n">
+        <v>22</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>17640</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>46178.70833333334</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D437" t="n">
+        <v>22</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>17940</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>46181.35356481482</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D438" t="n">
+        <v>22</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>18442</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="n">
+        <v>46181.40673611111</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D439" t="n">
+        <v>22</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>18188</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>46181.44445601852</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D440" t="n">
+        <v>22</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>18409</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>46181.48393518518</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D441" t="n">
+        <v>22</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>18490</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="n">
+        <v>46178.64079861111</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K192"/>
+  <dimension ref="A1:K210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8665,16 +8665,16 @@
         <v>2026</v>
       </c>
       <c r="D162" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -9379,16 +9379,16 @@
         <v>2026</v>
       </c>
       <c r="D176" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -9430,16 +9430,16 @@
         <v>2026</v>
       </c>
       <c r="D177" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -9627,23 +9627,23 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>2026</v>
       </c>
       <c r="D181" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -9685,16 +9685,16 @@
         <v>2026</v>
       </c>
       <c r="D182" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -9838,16 +9838,16 @@
         <v>2026</v>
       </c>
       <c r="D185" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -9940,16 +9940,16 @@
         <v>2026</v>
       </c>
       <c r="D187" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -9991,16 +9991,16 @@
         <v>2026</v>
       </c>
       <c r="D188" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10042,16 +10042,16 @@
         <v>2026</v>
       </c>
       <c r="D189" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10093,16 +10093,16 @@
         <v>2026</v>
       </c>
       <c r="D190" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10144,16 +10144,16 @@
         <v>2026</v>
       </c>
       <c r="D191" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10222,10 +10222,928 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D193" t="n">
+        <v>23</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>18829</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>46188.42400462963</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D194" t="n">
+        <v>23</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>16819</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>46157.64317129629</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D195" t="n">
+        <v>23</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>18418</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>46178.70833333334</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D196" t="n">
+        <v>23</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>18653</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>46184.5436574074</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D197" t="n">
+        <v>23</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>18665</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>46184.61206018519</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D198" t="n">
+        <v>23</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>18730</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>46185.40383101852</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D199" t="n">
+        <v>23</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>18485</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>46181.62840277778</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D200" t="n">
+        <v>23</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>18593</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>46184.33337962963</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D201" t="n">
+        <v>23</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>18489</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>46181.64040509259</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D202" t="n">
+        <v>23</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>18501</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>46181.68621527778</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D203" t="n">
+        <v>23</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>18664</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>46184.61175925926</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D204" t="n">
+        <v>23</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>18749</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>46185.49927083333</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D205" t="n">
+        <v>23</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>18754</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>46185.55496527778</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D206" t="n">
+        <v>23</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>18775</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>46184.67892361111</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D207" t="n">
+        <v>23</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>18780</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>46185.69163194444</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D208" t="n">
+        <v>23</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>18783</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>46185.70833333334</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Kleberson Matias</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D209" t="n">
+        <v>23</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>17965</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>46182.99998842592</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Mara Neves</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D210" t="n">
+        <v>23</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>18885</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>46188.58333333334</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -10242,7 +11160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K441"/>
+  <dimension ref="A1:K458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29544,7 +30462,7 @@
         <v>2026</v>
       </c>
       <c r="D379" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -29562,11 +30480,11 @@
         </is>
       </c>
       <c r="H379" s="2" t="n">
-        <v>46167.70833333334</v>
+        <v>46164.42878472222</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -29799,7 +30717,7 @@
         <v>2026</v>
       </c>
       <c r="D384" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -29817,11 +30735,11 @@
         </is>
       </c>
       <c r="H384" s="2" t="n">
-        <v>46181.42672453704</v>
+        <v>46165.99998842592</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -30564,16 +31482,16 @@
         <v>2026</v>
       </c>
       <c r="D399" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -30582,16 +31500,16 @@
         </is>
       </c>
       <c r="H399" s="2" t="n">
-        <v>46164.58333333334</v>
+        <v>46162.64236111111</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -30642,7 +31560,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -30666,7 +31584,7 @@
         <v>2026</v>
       </c>
       <c r="D401" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -30684,16 +31602,16 @@
         </is>
       </c>
       <c r="H401" s="2" t="n">
-        <v>46181.41347222222</v>
+        <v>46162.69203703704</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -30795,7 +31713,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -30819,7 +31737,7 @@
         <v>2026</v>
       </c>
       <c r="D404" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -30837,11 +31755,11 @@
         </is>
       </c>
       <c r="H404" s="2" t="n">
-        <v>46179.99998842592</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -31074,7 +31992,7 @@
         <v>2026</v>
       </c>
       <c r="D409" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -31092,16 +32010,16 @@
         </is>
       </c>
       <c r="H409" s="2" t="n">
-        <v>46177.37328703704</v>
+        <v>46171.3843287037</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -31203,7 +32121,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -31254,7 +32172,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -31305,7 +32223,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -31356,7 +32274,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -31407,7 +32325,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -31458,7 +32376,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -31509,7 +32427,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -31560,7 +32478,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -31611,7 +32529,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -31662,7 +32580,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -31713,7 +32631,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -31764,7 +32682,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -31815,7 +32733,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -31866,7 +32784,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -31917,7 +32835,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -31968,7 +32886,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -32019,7 +32937,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -32070,7 +32988,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -32121,7 +33039,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -32172,7 +33090,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -32223,7 +33141,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -32274,7 +33192,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -32325,7 +33243,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -32376,7 +33294,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -32427,7 +33345,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -32451,7 +33369,7 @@
         <v>2026</v>
       </c>
       <c r="D436" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -32469,11 +33387,11 @@
         </is>
       </c>
       <c r="H436" s="2" t="n">
-        <v>46178.70833333334</v>
+        <v>46179.99998842592</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -32529,7 +33447,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -32580,7 +33498,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -32604,7 +33522,7 @@
         <v>2026</v>
       </c>
       <c r="D439" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -32622,11 +33540,11 @@
         </is>
       </c>
       <c r="H439" s="2" t="n">
-        <v>46181.44445601852</v>
+        <v>46177.37328703704</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -32682,7 +33600,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -32706,7 +33624,7 @@
         <v>2026</v>
       </c>
       <c r="D441" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -32728,15 +33646,882 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D442" t="n">
+        <v>23</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="J441" t="inlineStr">
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>18738</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="n">
+        <v>46184.68549768518</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D443" t="n">
+        <v>23</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>18844</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="n">
+        <v>46188.53701388889</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D444" t="n">
+        <v>23</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>18848</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="n">
+        <v>46188.54712962963</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D445" t="n">
+        <v>23</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>18626</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="n">
+        <v>46184.44909722222</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr">
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D446" t="n">
+        <v>23</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>18649</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="n">
+        <v>46184.4005787037</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D447" t="n">
+        <v>23</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>18731</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="n">
+        <v>46185.40510416667</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D448" t="n">
+        <v>23</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>18828</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="n">
+        <v>46188.42299768519</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D449" t="n">
+        <v>23</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>18544</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="n">
+        <v>46183.39971064815</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D450" t="n">
+        <v>23</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>18561</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="n">
+        <v>46183.69546296296</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D451" t="n">
+        <v>23</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>18742</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="n">
+        <v>46184.69770833333</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D452" t="n">
+        <v>23</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>18743</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="n">
+        <v>46188.4491087963</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D453" t="n">
+        <v>23</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>18789</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="n">
+        <v>46188.35795138889</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D454" t="n">
+        <v>23</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>18824</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="n">
+        <v>46185.64020833333</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D455" t="n">
+        <v>23</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>16128</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="n">
+        <v>46149.41342592592</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D456" t="n">
+        <v>23</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>18506</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="n">
+        <v>46183.70833333334</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D457" t="n">
+        <v>23</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>18650</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="n">
+        <v>46184.5280787037</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D458" t="n">
+        <v>23</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>18982</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="n">
+        <v>46188.33335648148</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K210"/>
+  <dimension ref="A1:K217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8665,16 +8665,16 @@
         <v>2026</v>
       </c>
       <c r="D162" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9379,16 +9379,16 @@
         <v>2026</v>
       </c>
       <c r="D176" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -9430,16 +9430,16 @@
         <v>2026</v>
       </c>
       <c r="D177" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -9685,16 +9685,16 @@
         <v>2026</v>
       </c>
       <c r="D182" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -9838,16 +9838,16 @@
         <v>2026</v>
       </c>
       <c r="D185" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -9940,16 +9940,16 @@
         <v>2026</v>
       </c>
       <c r="D187" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -9991,16 +9991,16 @@
         <v>2026</v>
       </c>
       <c r="D188" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10042,16 +10042,16 @@
         <v>2026</v>
       </c>
       <c r="D189" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10093,16 +10093,16 @@
         <v>2026</v>
       </c>
       <c r="D190" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10144,16 +10144,16 @@
         <v>2026</v>
       </c>
       <c r="D191" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10297,16 +10297,16 @@
         <v>2026</v>
       </c>
       <c r="D194" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -10348,16 +10348,16 @@
         <v>2026</v>
       </c>
       <c r="D195" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -10552,16 +10552,16 @@
         <v>2026</v>
       </c>
       <c r="D199" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -10603,16 +10603,16 @@
         <v>2026</v>
       </c>
       <c r="D200" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -10654,16 +10654,16 @@
         <v>2026</v>
       </c>
       <c r="D201" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -10705,16 +10705,16 @@
         <v>2026</v>
       </c>
       <c r="D202" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -10756,16 +10756,16 @@
         <v>2026</v>
       </c>
       <c r="D203" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -10807,16 +10807,16 @@
         <v>2026</v>
       </c>
       <c r="D204" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -10858,16 +10858,16 @@
         <v>2026</v>
       </c>
       <c r="D205" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -10909,16 +10909,16 @@
         <v>2026</v>
       </c>
       <c r="D206" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -10960,16 +10960,16 @@
         <v>2026</v>
       </c>
       <c r="D207" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11011,16 +11011,16 @@
         <v>2026</v>
       </c>
       <c r="D208" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11144,6 +11144,363 @@
         </is>
       </c>
       <c r="K210" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D211" t="n">
+        <v>24</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>19299</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>46195.58340277777</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D212" t="n">
+        <v>24</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>19080</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>46191.33334490741</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D213" t="n">
+        <v>24</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>18897</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>46189.37665509259</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D214" t="n">
+        <v>24</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>18911</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>46189.44861111111</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D215" t="n">
+        <v>24</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>18942</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>46189.61232638889</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D216" t="n">
+        <v>24</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>19032</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>46190.68834490741</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D217" t="n">
+        <v>24</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>18994</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>46189.69623842592</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11160,7 +11517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K458"/>
+  <dimension ref="A1:K479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30462,16 +30819,16 @@
         <v>2026</v>
       </c>
       <c r="D379" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -30484,7 +30841,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -30717,16 +31074,16 @@
         <v>2026</v>
       </c>
       <c r="D384" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -30739,7 +31096,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -31482,16 +31839,16 @@
         <v>2026</v>
       </c>
       <c r="D399" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -31504,7 +31861,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -31737,16 +32094,16 @@
         <v>2026</v>
       </c>
       <c r="D404" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -31759,7 +32116,7 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -33369,16 +33726,16 @@
         <v>2026</v>
       </c>
       <c r="D436" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -33391,7 +33748,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -33522,16 +33879,16 @@
         <v>2026</v>
       </c>
       <c r="D439" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -33544,7 +33901,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -33617,23 +33974,23 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C441" t="n">
         <v>2026</v>
       </c>
       <c r="D441" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -33646,7 +34003,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -33828,16 +34185,16 @@
         <v>2026</v>
       </c>
       <c r="D445" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -33850,7 +34207,7 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -33879,16 +34236,16 @@
         <v>2026</v>
       </c>
       <c r="D446" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -33901,7 +34258,7 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -33957,7 +34314,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -34008,7 +34365,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -34059,7 +34416,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
@@ -34416,7 +34773,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
@@ -34440,16 +34797,16 @@
         <v>2026</v>
       </c>
       <c r="D457" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -34462,7 +34819,7 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -34522,6 +34879,1077 @@
         </is>
       </c>
       <c r="K458" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D459" t="n">
+        <v>24</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="n">
+        <v>46190.58333333334</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D460" t="n">
+        <v>24</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>19203</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="n">
+        <v>46192.57590277777</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D461" t="n">
+        <v>24</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>19213</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="n">
+        <v>46192.70833333334</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D462" t="n">
+        <v>24</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>19214</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="n">
+        <v>46192.70833333334</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D463" t="n">
+        <v>24</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>19236</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="n">
+        <v>46195.36821759259</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D464" t="n">
+        <v>24</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>19237</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="n">
+        <v>46195.33435185185</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D465" t="n">
+        <v>24</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>19266</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="n">
+        <v>46192.65648148148</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D466" t="n">
+        <v>24</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>19281</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="n">
+        <v>46195.57657407408</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D467" t="n">
+        <v>24</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>19205</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="n">
+        <v>46192.35711805556</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D468" t="n">
+        <v>24</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>19254</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="n">
+        <v>46192.35331018519</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D469" t="n">
+        <v>24</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>19293</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="n">
+        <v>46195.53289351852</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D470" t="n">
+        <v>24</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>19386</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="n">
+        <v>46195.5577662037</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D471" t="n">
+        <v>24</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>19131</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="n">
+        <v>46192.38016203704</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D472" t="n">
+        <v>24</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>19195</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="n">
+        <v>46192.5730787037</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D473" t="n">
+        <v>24</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>19090</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="n">
+        <v>46190.35675925926</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D474" t="n">
+        <v>24</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>19234</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="n">
+        <v>46191.69305555556</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D475" t="n">
+        <v>24</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>19211</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="n">
+        <v>46191.55715277778</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D476" t="n">
+        <v>24</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>19093</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="n">
+        <v>46191.3712037037</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D477" t="n">
+        <v>24</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>18927</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="n">
+        <v>46189.45256944445</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D478" t="n">
+        <v>24</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>19235</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="n">
+        <v>46192.69414351852</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D479" t="n">
+        <v>24</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>19257</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="n">
+        <v>46195.36251157407</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K217"/>
+  <dimension ref="A1:K216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Fabio Silva</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Fabio Silva</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -11178,11 +11178,11 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
-        <v>46195.58340277777</v>
+        <v>46191.33334490741</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fabio Silva</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -11229,11 +11229,11 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
-        <v>46191.33334490741</v>
+        <v>46189.37665509259</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -11280,11 +11280,11 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="H213" s="2" t="n">
-        <v>46189.37665509259</v>
+        <v>46189.44861111111</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -11331,11 +11331,11 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="H214" s="2" t="n">
-        <v>46189.44861111111</v>
+        <v>46189.61232638889</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -11382,11 +11382,11 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="H215" s="2" t="n">
-        <v>46189.61232638889</v>
+        <v>46190.68834490741</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Willian Rios</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -11433,11 +11433,11 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="H216" s="2" t="n">
-        <v>46190.68834490741</v>
+        <v>46189.69623842592</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -11446,61 +11446,10 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
-        <is>
-          <t>Willian Rios</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>SPN</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Willian Rios</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D217" t="n">
-        <v>24</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>18994</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="n">
-        <v>46189.69623842592</v>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11517,7 +11466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K479"/>
+  <dimension ref="A1:K480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34926,7 +34875,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -34977,7 +34926,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
@@ -35028,7 +34977,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
@@ -35079,7 +35028,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -35130,7 +35079,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -35181,7 +35130,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
@@ -35385,7 +35334,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -35436,7 +35385,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -35487,7 +35436,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
@@ -35538,7 +35487,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
@@ -35640,7 +35589,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -35691,7 +35640,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -35742,7 +35691,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
@@ -35844,7 +35793,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
@@ -35895,7 +35844,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -35950,6 +35899,57 @@
         </is>
       </c>
       <c r="K479" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D480" t="n">
+        <v>24</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>19299</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>46195.58340277777</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -8526,11 +8526,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="H159" s="2" t="n">
-        <v>46162.65229166667</v>
+        <v>46161.37039351852</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -8577,11 +8577,11 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="H160" s="2" t="n">
-        <v>46161.37039351852</v>
+        <v>46162.38668981481</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -8614,34 +8614,34 @@
         <v>2026</v>
       </c>
       <c r="D161" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>46162.38668981481</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -8665,34 +8665,34 @@
         <v>2026</v>
       </c>
       <c r="D162" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>46163.70833333334</v>
+        <v>46164.46084490741</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -8730,11 +8730,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>46164.46084490741</v>
+        <v>46164.35240740741</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -8760,36 +8760,36 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Gabriel Coelho</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>2026</v>
       </c>
       <c r="D164" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>46164.35240740741</v>
+        <v>46163.38953703704</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Gabriel Coelho</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -8832,11 +8832,11 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46163.38953703704</v>
+        <v>46168.35542824074</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8862,36 +8862,36 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Mara Neves</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>2026</v>
       </c>
       <c r="D166" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>46168.35542824074</v>
+        <v>46169.55157407407</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8913,36 +8913,36 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C167" t="n">
         <v>2026</v>
       </c>
       <c r="D167" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17615</t>
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>46169.55157407407</v>
+        <v>46168.59733796296</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -8971,29 +8971,29 @@
         <v>2026</v>
       </c>
       <c r="D168" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>46168.59733796296</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9022,29 +9022,29 @@
         <v>2026</v>
       </c>
       <c r="D169" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>46171.70833333334</v>
+        <v>46174.34743055556</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9087,11 +9087,11 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>46174.34743055556</v>
+        <v>46174.44751157407</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -9117,36 +9117,36 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>2026</v>
       </c>
       <c r="D171" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
-        <v>46174.44751157407</v>
+        <v>46176.62567129629</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9189,11 +9189,11 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>46176.62567129629</v>
+        <v>46177.4203125</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -9240,11 +9240,11 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>46177.4203125</v>
+        <v>46177.44097222222</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Clanderson Oliveira</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -9291,11 +9291,11 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>46177.44097222222</v>
+        <v>46174.65693287037</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -9321,36 +9321,36 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Clanderson Oliveira</t>
+          <t>Elisandra Chaves</t>
         </is>
       </c>
       <c r="C175" t="n">
         <v>2026</v>
       </c>
       <c r="D175" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>46174.65693287037</v>
+        <v>46177.70833333334</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -9372,41 +9372,41 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Gabriel Coelho</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>2026</v>
       </c>
       <c r="D176" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="H176" s="2" t="n">
-        <v>46178.53854166667</v>
+        <v>46181.44583333333</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -9423,36 +9423,36 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Elisandra Chaves</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>2026</v>
       </c>
       <c r="D177" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="H177" s="2" t="n">
-        <v>46177.70833333334</v>
+        <v>46174.69118055556</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Gabriel Coelho</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -9495,11 +9495,11 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="H178" s="2" t="n">
-        <v>46181.44583333333</v>
+        <v>46175.34121527777</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -9525,36 +9525,36 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>2026</v>
       </c>
       <c r="D179" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="H179" s="2" t="n">
-        <v>46174.69118055556</v>
+        <v>46175.70833333334</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -9583,29 +9583,29 @@
         <v>2026</v>
       </c>
       <c r="D180" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="H180" s="2" t="n">
-        <v>46175.34121527777</v>
+        <v>46175.70833333334</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -9627,36 +9627,36 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>2026</v>
       </c>
       <c r="D181" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="H181" s="2" t="n">
-        <v>46175.70833333334</v>
+        <v>46177.33506944445</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -9685,29 +9685,29 @@
         <v>2026</v>
       </c>
       <c r="D182" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>46175.70833333334</v>
+        <v>46177.70833333334</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -9736,34 +9736,34 @@
         <v>2026</v>
       </c>
       <c r="D183" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>18176</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>46177.33506944445</v>
+        <v>46178.44940972222</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -9801,11 +9801,11 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>46177.70833333334</v>
+        <v>46178.45815972222</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -9852,11 +9852,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>46178.44940972222</v>
+        <v>46177.66613425926</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -9889,29 +9889,29 @@
         <v>2026</v>
       </c>
       <c r="D186" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="H186" s="2" t="n">
-        <v>46178.45815972222</v>
+        <v>46178.70833333334</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -9954,11 +9954,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="H187" s="2" t="n">
-        <v>46177.66613425926</v>
+        <v>46181.36931712963</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -9991,29 +9991,29 @@
         <v>2026</v>
       </c>
       <c r="D188" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>46178.70833333334</v>
+        <v>46181.44561342592</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10042,29 +10042,29 @@
         <v>2026</v>
       </c>
       <c r="D189" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>46181.36931712963</v>
+        <v>46181.50734953704</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10086,41 +10086,41 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Luan Nicocelli</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>2026</v>
       </c>
       <c r="D190" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46181.44561342592</v>
+        <v>46178.49583333333</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -10137,41 +10137,41 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Arthur Hassuma</t>
         </is>
       </c>
       <c r="C191" t="n">
         <v>2026</v>
       </c>
       <c r="D191" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>18460</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
-        <v>46181.50734953704</v>
+        <v>46188.42400462963</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -10188,36 +10188,36 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Luan Nicocelli</t>
+          <t>Elisandra Chaves</t>
         </is>
       </c>
       <c r="C192" t="n">
         <v>2026</v>
       </c>
       <c r="D192" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>46178.49583333333</v>
+        <v>46181.62840277778</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10239,36 +10239,36 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Arthur Hassuma</t>
+          <t>Fabio Silva</t>
         </is>
       </c>
       <c r="C193" t="n">
         <v>2026</v>
       </c>
       <c r="D193" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
-        <v>46188.42400462963</v>
+        <v>46184.33337962963</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -10290,36 +10290,36 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Fabio Silva</t>
         </is>
       </c>
       <c r="C194" t="n">
         <v>2026</v>
       </c>
       <c r="D194" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="H194" s="2" t="n">
-        <v>46157.64317129629</v>
+        <v>46177.43207175926</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -10341,36 +10341,36 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>2026</v>
       </c>
       <c r="D195" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="H195" s="2" t="n">
-        <v>46178.70833333334</v>
+        <v>46181.68621527778</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10392,36 +10392,36 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C196" t="n">
         <v>2026</v>
       </c>
       <c r="D196" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46184.5436574074</v>
+        <v>46184.61175925926</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -10443,41 +10443,41 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>2026</v>
       </c>
       <c r="D197" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>46184.61206018519</v>
+        <v>46185.49927083333</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -10494,36 +10494,36 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>2026</v>
       </c>
       <c r="D198" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>46185.40383101852</v>
+        <v>46185.55496527778</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -10545,41 +10545,41 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Elisandra Chaves</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C199" t="n">
         <v>2026</v>
       </c>
       <c r="D199" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>46181.62840277778</v>
+        <v>46184.67892361111</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fabio Silva</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -10617,11 +10617,11 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>46184.33337962963</v>
+        <v>46185.69163194444</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Fabio Silva</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>46181.64040509259</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -10698,41 +10698,41 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Kleberson Matias</t>
         </is>
       </c>
       <c r="C202" t="n">
         <v>2026</v>
       </c>
       <c r="D202" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>46181.68621527778</v>
+        <v>46182.99998842592</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -10749,41 +10749,41 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Mara Neves</t>
         </is>
       </c>
       <c r="C203" t="n">
         <v>2026</v>
       </c>
       <c r="D203" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>46184.61175925926</v>
+        <v>46188.58333333334</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Fabio Silva</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -10821,11 +10821,11 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>46185.49927083333</v>
+        <v>46191.33334490741</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -10872,11 +10872,11 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="H205" s="2" t="n">
-        <v>46185.55496527778</v>
+        <v>46189.37665509259</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -10902,36 +10902,36 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C206" t="n">
         <v>2026</v>
       </c>
       <c r="D206" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>46184.67892361111</v>
+        <v>46188.44815972223</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -10974,11 +10974,11 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="H207" s="2" t="n">
-        <v>46185.69163194444</v>
+        <v>46189.61232638889</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -11011,34 +11011,34 @@
         <v>2026</v>
       </c>
       <c r="D208" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>46185.70833333334</v>
+        <v>46190.68834490741</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11055,36 +11055,36 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Kleberson Matias</t>
+          <t>Willian Rios</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>2026</v>
       </c>
       <c r="D209" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="H209" s="2" t="n">
-        <v>46182.99998842592</v>
+        <v>46189.69623842592</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -11106,41 +11106,41 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Mara Neves</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>2026</v>
       </c>
       <c r="D210" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>46188.58333333334</v>
+        <v>46195.67024305555</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -11157,41 +11157,41 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Fabio Silva</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C211" t="n">
         <v>2026</v>
       </c>
       <c r="D211" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
-        <v>46191.33334490741</v>
+        <v>46195.43866898148</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -11208,41 +11208,41 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C212" t="n">
         <v>2026</v>
       </c>
       <c r="D212" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
-        <v>46189.37665509259</v>
+        <v>46196.60847222222</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -11266,29 +11266,29 @@
         <v>2026</v>
       </c>
       <c r="D213" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>19755</t>
         </is>
       </c>
       <c r="H213" s="2" t="n">
-        <v>46189.44861111111</v>
+        <v>46202.47652777778</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11310,36 +11310,36 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Mara Moraes</t>
         </is>
       </c>
       <c r="C214" t="n">
         <v>2026</v>
       </c>
       <c r="D214" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="H214" s="2" t="n">
-        <v>46189.61232638889</v>
+        <v>46202.39996527778</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -11348,108 +11348,6 @@
         </is>
       </c>
       <c r="K214" t="inlineStr">
-        <is>
-          <t>Willian Rios</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>SPN</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Higor Jesus</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D215" t="n">
-        <v>24</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>19032</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="n">
-        <v>46190.68834490741</v>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Willian Rios</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>SPN</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Willian Rios</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D216" t="n">
-        <v>24</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>18994</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="n">
-        <v>46189.69623842592</v>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Resolvido</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11466,7 +11364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K480"/>
+  <dimension ref="A1:K513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30768,16 +30666,16 @@
         <v>2026</v>
       </c>
       <c r="D379" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -30790,7 +30688,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -31023,16 +30921,16 @@
         <v>2026</v>
       </c>
       <c r="D384" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -31045,7 +30943,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -31815,7 +31713,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -31985,36 +31883,36 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C403" t="n">
         <v>2026</v>
       </c>
       <c r="D403" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="H403" s="2" t="n">
-        <v>46177.33384259259</v>
+        <v>46162.65229166667</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -32024,7 +31922,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -32036,41 +31934,41 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C404" t="n">
         <v>2026</v>
       </c>
       <c r="D404" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="H404" s="2" t="n">
-        <v>46167.70833333334</v>
+        <v>46177.33384259259</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -32094,34 +31992,34 @@
         <v>2026</v>
       </c>
       <c r="D405" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="H405" s="2" t="n">
-        <v>46169.42894675926</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -32138,7 +32036,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -32159,11 +32057,11 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="H406" s="2" t="n">
-        <v>46169.6337037037</v>
+        <v>46169.42894675926</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -32189,7 +32087,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -32210,11 +32108,11 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="H407" s="2" t="n">
-        <v>46171.3628125</v>
+        <v>46169.6337037037</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -32240,7 +32138,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -32261,11 +32159,11 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="H408" s="2" t="n">
-        <v>46174.37847222222</v>
+        <v>46171.3628125</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -32291,36 +32189,36 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C409" t="n">
         <v>2026</v>
       </c>
       <c r="D409" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="H409" s="2" t="n">
-        <v>46171.3843287037</v>
+        <v>46174.37847222222</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -32342,36 +32240,36 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C410" t="n">
         <v>2026</v>
       </c>
       <c r="D410" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="H410" s="2" t="n">
-        <v>46174.35002314814</v>
+        <v>46171.3843287037</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -32393,36 +32291,36 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C411" t="n">
         <v>2026</v>
       </c>
       <c r="D411" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="H411" s="2" t="n">
-        <v>46167.70700231481</v>
+        <v>46174.35002314814</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -32465,11 +32363,11 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="H412" s="2" t="n">
-        <v>46162.69203703704</v>
+        <v>46167.70700231481</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -32516,11 +32414,11 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="H413" s="2" t="n">
-        <v>46163.3453125</v>
+        <v>46162.69203703704</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -32567,11 +32465,11 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="H414" s="2" t="n">
-        <v>46165.99998842592</v>
+        <v>46163.3453125</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -32618,11 +32516,11 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="H415" s="2" t="n">
-        <v>46164.42878472222</v>
+        <v>46165.99998842592</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -32648,7 +32546,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -32669,11 +32567,11 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>18348</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="H416" s="2" t="n">
-        <v>46175.54391203704</v>
+        <v>46164.42878472222</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -32699,7 +32597,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -32720,11 +32618,11 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="H417" s="2" t="n">
-        <v>46179.99998842592</v>
+        <v>46175.54391203704</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -32771,11 +32669,11 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="H418" s="2" t="n">
-        <v>46171.3843287037</v>
+        <v>46179.99998842592</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -32822,11 +32720,11 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>18186</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="H419" s="2" t="n">
-        <v>46175.50818287037</v>
+        <v>46171.3843287037</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -32873,11 +32771,11 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="H420" s="2" t="n">
-        <v>46177.47008101852</v>
+        <v>46175.50818287037</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -32924,11 +32822,11 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="H421" s="2" t="n">
-        <v>46174.68819444445</v>
+        <v>46177.47008101852</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -32975,11 +32873,11 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="H422" s="2" t="n">
-        <v>46175.70833333334</v>
+        <v>46174.68819444445</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -33005,7 +32903,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -33026,11 +32924,11 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="H423" s="2" t="n">
-        <v>46174.41666666666</v>
+        <v>46175.70833333334</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -33056,7 +32954,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -33077,11 +32975,11 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="H424" s="2" t="n">
-        <v>46176.61097222222</v>
+        <v>46174.41666666666</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -33107,7 +33005,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -33128,11 +33026,11 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18482</t>
         </is>
       </c>
       <c r="H425" s="2" t="n">
-        <v>46178.365625</v>
+        <v>46176.61097222222</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -33158,7 +33056,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -33179,11 +33077,11 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>18443</t>
         </is>
       </c>
       <c r="H426" s="2" t="n">
-        <v>46176.45597222223</v>
+        <v>46178.365625</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -33230,11 +33128,11 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="H427" s="2" t="n">
-        <v>46178.65739583333</v>
+        <v>46176.45597222223</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -33260,7 +33158,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -33281,11 +33179,11 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="H428" s="2" t="n">
-        <v>46177.58333333334</v>
+        <v>46178.65739583333</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -33332,7 +33230,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="H429" s="2" t="n">
@@ -33383,11 +33281,11 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="H430" s="2" t="n">
-        <v>46177.58939814815</v>
+        <v>46177.58333333334</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -33434,11 +33332,11 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="H431" s="2" t="n">
-        <v>46178.44984953704</v>
+        <v>46177.58939814815</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -33485,11 +33383,11 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="H432" s="2" t="n">
-        <v>46178.49792824074</v>
+        <v>46178.44984953704</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -33536,11 +33434,11 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="H433" s="2" t="n">
-        <v>46181.55126157407</v>
+        <v>46178.49792824074</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -33587,11 +33485,11 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18257</t>
         </is>
       </c>
       <c r="H434" s="2" t="n">
-        <v>46178.49097222222</v>
+        <v>46181.55126157407</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -33638,11 +33536,11 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="H435" s="2" t="n">
-        <v>46178.66917824074</v>
+        <v>46178.49097222222</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -33668,41 +33566,41 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C436" t="n">
         <v>2026</v>
       </c>
       <c r="D436" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="H436" s="2" t="n">
-        <v>46179.99998842592</v>
+        <v>46178.66917824074</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -33726,29 +33624,29 @@
         <v>2026</v>
       </c>
       <c r="D437" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="H437" s="2" t="n">
-        <v>46181.35356481482</v>
+        <v>46179.99998842592</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -33770,7 +33668,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -33791,11 +33689,11 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="H438" s="2" t="n">
-        <v>46181.40673611111</v>
+        <v>46181.35356481482</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33821,41 +33719,41 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C439" t="n">
         <v>2026</v>
       </c>
       <c r="D439" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="H439" s="2" t="n">
-        <v>46177.37328703704</v>
+        <v>46181.40673611111</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -33879,34 +33777,34 @@
         <v>2026</v>
       </c>
       <c r="D440" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="H440" s="2" t="n">
-        <v>46181.48393518518</v>
+        <v>46177.37328703704</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -33923,41 +33821,41 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C441" t="n">
         <v>2026</v>
       </c>
       <c r="D441" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="H441" s="2" t="n">
-        <v>46178.64079861111</v>
+        <v>46181.48393518518</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -33974,41 +33872,41 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C442" t="n">
         <v>2026</v>
       </c>
       <c r="D442" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="H442" s="2" t="n">
-        <v>46184.68549768518</v>
+        <v>46178.64079861111</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -34025,46 +33923,46 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C443" t="n">
         <v>2026</v>
       </c>
       <c r="D443" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="H443" s="2" t="n">
-        <v>46188.53701388889</v>
+        <v>46178.53854166667</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -34097,11 +33995,11 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="H444" s="2" t="n">
-        <v>46188.54712962963</v>
+        <v>46184.68549768518</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -34127,41 +34025,41 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C445" t="n">
         <v>2026</v>
       </c>
       <c r="D445" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18844</t>
         </is>
       </c>
       <c r="H445" s="2" t="n">
-        <v>46184.44909722222</v>
+        <v>46188.53701388889</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -34178,41 +34076,41 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C446" t="n">
         <v>2026</v>
       </c>
       <c r="D446" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="H446" s="2" t="n">
-        <v>46184.4005787037</v>
+        <v>46188.54712962963</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -34229,41 +34127,41 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C447" t="n">
         <v>2026</v>
       </c>
       <c r="D447" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="H447" s="2" t="n">
-        <v>46185.40510416667</v>
+        <v>46184.44909722222</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -34280,41 +34178,41 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C448" t="n">
         <v>2026</v>
       </c>
       <c r="D448" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="H448" s="2" t="n">
-        <v>46188.42299768519</v>
+        <v>46184.4005787037</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -34331,7 +34229,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -34352,11 +34250,11 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="H449" s="2" t="n">
-        <v>46183.39971064815</v>
+        <v>46185.40510416667</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -34382,7 +34280,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -34403,11 +34301,11 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="H450" s="2" t="n">
-        <v>46183.69546296296</v>
+        <v>46188.42299768519</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -34454,11 +34352,11 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="H451" s="2" t="n">
-        <v>46184.69770833333</v>
+        <v>46183.39971064815</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
@@ -34505,11 +34403,11 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="H452" s="2" t="n">
-        <v>46188.4491087963</v>
+        <v>46183.69546296296</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
@@ -34556,11 +34454,11 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="H453" s="2" t="n">
-        <v>46188.35795138889</v>
+        <v>46184.69770833333</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
@@ -34607,11 +34505,11 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="H454" s="2" t="n">
-        <v>46185.64020833333</v>
+        <v>46188.4491087963</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
@@ -34637,7 +34535,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -34648,21 +34546,21 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="H455" s="2" t="n">
-        <v>46149.41342592592</v>
+        <v>46188.35795138889</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
@@ -34688,7 +34586,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -34709,11 +34607,11 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>18506</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="H456" s="2" t="n">
-        <v>46183.70833333334</v>
+        <v>46185.64020833333</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
@@ -34739,41 +34637,41 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C457" t="n">
         <v>2026</v>
       </c>
       <c r="D457" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="H457" s="2" t="n">
-        <v>46184.5280787037</v>
+        <v>46149.41342592592</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
@@ -34790,7 +34688,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -34811,11 +34709,11 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="H458" s="2" t="n">
-        <v>46188.33335648148</v>
+        <v>46183.70833333334</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
@@ -34841,41 +34739,41 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C459" t="n">
         <v>2026</v>
       </c>
       <c r="D459" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="H459" s="2" t="n">
-        <v>46190.58333333334</v>
+        <v>46184.5280787037</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -34892,36 +34790,36 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C460" t="n">
         <v>2026</v>
       </c>
       <c r="D460" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="H460" s="2" t="n">
-        <v>46192.57590277777</v>
+        <v>46188.33335648148</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -34943,7 +34841,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -34964,11 +34862,11 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="H461" s="2" t="n">
-        <v>46192.70833333334</v>
+        <v>46157.64317129629</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -34982,7 +34880,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -34994,46 +34892,46 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C462" t="n">
         <v>2026</v>
       </c>
       <c r="D462" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="H462" s="2" t="n">
-        <v>46192.70833333334</v>
+        <v>46178.70833333334</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -35045,36 +34943,36 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C463" t="n">
         <v>2026</v>
       </c>
       <c r="D463" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="H463" s="2" t="n">
-        <v>46195.36821759259</v>
+        <v>46184.5436574074</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -35084,7 +34982,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -35096,36 +34994,36 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C464" t="n">
         <v>2026</v>
       </c>
       <c r="D464" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="H464" s="2" t="n">
-        <v>46195.33435185185</v>
+        <v>46184.61206018519</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -35135,7 +35033,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -35147,46 +35045,46 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C465" t="n">
         <v>2026</v>
       </c>
       <c r="D465" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="H465" s="2" t="n">
-        <v>46192.65648148148</v>
+        <v>46185.40383101852</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>Emerson Simette</t>
+          <t>Willian Rios</t>
         </is>
       </c>
     </row>
@@ -35219,11 +35117,11 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="H466" s="2" t="n">
-        <v>46195.57657407408</v>
+        <v>46190.58333333334</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
@@ -35232,7 +35130,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
@@ -35249,7 +35147,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -35270,11 +35168,11 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="H467" s="2" t="n">
-        <v>46192.35711805556</v>
+        <v>46192.57590277777</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -35283,7 +35181,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
@@ -35300,7 +35198,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -35321,11 +35219,11 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="H468" s="2" t="n">
-        <v>46192.35331018519</v>
+        <v>46192.70833333334</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -35351,7 +35249,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -35372,11 +35270,11 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>19293</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="H469" s="2" t="n">
-        <v>46195.53289351852</v>
+        <v>46192.70833333334</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35402,7 +35300,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -35423,11 +35321,11 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="H470" s="2" t="n">
-        <v>46195.5577662037</v>
+        <v>46195.36821759259</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35453,7 +35351,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -35474,11 +35372,11 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>19131</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="H471" s="2" t="n">
-        <v>46192.38016203704</v>
+        <v>46195.33435185185</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35504,7 +35402,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -35525,11 +35423,11 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="H472" s="2" t="n">
-        <v>46192.5730787037</v>
+        <v>46192.65648148148</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35538,7 +35436,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
@@ -35555,7 +35453,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -35576,11 +35474,11 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="H473" s="2" t="n">
-        <v>46190.35675925926</v>
+        <v>46195.57657407408</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35606,7 +35504,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -35627,11 +35525,11 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="H474" s="2" t="n">
-        <v>46191.69305555556</v>
+        <v>46192.35711805556</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35657,7 +35555,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -35678,11 +35576,11 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="H475" s="2" t="n">
-        <v>46191.55715277778</v>
+        <v>46192.35331018519</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35708,7 +35606,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -35729,11 +35627,11 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19293</t>
         </is>
       </c>
       <c r="H476" s="2" t="n">
-        <v>46191.3712037037</v>
+        <v>46195.53289351852</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35742,7 +35640,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
@@ -35759,7 +35657,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -35780,11 +35678,11 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="H477" s="2" t="n">
-        <v>46189.45256944445</v>
+        <v>46195.5577662037</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35810,7 +35708,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -35831,11 +35729,11 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="H478" s="2" t="n">
-        <v>46192.69414351852</v>
+        <v>46192.38016203704</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35861,36 +35759,36 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C479" t="n">
         <v>2026</v>
       </c>
       <c r="D479" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="H479" s="2" t="n">
-        <v>46195.36251157407</v>
+        <v>46192.5730787037</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -35912,7 +35810,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -35933,23 +35831,1706 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
+          <t>19090</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>46190.35675925926</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D481" t="n">
+        <v>24</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>19234</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="n">
+        <v>46191.69305555556</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D482" t="n">
+        <v>24</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>19211</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="n">
+        <v>46191.55715277778</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D483" t="n">
+        <v>24</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>19093</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="n">
+        <v>46191.3712037037</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D484" t="n">
+        <v>24</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>18927</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="n">
+        <v>46189.45256944445</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D485" t="n">
+        <v>24</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>19235</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="n">
+        <v>46192.69414351852</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D486" t="n">
+        <v>25</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>19257</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="n">
+        <v>46195.36251157407</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D487" t="n">
+        <v>24</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
           <t>19299</t>
         </is>
       </c>
-      <c r="H480" s="2" t="n">
+      <c r="H487" s="2" t="n">
         <v>46195.58340277777</v>
       </c>
-      <c r="I480" t="inlineStr">
+      <c r="I487" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="J480" t="inlineStr">
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D488" t="n">
+        <v>25</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>19606</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>46199.56194444445</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr">
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D489" t="n">
+        <v>25</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>19688</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="n">
+        <v>46199.67670138889</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D490" t="n">
+        <v>25</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>19691</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="n">
+        <v>46199.66152777777</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D491" t="n">
+        <v>25</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>19693</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="n">
+        <v>46199.70833333334</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D492" t="n">
+        <v>25</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>19694</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="n">
+        <v>46199.65715277778</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D493" t="n">
+        <v>25</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>19698</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>46199.70833333334</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D494" t="n">
+        <v>25</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>19703</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="n">
+        <v>46202.38981481481</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D495" t="n">
+        <v>25</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>19704</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="n">
+        <v>46202.42601851852</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D496" t="n">
+        <v>25</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>19722</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>46202.3830787037</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D497" t="n">
+        <v>25</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>19724</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="n">
+        <v>46199.70833333334</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D498" t="n">
+        <v>25</v>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>19727</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="n">
+        <v>46199.70833333334</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D499" t="n">
+        <v>25</v>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>19734</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="n">
+        <v>46202.36549768518</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D500" t="n">
+        <v>25</v>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>19737</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="n">
+        <v>46199.63583333333</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D501" t="n">
+        <v>25</v>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>19738</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="n">
+        <v>46202.54703703704</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D502" t="n">
+        <v>25</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>19747</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>46202.43180555556</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D503" t="n">
+        <v>25</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>19749</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="n">
+        <v>46202.43614583334</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D504" t="n">
+        <v>25</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>19751</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="n">
+        <v>46202.4540162037</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D505" t="n">
+        <v>25</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>19826</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="n">
+        <v>46202.44827546296</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D506" t="n">
+        <v>25</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>19359</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="n">
+        <v>46199.50884259259</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D507" t="n">
+        <v>25</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>19407</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="n">
+        <v>46195.68649305555</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D508" t="n">
+        <v>25</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>19657</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>46199.45320601852</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D509" t="n">
+        <v>25</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>19671</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>46202.55322916667</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D510" t="n">
+        <v>25</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>19530</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="n">
+        <v>46202.50553240741</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Patrick Doyle</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D511" t="n">
+        <v>25</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>19631</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="n">
+        <v>46198.59567129629</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D512" t="n">
+        <v>25</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>19444</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="n">
+        <v>46197.4875925926</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D513" t="n">
+        <v>25</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>19522</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="n">
+        <v>46197.613125</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -9763,7 +9763,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Fabio Silva</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -33957,12 +33957,12 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Willian Rios</t>
+          <t>Emerson Simette</t>
         </is>
       </c>
     </row>
@@ -34926,12 +34926,12 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>Willian Rios</t>
+          <t>Emerson Simette</t>
         </is>
       </c>
     </row>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
@@ -36252,7 +36252,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
@@ -36354,7 +36354,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
@@ -36405,7 +36405,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
@@ -36456,7 +36456,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
@@ -36558,7 +36558,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
@@ -36609,7 +36609,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
@@ -36711,7 +36711,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -36728,7 +36728,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -36864,7 +36864,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
@@ -36915,7 +36915,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -37068,7 +37068,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
@@ -37119,7 +37119,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
@@ -37221,7 +37221,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
@@ -37323,7 +37323,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -37476,7 +37476,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K214"/>
+  <dimension ref="A1:K218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8614,16 +8614,16 @@
         <v>2026</v>
       </c>
       <c r="D161" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9991,16 +9991,16 @@
         <v>2026</v>
       </c>
       <c r="D188" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10042,16 +10042,16 @@
         <v>2026</v>
       </c>
       <c r="D189" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10552,16 +10552,16 @@
         <v>2026</v>
       </c>
       <c r="D199" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -10909,16 +10909,16 @@
         <v>2026</v>
       </c>
       <c r="D206" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11215,16 +11215,16 @@
         <v>2026</v>
       </c>
       <c r="D212" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -11344,10 +11344,214 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Arthur Hassuma</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D215" t="n">
+        <v>26</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>20230</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>46209.52760416667</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D216" t="n">
+        <v>26</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>46205.34581018519</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D217" t="n">
+        <v>26</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>20169</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>46206.70833333334</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Ivonei Feiler</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D218" t="n">
+        <v>26</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>20235</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>46209.42638888889</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11364,7 +11568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K513"/>
+  <dimension ref="A1:K540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30666,16 +30870,16 @@
         <v>2026</v>
       </c>
       <c r="D379" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -30688,12 +30892,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -30948,7 +31152,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -31992,16 +32196,16 @@
         <v>2026</v>
       </c>
       <c r="D405" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -32014,7 +32218,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -33777,16 +33981,16 @@
         <v>2026</v>
       </c>
       <c r="D440" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -33799,7 +34003,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -33879,16 +34083,16 @@
         <v>2026</v>
       </c>
       <c r="D442" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -33901,7 +34105,7 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -34134,16 +34338,16 @@
         <v>2026</v>
       </c>
       <c r="D447" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -34156,7 +34360,7 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -34185,16 +34389,16 @@
         <v>2026</v>
       </c>
       <c r="D448" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -34207,7 +34411,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -34746,16 +34950,16 @@
         <v>2026</v>
       </c>
       <c r="D459" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -34768,7 +34972,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -36762,7 +36966,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
@@ -36813,7 +37017,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
@@ -36966,7 +37170,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
@@ -37017,7 +37221,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
@@ -37136,23 +37340,23 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C506" t="n">
         <v>2026</v>
       </c>
       <c r="D506" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -37165,12 +37369,12 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
@@ -37245,16 +37449,16 @@
         <v>2026</v>
       </c>
       <c r="D508" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -37267,7 +37471,7 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -37391,23 +37595,23 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Patrick Doyle</t>
+          <t>patrick doyle</t>
         </is>
       </c>
       <c r="C511" t="n">
         <v>2026</v>
       </c>
       <c r="D511" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -37420,7 +37624,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -37527,10 +37731,1387 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D514" t="n">
+        <v>26</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>20112</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="n">
+        <v>46205.64234953704</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D515" t="n">
+        <v>26</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>20140</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="n">
+        <v>46206.42371527778</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D516" t="n">
+        <v>26</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>20162</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="n">
+        <v>46209.45043981481</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr">
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D517" t="n">
+        <v>26</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>20168</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="n">
+        <v>46209.37145833333</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D518" t="n">
+        <v>26</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>20183</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="n">
+        <v>46209.35814814815</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D519" t="n">
+        <v>26</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>20185</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="n">
+        <v>46209.34961805555</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D520" t="n">
+        <v>26</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>20190</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="n">
+        <v>46209.51263888889</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D521" t="n">
+        <v>26</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>20201</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="n">
+        <v>46209.46085648148</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D522" t="n">
+        <v>26</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>20203</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="n">
+        <v>46209.44386574074</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D523" t="n">
+        <v>26</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>20207</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="n">
+        <v>46206.66109953704</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D524" t="n">
+        <v>26</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>20222</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="n">
+        <v>46206.70504629629</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D525" t="n">
+        <v>26</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>20225</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="n">
+        <v>46209.45961805555</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D526" t="n">
+        <v>26</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="n">
+        <v>46209.41096064815</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D527" t="n">
+        <v>26</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>20156</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="n">
+        <v>46206.6478587963</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D528" t="n">
+        <v>26</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>19928</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="n">
+        <v>46205.63430555556</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D529" t="n">
+        <v>26</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="n">
+        <v>46205.37614583333</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D530" t="n">
+        <v>26</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>20011</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="n">
+        <v>46205.4203587963</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D531" t="n">
+        <v>26</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="n">
+        <v>46204.43034722222</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D532" t="n">
+        <v>26</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>20053</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="n">
+        <v>46206.65353009259</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D533" t="n">
+        <v>26</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>20099</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="n">
+        <v>46206.37006944444</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D534" t="n">
+        <v>26</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="n">
+        <v>46206.40895833333</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D535" t="n">
+        <v>26</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>17288</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="n">
+        <v>46203.45138888889</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D536" t="n">
+        <v>26</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="n">
+        <v>46205.70833333334</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D537" t="n">
+        <v>26</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>20151</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="n">
+        <v>46206.62555555555</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D538" t="n">
+        <v>26</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>19794</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="n">
+        <v>46206.59289351852</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D539" t="n">
+        <v>26</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>20020</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="n">
+        <v>46205.54998842593</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D540" t="n">
+        <v>26</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>20218</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="n">
+        <v>46206.68806712963</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K218"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9991,16 +9991,16 @@
         <v>2026</v>
       </c>
       <c r="D188" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10042,16 +10042,16 @@
         <v>2026</v>
       </c>
       <c r="D189" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11215,16 +11215,16 @@
         <v>2026</v>
       </c>
       <c r="D212" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -11552,6 +11552,618 @@
         </is>
       </c>
       <c r="K218" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D219" t="n">
+        <v>27</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>20495</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>46212.34274305555</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D220" t="n">
+        <v>27</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>19301</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>46195.58802083333</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D221" t="n">
+        <v>27</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>20396</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>46211.42284722222</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D222" t="n">
+        <v>27</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>20421</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>46211.57856481482</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D223" t="n">
+        <v>27</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>20586</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>46212.47512731481</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D224" t="n">
+        <v>27</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>20623</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>46212.6733912037</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D225" t="n">
+        <v>27</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>20717</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>46213.56881944444</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D226" t="n">
+        <v>27</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>20720</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>46213.588125</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D227" t="n">
+        <v>27</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>20747</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>46213.67231481482</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D228" t="n">
+        <v>27</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>20770</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>46216.38118055555</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D229" t="n">
+        <v>27</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>20773</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>46216.40868055556</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D230" t="n">
+        <v>27</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>20794</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>46216.53247685185</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -11568,7 +12180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K540"/>
+  <dimension ref="A1:K598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32196,16 +32808,16 @@
         <v>2026</v>
       </c>
       <c r="D405" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -32218,7 +32830,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -33981,16 +34593,16 @@
         <v>2026</v>
       </c>
       <c r="D440" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -34003,7 +34615,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -34083,16 +34695,16 @@
         <v>2026</v>
       </c>
       <c r="D442" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -34105,7 +34717,7 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -34338,16 +34950,16 @@
         <v>2026</v>
       </c>
       <c r="D447" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -34360,7 +34972,7 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -34416,7 +35028,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -34977,7 +35589,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -37449,16 +38061,16 @@
         <v>2026</v>
       </c>
       <c r="D508" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -37471,7 +38083,7 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -37595,23 +38207,23 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>patrick doyle</t>
+          <t>Patrick Doyle</t>
         </is>
       </c>
       <c r="C511" t="n">
         <v>2026</v>
       </c>
       <c r="D511" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -37624,7 +38236,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -37884,7 +38496,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
@@ -38037,7 +38649,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
@@ -38139,7 +38751,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -38163,16 +38775,16 @@
         <v>2026</v>
       </c>
       <c r="D522" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -38185,7 +38797,7 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -38316,16 +38928,16 @@
         <v>2026</v>
       </c>
       <c r="D525" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -38338,7 +38950,7 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -38394,7 +39006,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -38418,16 +39030,16 @@
         <v>2026</v>
       </c>
       <c r="D527" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -38440,7 +39052,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -38547,7 +39159,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -38598,7 +39210,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -38622,16 +39234,16 @@
         <v>2026</v>
       </c>
       <c r="D531" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -38644,7 +39256,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -38928,16 +39540,16 @@
         <v>2026</v>
       </c>
       <c r="D537" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -38950,7 +39562,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -38979,16 +39591,16 @@
         <v>2026</v>
       </c>
       <c r="D538" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -39001,7 +39613,7 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
@@ -39112,6 +39724,2964 @@
         </is>
       </c>
       <c r="K540" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D541" t="n">
+        <v>27</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>19364</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="n">
+        <v>46211.64305555556</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D542" t="n">
+        <v>27</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>20244</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="n">
+        <v>46212.39422453703</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D543" t="n">
+        <v>27</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>20264</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="n">
+        <v>46209.67506944444</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D544" t="n">
+        <v>27</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>20268</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="n">
+        <v>46209.68655092592</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D545" t="n">
+        <v>27</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>20269</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="n">
+        <v>46211.70833333334</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D546" t="n">
+        <v>27</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>20271</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="n">
+        <v>46211.65098379629</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D547" t="n">
+        <v>27</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>20296</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="n">
+        <v>46210.45550925926</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D548" t="n">
+        <v>27</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>20309</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="n">
+        <v>46210.45240740741</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D549" t="n">
+        <v>27</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>20314</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="n">
+        <v>46210.44780092593</v>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D550" t="n">
+        <v>27</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>20334</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="n">
+        <v>46210.68910879629</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D551" t="n">
+        <v>27</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>20349</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="n">
+        <v>46210.70833333334</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D552" t="n">
+        <v>27</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>20358</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="n">
+        <v>46210.6875</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D553" t="n">
+        <v>27</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>20367</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="n">
+        <v>46211.68658564815</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D554" t="n">
+        <v>27</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>20372</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="n">
+        <v>46210.70833333334</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D555" t="n">
+        <v>27</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>20375</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="n">
+        <v>46211.36699074074</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D556" t="n">
+        <v>27</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>20380</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="n">
+        <v>46211.54288194444</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D557" t="n">
+        <v>27</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>20387</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="n">
+        <v>46212.43766203704</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D558" t="n">
+        <v>27</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>20389</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="n">
+        <v>46210.40552083333</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D559" t="n">
+        <v>27</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>20403</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="n">
+        <v>46212.43748842592</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D560" t="n">
+        <v>27</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>20415</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="n">
+        <v>46212.63233796296</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D561" t="n">
+        <v>27</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>20418</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="n">
+        <v>46211.42357638889</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D562" t="n">
+        <v>27</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>20424</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="n">
+        <v>46211.47659722222</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D563" t="n">
+        <v>27</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>20429</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="n">
+        <v>46212.46340277778</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D564" t="n">
+        <v>27</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>20440</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="n">
+        <v>46210.67993055555</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D565" t="n">
+        <v>27</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>20442</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="n">
+        <v>46211.68484953704</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D566" t="n">
+        <v>27</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>20443</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="n">
+        <v>46211.70833333334</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D567" t="n">
+        <v>27</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>20458</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="n">
+        <v>46213.68130787037</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D568" t="n">
+        <v>27</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>20482</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="n">
+        <v>46211.70833333334</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D569" t="n">
+        <v>27</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>20486</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="n">
+        <v>46211.70833333334</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D570" t="n">
+        <v>27</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>20559</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="n">
+        <v>46212.35541666667</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D571" t="n">
+        <v>27</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>20560</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="n">
+        <v>46212.37936342593</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D572" t="n">
+        <v>27</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>20564</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="n">
+        <v>46212.42040509259</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D573" t="n">
+        <v>27</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>20572</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="n">
+        <v>46211.65148148148</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D574" t="n">
+        <v>27</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>20581</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="n">
+        <v>46212.49681712963</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D575" t="n">
+        <v>27</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>20601</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="n">
+        <v>46213.42203703704</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D576" t="n">
+        <v>27</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>20617</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="n">
+        <v>46212.51314814815</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D577" t="n">
+        <v>27</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>20618</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="n">
+        <v>46211.64252314815</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D578" t="n">
+        <v>27</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="n">
+        <v>46212.70833333334</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D579" t="n">
+        <v>27</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>20657</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="n">
+        <v>46212.70833333334</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D580" t="n">
+        <v>27</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>20686</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="n">
+        <v>46212.40633101852</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D581" t="n">
+        <v>27</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>20698</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="n">
+        <v>46213.45756944444</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D582" t="n">
+        <v>27</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="n">
+        <v>46213.45747685185</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D583" t="n">
+        <v>27</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>20709</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="n">
+        <v>46213.49418981482</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D584" t="n">
+        <v>27</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>20711</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="n">
+        <v>46213.52055555556</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D585" t="n">
+        <v>27</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>20712</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="n">
+        <v>46213.5928125</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D586" t="n">
+        <v>27</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>20715</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="n">
+        <v>46213.5646875</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D587" t="n">
+        <v>27</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>20719</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="n">
+        <v>46213.62619212963</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D588" t="n">
+        <v>27</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>20729</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="n">
+        <v>46216.50833333333</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D589" t="n">
+        <v>27</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>20754</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="n">
+        <v>46216.34885416667</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D590" t="n">
+        <v>27</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>20760</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="n">
+        <v>46213.58333333334</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D591" t="n">
+        <v>27</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>20783</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="n">
+        <v>46216.47300925926</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D592" t="n">
+        <v>27</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>20784</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="n">
+        <v>46216.35642361111</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D593" t="n">
+        <v>27</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>20788</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="n">
+        <v>46216.56230324074</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D594" t="n">
+        <v>27</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>20789</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="n">
+        <v>46216.56237268518</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D595" t="n">
+        <v>27</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>20801</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="n">
+        <v>46216.44944444444</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D596" t="n">
+        <v>27</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>20802</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="n">
+        <v>46213.57611111111</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D597" t="n">
+        <v>27</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>20803</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="n">
+        <v>46213.57773148148</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D598" t="n">
+        <v>27</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>20924</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="n">
+        <v>46216.33335648148</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K230"/>
+  <dimension ref="A1:K236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -11572,16 +11572,16 @@
         <v>2026</v>
       </c>
       <c r="D219" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -11590,11 +11590,11 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46212.34274305555</v>
+        <v>46204</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -11776,16 +11776,16 @@
         <v>2026</v>
       </c>
       <c r="D223" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -11794,11 +11794,11 @@
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>46212.47512731481</v>
+        <v>46204</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -11827,16 +11827,16 @@
         <v>2026</v>
       </c>
       <c r="D224" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -11845,11 +11845,11 @@
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>46212.6733912037</v>
+        <v>46204</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Gabriel Coelho</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Carine Georg</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -12160,10 +12160,316 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D231" t="n">
+        <v>28</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>21224</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D232" t="n">
+        <v>28</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>21229</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Fabio Silva</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D233" t="n">
+        <v>28</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>21058</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D234" t="n">
+        <v>28</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>20820</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D235" t="n">
+        <v>28</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>21287</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Isabela Borchardt</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D236" t="n">
+        <v>28</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>21177</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -12180,7 +12486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K598"/>
+  <dimension ref="A1:K620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32835,7 +33141,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -34620,7 +34926,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -34722,7 +35028,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -34977,7 +35283,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -38061,16 +38367,16 @@
         <v>2026</v>
       </c>
       <c r="D508" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -38079,11 +38385,11 @@
         </is>
       </c>
       <c r="H508" s="2" t="n">
-        <v>46199.45320601852</v>
+        <v>46174</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -38207,23 +38513,23 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Patrick Doyle</t>
+          <t>patrick doyle</t>
         </is>
       </c>
       <c r="C511" t="n">
         <v>2026</v>
       </c>
       <c r="D511" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -38232,11 +38538,11 @@
         </is>
       </c>
       <c r="H511" s="2" t="n">
-        <v>46198.59567129629</v>
+        <v>46174</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -38802,7 +39108,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
@@ -38955,7 +39261,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -39057,7 +39363,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -39261,7 +39567,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
@@ -39540,16 +39846,16 @@
         <v>2026</v>
       </c>
       <c r="D537" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -39558,11 +39864,11 @@
         </is>
       </c>
       <c r="H537" s="2" t="n">
-        <v>46206.62555555555</v>
+        <v>46204</v>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -39618,7 +39924,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
@@ -39737,7 +40043,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -39758,11 +40064,11 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="H541" s="2" t="n">
-        <v>46211.64305555556</v>
+        <v>46212.39422453703</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
@@ -39771,7 +40077,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
@@ -39809,11 +40115,11 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="H542" s="2" t="n">
-        <v>46212.39422453703</v>
+        <v>46209.67506944444</v>
       </c>
       <c r="I542" t="inlineStr">
         <is>
@@ -39822,7 +40128,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
@@ -39860,11 +40166,11 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="H543" s="2" t="n">
-        <v>46209.67506944444</v>
+        <v>46211.70833333334</v>
       </c>
       <c r="I543" t="inlineStr">
         <is>
@@ -39873,7 +40179,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
@@ -39890,7 +40196,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -39911,11 +40217,11 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="H544" s="2" t="n">
-        <v>46209.68655092592</v>
+        <v>46211.65098379629</v>
       </c>
       <c r="I544" t="inlineStr">
         <is>
@@ -39924,7 +40230,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K544" t="inlineStr">
@@ -39962,11 +40268,11 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="H545" s="2" t="n">
-        <v>46211.70833333334</v>
+        <v>46210.45550925926</v>
       </c>
       <c r="I545" t="inlineStr">
         <is>
@@ -39975,7 +40281,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
@@ -39992,7 +40298,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -40013,11 +40319,11 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="H546" s="2" t="n">
-        <v>46211.65098379629</v>
+        <v>46210.45240740741</v>
       </c>
       <c r="I546" t="inlineStr">
         <is>
@@ -40026,7 +40332,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
@@ -40064,11 +40370,11 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="H547" s="2" t="n">
-        <v>46210.45550925926</v>
+        <v>46210.44780092593</v>
       </c>
       <c r="I547" t="inlineStr">
         <is>
@@ -40077,7 +40383,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
@@ -40115,11 +40421,11 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="H548" s="2" t="n">
-        <v>46210.45240740741</v>
+        <v>46210.68910879629</v>
       </c>
       <c r="I548" t="inlineStr">
         <is>
@@ -40128,7 +40434,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
@@ -40166,11 +40472,11 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>20314</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="H549" s="2" t="n">
-        <v>46210.44780092593</v>
+        <v>46210.70833333334</v>
       </c>
       <c r="I549" t="inlineStr">
         <is>
@@ -40179,7 +40485,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
@@ -40217,11 +40523,11 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="H550" s="2" t="n">
-        <v>46210.68910879629</v>
+        <v>46211.68658564815</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -40230,7 +40536,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
@@ -40268,7 +40574,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="H551" s="2" t="n">
@@ -40281,7 +40587,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
@@ -40298,7 +40604,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -40319,11 +40625,11 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="H552" s="2" t="n">
-        <v>46210.6875</v>
+        <v>46211.36699074074</v>
       </c>
       <c r="I552" t="inlineStr">
         <is>
@@ -40332,7 +40638,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
@@ -40370,11 +40676,11 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="H553" s="2" t="n">
-        <v>46211.68658564815</v>
+        <v>46211.54288194444</v>
       </c>
       <c r="I553" t="inlineStr">
         <is>
@@ -40383,7 +40689,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K553" t="inlineStr">
@@ -40400,7 +40706,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -40421,11 +40727,11 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="H554" s="2" t="n">
-        <v>46210.70833333334</v>
+        <v>46212.43766203704</v>
       </c>
       <c r="I554" t="inlineStr">
         <is>
@@ -40434,7 +40740,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
@@ -40451,7 +40757,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -40472,11 +40778,11 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="H555" s="2" t="n">
-        <v>46211.36699074074</v>
+        <v>46212.43748842592</v>
       </c>
       <c r="I555" t="inlineStr">
         <is>
@@ -40485,7 +40791,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
@@ -40523,11 +40829,11 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="H556" s="2" t="n">
-        <v>46211.54288194444</v>
+        <v>46212.63233796296</v>
       </c>
       <c r="I556" t="inlineStr">
         <is>
@@ -40536,7 +40842,7 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
@@ -40574,11 +40880,11 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="H557" s="2" t="n">
-        <v>46212.43766203704</v>
+        <v>46211.42357638889</v>
       </c>
       <c r="I557" t="inlineStr">
         <is>
@@ -40587,7 +40893,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
@@ -40604,7 +40910,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -40625,11 +40931,11 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="H558" s="2" t="n">
-        <v>46210.40552083333</v>
+        <v>46212.46340277778</v>
       </c>
       <c r="I558" t="inlineStr">
         <is>
@@ -40638,7 +40944,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
@@ -40676,11 +40982,11 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="H559" s="2" t="n">
-        <v>46212.43748842592</v>
+        <v>46211.70833333334</v>
       </c>
       <c r="I559" t="inlineStr">
         <is>
@@ -40689,7 +40995,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -40727,11 +41033,11 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="H560" s="2" t="n">
-        <v>46212.63233796296</v>
+        <v>46213.68130787037</v>
       </c>
       <c r="I560" t="inlineStr">
         <is>
@@ -40740,7 +41046,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
@@ -40778,11 +41084,11 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="H561" s="2" t="n">
-        <v>46211.42357638889</v>
+        <v>46212.42040509259</v>
       </c>
       <c r="I561" t="inlineStr">
         <is>
@@ -40791,7 +41097,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
@@ -40808,7 +41114,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -40829,11 +41135,11 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="H562" s="2" t="n">
-        <v>46211.47659722222</v>
+        <v>46212.49681712963</v>
       </c>
       <c r="I562" t="inlineStr">
         <is>
@@ -40842,7 +41148,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
@@ -40880,11 +41186,11 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="H563" s="2" t="n">
-        <v>46212.46340277778</v>
+        <v>46213.42203703704</v>
       </c>
       <c r="I563" t="inlineStr">
         <is>
@@ -40893,7 +41199,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -40910,7 +41216,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Nicolau Berlandi</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -40931,11 +41237,11 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="H564" s="2" t="n">
-        <v>46210.67993055555</v>
+        <v>46212.51314814815</v>
       </c>
       <c r="I564" t="inlineStr">
         <is>
@@ -40944,7 +41250,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
@@ -40961,7 +41267,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -40982,11 +41288,11 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="H565" s="2" t="n">
-        <v>46211.68484953704</v>
+        <v>46213.45756944444</v>
       </c>
       <c r="I565" t="inlineStr">
         <is>
@@ -40995,7 +41301,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
@@ -41033,11 +41339,11 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="H566" s="2" t="n">
-        <v>46211.70833333334</v>
+        <v>46213.45747685185</v>
       </c>
       <c r="I566" t="inlineStr">
         <is>
@@ -41046,7 +41352,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
@@ -41084,11 +41390,11 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="H567" s="2" t="n">
-        <v>46213.68130787037</v>
+        <v>46213.5928125</v>
       </c>
       <c r="I567" t="inlineStr">
         <is>
@@ -41097,7 +41403,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
@@ -41114,7 +41420,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -41135,11 +41441,11 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="H568" s="2" t="n">
-        <v>46211.70833333334</v>
+        <v>46213.62619212963</v>
       </c>
       <c r="I568" t="inlineStr">
         <is>
@@ -41148,7 +41454,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
@@ -41165,7 +41471,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -41186,11 +41492,11 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="H569" s="2" t="n">
-        <v>46211.70833333334</v>
+        <v>46216.50833333333</v>
       </c>
       <c r="I569" t="inlineStr">
         <is>
@@ -41199,7 +41505,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
@@ -41216,7 +41522,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -41237,11 +41543,11 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="H570" s="2" t="n">
-        <v>46212.35541666667</v>
+        <v>46216.34885416667</v>
       </c>
       <c r="I570" t="inlineStr">
         <is>
@@ -41250,7 +41556,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
@@ -41267,7 +41573,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -41288,11 +41594,11 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="H571" s="2" t="n">
-        <v>46212.37936342593</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
@@ -41301,7 +41607,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
@@ -41339,11 +41645,11 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="H572" s="2" t="n">
-        <v>46212.42040509259</v>
+        <v>46213.57611111111</v>
       </c>
       <c r="I572" t="inlineStr">
         <is>
@@ -41352,7 +41658,7 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K572" t="inlineStr">
@@ -41369,7 +41675,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Edson Junior</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -41390,11 +41696,11 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="H573" s="2" t="n">
-        <v>46211.65148148148</v>
+        <v>46216.44944444444</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -41403,7 +41709,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
@@ -41420,7 +41726,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -41441,11 +41747,11 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20358</t>
         </is>
       </c>
       <c r="H574" s="2" t="n">
-        <v>46212.49681712963</v>
+        <v>46210.6875</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
@@ -41454,7 +41760,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
@@ -41471,7 +41777,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -41492,11 +41798,11 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="H575" s="2" t="n">
-        <v>46213.42203703704</v>
+        <v>46211.68484953704</v>
       </c>
       <c r="I575" t="inlineStr">
         <is>
@@ -41505,7 +41811,7 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K575" t="inlineStr">
@@ -41522,36 +41828,36 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C576" t="n">
         <v>2026</v>
       </c>
       <c r="D576" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="H576" s="2" t="n">
-        <v>46212.51314814815</v>
+        <v>46204</v>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -41573,7 +41879,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -41594,11 +41900,11 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="H577" s="2" t="n">
-        <v>46211.64252314815</v>
+        <v>46212.35541666667</v>
       </c>
       <c r="I577" t="inlineStr">
         <is>
@@ -41607,7 +41913,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K577" t="inlineStr">
@@ -41624,7 +41930,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -41645,7 +41951,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="H578" s="2" t="n">
@@ -41658,7 +41964,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
@@ -41696,11 +42002,11 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="H579" s="2" t="n">
-        <v>46212.70833333334</v>
+        <v>46213.49418981482</v>
       </c>
       <c r="I579" t="inlineStr">
         <is>
@@ -41709,7 +42015,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
@@ -41726,7 +42032,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Nicolau Berlandi</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -41747,11 +42053,11 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="H580" s="2" t="n">
-        <v>46212.40633101852</v>
+        <v>46216.47300925926</v>
       </c>
       <c r="I580" t="inlineStr">
         <is>
@@ -41760,7 +42066,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
@@ -41777,7 +42083,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -41798,11 +42104,11 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="H581" s="2" t="n">
-        <v>46213.45756944444</v>
+        <v>46210.40552083333</v>
       </c>
       <c r="I581" t="inlineStr">
         <is>
@@ -41811,7 +42117,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K581" t="inlineStr">
@@ -41828,7 +42134,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -41849,11 +42155,11 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>20424</t>
         </is>
       </c>
       <c r="H582" s="2" t="n">
-        <v>46213.45747685185</v>
+        <v>46211.47659722222</v>
       </c>
       <c r="I582" t="inlineStr">
         <is>
@@ -41862,7 +42168,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K582" t="inlineStr">
@@ -41879,7 +42185,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -41900,11 +42206,11 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>20709</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="H583" s="2" t="n">
-        <v>46213.49418981482</v>
+        <v>46212.37936342593</v>
       </c>
       <c r="I583" t="inlineStr">
         <is>
@@ -41913,7 +42219,7 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K583" t="inlineStr">
@@ -41930,7 +42236,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -41951,11 +42257,11 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="H584" s="2" t="n">
-        <v>46213.52055555556</v>
+        <v>46211.65148148148</v>
       </c>
       <c r="I584" t="inlineStr">
         <is>
@@ -41964,7 +42270,7 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
@@ -41981,7 +42287,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -42002,11 +42308,11 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>20712</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="H585" s="2" t="n">
-        <v>46213.5928125</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="I585" t="inlineStr">
         <is>
@@ -42015,7 +42321,7 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K585" t="inlineStr">
@@ -42032,7 +42338,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -42053,11 +42359,11 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="H586" s="2" t="n">
-        <v>46213.5646875</v>
+        <v>46216.35642361111</v>
       </c>
       <c r="I586" t="inlineStr">
         <is>
@@ -42066,7 +42372,7 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K586" t="inlineStr">
@@ -42083,7 +42389,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -42104,11 +42410,11 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>20788</t>
         </is>
       </c>
       <c r="H587" s="2" t="n">
-        <v>46213.62619212963</v>
+        <v>46216.56230324074</v>
       </c>
       <c r="I587" t="inlineStr">
         <is>
@@ -42117,7 +42423,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K587" t="inlineStr">
@@ -42134,7 +42440,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -42155,11 +42461,11 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="H588" s="2" t="n">
-        <v>46216.50833333333</v>
+        <v>46216.56237268518</v>
       </c>
       <c r="I588" t="inlineStr">
         <is>
@@ -42168,7 +42474,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K588" t="inlineStr">
@@ -42185,7 +42491,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -42206,11 +42512,11 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>20754</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="H589" s="2" t="n">
-        <v>46216.34885416667</v>
+        <v>46211.64305555556</v>
       </c>
       <c r="I589" t="inlineStr">
         <is>
@@ -42219,7 +42525,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K589" t="inlineStr">
@@ -42236,36 +42542,36 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C590" t="n">
         <v>2026</v>
       </c>
       <c r="D590" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="H590" s="2" t="n">
-        <v>46213.58333333334</v>
+        <v>46204</v>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -42287,7 +42593,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -42308,11 +42614,11 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="H591" s="2" t="n">
-        <v>46216.47300925926</v>
+        <v>46213.52055555556</v>
       </c>
       <c r="I591" t="inlineStr">
         <is>
@@ -42321,7 +42627,7 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
@@ -42338,7 +42644,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -42359,11 +42665,11 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="H592" s="2" t="n">
-        <v>46216.35642361111</v>
+        <v>46213.5646875</v>
       </c>
       <c r="I592" t="inlineStr">
         <is>
@@ -42372,7 +42678,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
@@ -42389,7 +42695,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Nicolau Berlandi</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -42410,11 +42716,11 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>20788</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="H593" s="2" t="n">
-        <v>46216.56230324074</v>
+        <v>46210.67993055555</v>
       </c>
       <c r="I593" t="inlineStr">
         <is>
@@ -42423,7 +42729,7 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K593" t="inlineStr">
@@ -42440,7 +42746,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Nicolau Berlandi</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -42461,11 +42767,11 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="H594" s="2" t="n">
-        <v>46216.56237268518</v>
+        <v>46212.40633101852</v>
       </c>
       <c r="I594" t="inlineStr">
         <is>
@@ -42474,7 +42780,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
@@ -42491,7 +42797,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Edson Junior</t>
+          <t>Nicolau Berlandi</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -42512,11 +42818,11 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="H595" s="2" t="n">
-        <v>46216.44944444444</v>
+        <v>46213.57773148148</v>
       </c>
       <c r="I595" t="inlineStr">
         <is>
@@ -42525,7 +42831,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
@@ -42542,36 +42848,36 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Alana Oliveira</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C596" t="n">
         <v>2026</v>
       </c>
       <c r="D596" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="H596" s="2" t="n">
-        <v>46213.57611111111</v>
+        <v>46204</v>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
@@ -42593,7 +42899,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Nicolau Berlandi</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -42614,11 +42920,11 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="H597" s="2" t="n">
-        <v>46213.57773148148</v>
+        <v>46211.64252314815</v>
       </c>
       <c r="I597" t="inlineStr">
         <is>
@@ -42627,7 +42933,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
@@ -42678,10 +42984,1132 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D599" t="n">
+        <v>28</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>20935</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr">
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D600" t="n">
+        <v>28</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>20963</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D601" t="n">
+        <v>28</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>20965</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D602" t="n">
+        <v>28</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>20968</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D603" t="n">
+        <v>28</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>20970</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D604" t="n">
+        <v>28</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>21007</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D605" t="n">
+        <v>28</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>21108</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D606" t="n">
+        <v>28</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>21151</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D607" t="n">
+        <v>28</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>21210</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D608" t="n">
+        <v>28</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D609" t="n">
+        <v>28</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>21208</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D610" t="n">
+        <v>28</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>21298</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D611" t="n">
+        <v>28</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>21340</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D612" t="n">
+        <v>28</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>20926</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D613" t="n">
+        <v>28</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>21389</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D614" t="n">
+        <v>28</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>20874</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D615" t="n">
+        <v>28</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>20776</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D616" t="n">
+        <v>28</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>20837</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D617" t="n">
+        <v>28</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>20873</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D618" t="n">
+        <v>28</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>20769</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D619" t="n">
+        <v>28</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>21202</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D620" t="n">
+        <v>28</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>21162</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K236"/>
+  <dimension ref="A1:K242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -12466,10 +12466,316 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Clanderson Oliveira</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D237" t="n">
+        <v>29</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>21354</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D238" t="n">
+        <v>29</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>21141</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D239" t="n">
+        <v>29</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>21425</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D240" t="n">
+        <v>29</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>21637</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Luana Giese</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D241" t="n">
+        <v>29</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>20387</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D242" t="n">
+        <v>29</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -12486,7 +12792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K620"/>
+  <dimension ref="A1:K650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33114,16 +33420,16 @@
         <v>2026</v>
       </c>
       <c r="D405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -33132,16 +33438,16 @@
         </is>
       </c>
       <c r="H405" s="2" t="n">
-        <v>46167.70833333334</v>
+        <v>46143</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -35001,16 +35307,16 @@
         <v>2026</v>
       </c>
       <c r="D442" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -35019,16 +35325,16 @@
         </is>
       </c>
       <c r="H442" s="2" t="n">
-        <v>46178.64079861111</v>
+        <v>46174</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -38394,7 +38700,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
@@ -38520,16 +38826,16 @@
         <v>2026</v>
       </c>
       <c r="D511" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -38542,7 +38848,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -39873,7 +40179,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -41835,16 +42141,16 @@
         <v>2026</v>
       </c>
       <c r="D576" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -41857,7 +42163,7 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -42549,16 +42855,16 @@
         <v>2026</v>
       </c>
       <c r="D590" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -42571,7 +42877,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -42882,7 +43188,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
@@ -43035,7 +43341,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
@@ -43086,7 +43392,7 @@
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
@@ -43137,7 +43443,7 @@
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
@@ -43188,7 +43494,7 @@
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
@@ -43212,16 +43518,16 @@
         <v>2026</v>
       </c>
       <c r="D603" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -43234,7 +43540,7 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -43290,7 +43596,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
@@ -43341,7 +43647,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K605" t="inlineStr">
@@ -43392,7 +43698,7 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
@@ -43443,7 +43749,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K607" t="inlineStr">
@@ -43494,7 +43800,7 @@
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K608" t="inlineStr">
@@ -43518,16 +43824,16 @@
         <v>2026</v>
       </c>
       <c r="D609" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -43540,7 +43846,7 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
@@ -43569,16 +43875,16 @@
         <v>2026</v>
       </c>
       <c r="D610" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -43591,7 +43897,7 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
@@ -43620,16 +43926,16 @@
         <v>2026</v>
       </c>
       <c r="D611" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -43642,7 +43948,7 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
@@ -43671,16 +43977,16 @@
         <v>2026</v>
       </c>
       <c r="D612" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -43693,7 +43999,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -43722,16 +44028,16 @@
         <v>2026</v>
       </c>
       <c r="D613" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -43744,7 +44050,7 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
@@ -43800,7 +44106,7 @@
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K614" t="inlineStr">
@@ -43817,23 +44123,23 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C615" t="n">
         <v>2026</v>
       </c>
       <c r="D615" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -43846,7 +44152,7 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
@@ -43875,16 +44181,16 @@
         <v>2026</v>
       </c>
       <c r="D616" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -43897,7 +44203,7 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
@@ -43953,7 +44259,7 @@
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K617" t="inlineStr">
@@ -44004,7 +44310,7 @@
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K618" t="inlineStr">
@@ -44028,16 +44334,16 @@
         <v>2026</v>
       </c>
       <c r="D619" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -44050,7 +44356,7 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
@@ -44106,10 +44412,1540 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D621" t="n">
+        <v>29</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>21446</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr">
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D622" t="n">
+        <v>29</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>21528</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D623" t="n">
+        <v>29</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>21611</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D624" t="n">
+        <v>29</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>21631</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D625" t="n">
+        <v>29</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>21698</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D626" t="n">
+        <v>29</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>21707</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Eduardo Silva</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D627" t="n">
+        <v>29</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>21734</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D628" t="n">
+        <v>29</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>21281</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D629" t="n">
+        <v>29</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>21374</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D630" t="n">
+        <v>29</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>21418</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D631" t="n">
+        <v>29</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>21440</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D632" t="n">
+        <v>29</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>21442</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D633" t="n">
+        <v>29</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>21443</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D634" t="n">
+        <v>29</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>21674</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D635" t="n">
+        <v>29</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>21596</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D636" t="n">
+        <v>29</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>21600</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D637" t="n">
+        <v>29</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D638" t="n">
+        <v>29</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>21754</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D639" t="n">
+        <v>29</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>21545</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D640" t="n">
+        <v>29</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>21552</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D641" t="n">
+        <v>29</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>21553</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D642" t="n">
+        <v>29</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>21577</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D643" t="n">
+        <v>29</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>21595</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D644" t="n">
+        <v>29</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>21381</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D645" t="n">
+        <v>29</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>21488</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D646" t="n">
+        <v>29</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>21345</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D647" t="n">
+        <v>29</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>21349</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D648" t="n">
+        <v>29</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>21394</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D649" t="n">
+        <v>29</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>21376</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D650" t="n">
+        <v>29</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>21608</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K242"/>
+  <dimension ref="A1:K245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12126,23 +12126,23 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Luana Giese</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>2026</v>
       </c>
       <c r="D230" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -12151,16 +12151,16 @@
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>46216.53247685185</v>
+        <v>46204</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -12745,16 +12745,16 @@
         <v>2026</v>
       </c>
       <c r="D242" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -12776,6 +12776,159 @@
         </is>
       </c>
       <c r="K242" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D243" t="n">
+        <v>30</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>21980</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D244" t="n">
+        <v>30</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>21920</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D245" t="n">
+        <v>30</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>21946</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -12792,7 +12945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K650"/>
+  <dimension ref="A1:K664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33447,7 +33600,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -35334,7 +35487,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -38853,7 +39006,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
@@ -42141,16 +42294,16 @@
         <v>2026</v>
       </c>
       <c r="D576" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -42163,7 +42316,7 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -42855,16 +43008,16 @@
         <v>2026</v>
       </c>
       <c r="D590" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -42877,7 +43030,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -43545,7 +43698,7 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
@@ -43851,7 +44004,7 @@
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
@@ -43902,7 +44055,7 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
@@ -43953,7 +44106,7 @@
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K611" t="inlineStr">
@@ -43977,16 +44130,16 @@
         <v>2026</v>
       </c>
       <c r="D612" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -43999,7 +44152,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -44028,16 +44181,16 @@
         <v>2026</v>
       </c>
       <c r="D613" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -44050,7 +44203,7 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
@@ -44130,16 +44283,16 @@
         <v>2026</v>
       </c>
       <c r="D615" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -44152,7 +44305,7 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
@@ -44208,7 +44361,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
@@ -44334,16 +44487,16 @@
         <v>2026</v>
       </c>
       <c r="D619" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -44356,7 +44509,7 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
@@ -44463,7 +44616,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
@@ -44514,7 +44667,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
@@ -44531,7 +44684,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -44565,7 +44718,7 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
@@ -44616,7 +44769,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -44667,7 +44820,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
@@ -44718,7 +44871,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
@@ -44769,7 +44922,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -44820,7 +44973,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
@@ -44871,7 +45024,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
@@ -44922,7 +45075,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
@@ -44973,7 +45126,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
@@ -45024,7 +45177,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
@@ -45075,7 +45228,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
@@ -45126,7 +45279,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
@@ -45150,16 +45303,16 @@
         <v>2026</v>
       </c>
       <c r="D635" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -45172,7 +45325,7 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
@@ -45201,16 +45354,16 @@
         <v>2026</v>
       </c>
       <c r="D636" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -45223,7 +45376,7 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
@@ -45252,16 +45405,16 @@
         <v>2026</v>
       </c>
       <c r="D637" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -45274,7 +45427,7 @@
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
@@ -45303,16 +45456,16 @@
         <v>2026</v>
       </c>
       <c r="D638" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -45325,7 +45478,7 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
@@ -45381,7 +45534,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
@@ -45432,7 +45585,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
@@ -45483,7 +45636,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
@@ -45534,7 +45687,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -45585,7 +45738,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -45609,16 +45762,16 @@
         <v>2026</v>
       </c>
       <c r="D644" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -45631,7 +45784,7 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
@@ -45660,16 +45813,16 @@
         <v>2026</v>
       </c>
       <c r="D645" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -45682,7 +45835,7 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
@@ -45738,7 +45891,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
@@ -45789,7 +45942,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
@@ -45840,7 +45993,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
@@ -45891,7 +46044,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
@@ -45915,16 +46068,16 @@
         <v>2026</v>
       </c>
       <c r="D650" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -45937,7 +46090,7 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
@@ -45946,6 +46099,720 @@
         </is>
       </c>
       <c r="K650" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D651" t="n">
+        <v>30</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>21975</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D652" t="n">
+        <v>30</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>21876</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D653" t="n">
+        <v>30</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>21858</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D654" t="n">
+        <v>30</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>22080</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D655" t="n">
+        <v>30</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>22098</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D656" t="n">
+        <v>30</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>22094</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D657" t="n">
+        <v>30</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>21801</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D658" t="n">
+        <v>30</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>21817</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D659" t="n">
+        <v>30</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>21818</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D660" t="n">
+        <v>30</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>21797</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D661" t="n">
+        <v>30</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>22111</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D662" t="n">
+        <v>30</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>21994</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Mateus Neckel</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D663" t="n">
+        <v>30</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>21038</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D664" t="n">
+        <v>30</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>15390</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -12160,7 +12160,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K612" t="inlineStr">
@@ -44208,7 +44208,7 @@
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K613" t="inlineStr">
@@ -44310,7 +44310,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
@@ -45330,7 +45330,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
@@ -45381,7 +45381,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
@@ -45432,7 +45432,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -46350,7 +46350,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
@@ -46401,7 +46401,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
@@ -46452,7 +46452,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
@@ -46503,7 +46503,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
@@ -46554,7 +46554,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
@@ -46656,7 +46656,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
@@ -46707,7 +46707,7 @@
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
@@ -46809,7 +46809,7 @@
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K245"/>
+  <dimension ref="A1:K249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12745,16 +12745,16 @@
         <v>2026</v>
       </c>
       <c r="D242" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -12796,16 +12796,16 @@
         <v>2026</v>
       </c>
       <c r="D243" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -12814,11 +12814,11 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -12925,10 +12925,214 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D246" t="n">
+        <v>31</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>22123</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D247" t="n">
+        <v>31</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>22132</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D248" t="n">
+        <v>31</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>22229</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D249" t="n">
+        <v>31</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>22278</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -12945,7 +13149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K664"/>
+  <dimension ref="A1:K692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42294,16 +42498,16 @@
         <v>2026</v>
       </c>
       <c r="D576" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -42316,7 +42520,7 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -43008,16 +43212,16 @@
         <v>2026</v>
       </c>
       <c r="D590" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -43030,7 +43234,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -44487,16 +44691,16 @@
         <v>2026</v>
       </c>
       <c r="D619" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -44509,7 +44713,7 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
@@ -45483,7 +45687,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
@@ -45755,23 +45959,23 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C644" t="n">
         <v>2026</v>
       </c>
       <c r="D644" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -45784,7 +45988,7 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
@@ -45806,23 +46010,23 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Nicolau Berlandi</t>
         </is>
       </c>
       <c r="C645" t="n">
         <v>2026</v>
       </c>
       <c r="D645" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -45835,7 +46039,7 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
@@ -46068,16 +46272,16 @@
         <v>2026</v>
       </c>
       <c r="D650" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -46090,7 +46294,7 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
@@ -46170,16 +46374,16 @@
         <v>2026</v>
       </c>
       <c r="D652" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -46192,7 +46396,7 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
@@ -46248,7 +46452,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
@@ -46272,16 +46476,16 @@
         <v>2026</v>
       </c>
       <c r="D654" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -46294,7 +46498,7 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
@@ -46605,7 +46809,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -46724,23 +46928,23 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Mateus Neckel</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C663" t="n">
         <v>2026</v>
       </c>
       <c r="D663" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -46753,7 +46957,7 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
@@ -46813,6 +47017,1434 @@
         </is>
       </c>
       <c r="K664" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D665" t="n">
+        <v>31</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>22140</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D666" t="n">
+        <v>31</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>22158</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D667" t="n">
+        <v>31</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>22167</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D668" t="n">
+        <v>31</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>22187</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D669" t="n">
+        <v>31</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>22225</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D670" t="n">
+        <v>31</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>22233</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D671" t="n">
+        <v>31</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>22267</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D672" t="n">
+        <v>31</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>22272</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D673" t="n">
+        <v>31</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>22311</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D674" t="n">
+        <v>31</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D675" t="n">
+        <v>31</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D676" t="n">
+        <v>31</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>22452</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D677" t="n">
+        <v>31</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>22453</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D678" t="n">
+        <v>31</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>22454</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D679" t="n">
+        <v>31</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>22455</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D680" t="n">
+        <v>31</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>22456</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D681" t="n">
+        <v>31</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>22457</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D682" t="n">
+        <v>31</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>22458</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D683" t="n">
+        <v>31</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>22466</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D684" t="n">
+        <v>31</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>22469</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D685" t="n">
+        <v>31</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>22472</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D686" t="n">
+        <v>31</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>22473</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D687" t="n">
+        <v>31</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>22485</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D688" t="n">
+        <v>31</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>22487</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D689" t="n">
+        <v>31</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>22500</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D690" t="n">
+        <v>31</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>22517</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D691" t="n">
+        <v>31</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>22555</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D692" t="n">
+        <v>31</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>22562</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:K258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12745,16 +12745,16 @@
         <v>2026</v>
       </c>
       <c r="D242" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -12942,36 +12942,36 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Mara Moraes</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C246" t="n">
         <v>2026</v>
       </c>
       <c r="D246" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Mara Moraes</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="H247" s="2" t="n">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -13129,10 +13129,469 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D250" t="n">
+        <v>32</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>22885</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D251" t="n">
+        <v>32</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>22896</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D252" t="n">
+        <v>32</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>22930</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D253" t="n">
+        <v>32</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>22944</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D254" t="n">
+        <v>32</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D255" t="n">
+        <v>32</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>22149</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D256" t="n">
+        <v>32</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>22619</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D257" t="n">
+        <v>32</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>22908</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D258" t="n">
+        <v>32</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>22659</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -13149,7 +13608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K692"/>
+  <dimension ref="A1:K739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42498,16 +42957,16 @@
         <v>2026</v>
       </c>
       <c r="D576" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -42520,12 +42979,12 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
@@ -43239,7 +43698,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K590" t="inlineStr">
@@ -44691,16 +45150,16 @@
         <v>2026</v>
       </c>
       <c r="D619" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -44713,12 +45172,12 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
@@ -45959,23 +46418,23 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Guilherme Worel</t>
+          <t>Mateus Neckel</t>
         </is>
       </c>
       <c r="C644" t="n">
         <v>2026</v>
       </c>
       <c r="D644" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -45988,12 +46447,12 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -46017,16 +46476,16 @@
         <v>2026</v>
       </c>
       <c r="D645" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -46039,12 +46498,12 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -46272,16 +46731,16 @@
         <v>2026</v>
       </c>
       <c r="D650" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -46294,12 +46753,12 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -46374,16 +46833,16 @@
         <v>2026</v>
       </c>
       <c r="D652" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -46396,12 +46855,12 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -46476,16 +46935,16 @@
         <v>2026</v>
       </c>
       <c r="D654" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -46498,12 +46957,12 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -46962,7 +47421,7 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
@@ -47030,7 +47489,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Felipe Nascimento</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -47051,7 +47510,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="H665" s="2" t="n">
@@ -47064,7 +47523,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -47102,7 +47561,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="H666" s="2" t="n">
@@ -47115,7 +47574,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -47153,7 +47612,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="H667" s="2" t="n">
@@ -47166,7 +47625,7 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
@@ -47183,28 +47642,28 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C668" t="n">
         <v>2026</v>
       </c>
       <c r="D668" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="H668" s="2" t="n">
@@ -47212,12 +47671,12 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
@@ -47255,7 +47714,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>22562</t>
         </is>
       </c>
       <c r="H669" s="2" t="n">
@@ -47268,7 +47727,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
@@ -47285,41 +47744,41 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C670" t="n">
         <v>2026</v>
       </c>
       <c r="D670" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22140</t>
         </is>
       </c>
       <c r="H670" s="2" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
@@ -47336,41 +47795,41 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C671" t="n">
         <v>2026</v>
       </c>
       <c r="D671" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="H671" s="2" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
@@ -47387,7 +47846,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Gabriel López</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -47408,7 +47867,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="H672" s="2" t="n">
@@ -47421,7 +47880,7 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
@@ -47438,7 +47897,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -47459,7 +47918,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="H673" s="2" t="n">
@@ -47472,7 +47931,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
@@ -47489,7 +47948,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -47510,7 +47969,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="H674" s="2" t="n">
@@ -47523,7 +47982,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
@@ -47547,21 +48006,21 @@
         <v>2026</v>
       </c>
       <c r="D675" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="H675" s="2" t="n">
@@ -47569,12 +48028,12 @@
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
@@ -47612,7 +48071,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="H676" s="2" t="n">
@@ -47625,7 +48084,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
@@ -47663,7 +48122,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="H677" s="2" t="n">
@@ -47676,7 +48135,7 @@
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
@@ -47714,7 +48173,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="H678" s="2" t="n">
@@ -47727,7 +48186,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
@@ -47765,7 +48224,7 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="H679" s="2" t="n">
@@ -47778,7 +48237,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
@@ -47816,7 +48275,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="H680" s="2" t="n">
@@ -47829,7 +48288,7 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
@@ -47867,7 +48326,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="H681" s="2" t="n">
@@ -47880,7 +48339,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
@@ -47918,7 +48377,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="H682" s="2" t="n">
@@ -47931,7 +48390,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
@@ -47969,7 +48428,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="H683" s="2" t="n">
@@ -47982,7 +48441,7 @@
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
@@ -48020,7 +48479,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="H684" s="2" t="n">
@@ -48033,7 +48492,7 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
@@ -48050,7 +48509,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -48071,7 +48530,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="H685" s="2" t="n">
@@ -48084,7 +48543,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
@@ -48135,7 +48594,7 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
@@ -48186,7 +48645,7 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
@@ -48210,16 +48669,16 @@
         <v>2026</v>
       </c>
       <c r="D688" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -48232,12 +48691,12 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
@@ -48288,7 +48747,7 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
@@ -48326,7 +48785,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="H690" s="2" t="n">
@@ -48339,7 +48798,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -48356,7 +48815,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -48377,7 +48836,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="H691" s="2" t="n">
@@ -48390,7 +48849,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
@@ -48407,28 +48866,28 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C692" t="n">
         <v>2026</v>
       </c>
       <c r="D692" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="H692" s="2" t="n">
@@ -48436,15 +48895,2412 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pentende</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D693" t="n">
+        <v>32</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>22708</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D694" t="n">
+        <v>32</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>22577</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D695" t="n">
+        <v>32</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>22383</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D696" t="n">
+        <v>32</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>22647</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D697" t="n">
+        <v>32</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>22803</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D698" t="n">
+        <v>32</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>22583</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D699" t="n">
+        <v>32</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>22660</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D700" t="n">
+        <v>32</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>22993</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D701" t="n">
+        <v>32</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>23042</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D702" t="n">
+        <v>32</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>22483</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D703" t="n">
+        <v>32</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>22605</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D704" t="n">
+        <v>32</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>22680</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D705" t="n">
+        <v>32</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>22718</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D706" t="n">
+        <v>32</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>22720</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D707" t="n">
+        <v>32</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>22725</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D708" t="n">
+        <v>32</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>22730</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D709" t="n">
+        <v>32</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>22743</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D710" t="n">
+        <v>32</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>22744</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D711" t="n">
+        <v>32</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>22775</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D712" t="n">
+        <v>32</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>22784</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D713" t="n">
+        <v>32</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>22791</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D714" t="n">
+        <v>32</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>22797</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D715" t="n">
+        <v>32</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D716" t="n">
+        <v>32</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>22814</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D717" t="n">
+        <v>32</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>22815</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D718" t="n">
+        <v>32</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>22816</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D719" t="n">
+        <v>32</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>22821</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D720" t="n">
+        <v>32</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>22824</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D721" t="n">
+        <v>32</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>22835</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D722" t="n">
+        <v>32</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>22836</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D723" t="n">
+        <v>32</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>22844</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D724" t="n">
+        <v>32</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>22847</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D725" t="n">
+        <v>32</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D726" t="n">
+        <v>32</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>22863</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D727" t="n">
+        <v>32</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>22866</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D728" t="n">
+        <v>32</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>22867</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D729" t="n">
+        <v>32</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>22898</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D730" t="n">
+        <v>32</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>22899</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D731" t="n">
+        <v>32</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>22904</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>Pentende</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
